--- a/db/A7XLK-1102-HouseBigData.xlsx
+++ b/db/A7XLK-1102-HouseBigData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou2/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDE0790-8FCC-5B4E-B83E-D526BAA1D4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B5E95F-1D2B-DC49-B5D3-E9EC847DF650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10900" yWindow="580" windowWidth="39980" windowHeight="22540" activeTab="12" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
+    <workbookView xWindow="560" yWindow="500" windowWidth="39920" windowHeight="22540" activeTab="12" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure-1" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,8 @@
     <sheet name="Figure-10" sheetId="11" r:id="rId10"/>
     <sheet name="Figure-11" sheetId="12" r:id="rId11"/>
     <sheet name="Analysis-01" sheetId="13" r:id="rId12"/>
-    <sheet name="建案資料" sheetId="1" r:id="rId13"/>
+    <sheet name="車位分配" sheetId="14" r:id="rId13"/>
+    <sheet name="建案資料" sheetId="1" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'Figure-8'!$E$4:$E$48</definedName>
@@ -34,8 +35,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId14"/>
-    <pivotCache cacheId="8" r:id="rId15"/>
+    <pivotCache cacheId="0" r:id="rId15"/>
+    <pivotCache cacheId="6" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2453" uniqueCount="1153">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -6794,6 +6795,432 @@
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[A7XLK-1102-HouseBigData.xlsx]車位分配!樞紐分析表1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="2800" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>A7</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2800" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>重劃區 每戶汽車車位配比</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>車位分配!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>合計</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>車位分配!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>中心商業區</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>產業專用區</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>第三種住宅區</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>第五種住宅區</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>第四種住宅區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>車位分配!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.94555555555555548</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.07</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.98066666666666669</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0011111111111111</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8018-9949-9B7B-FFD386E572CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
+        <c:axId val="688088991"/>
+        <c:axId val="688462959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="688088991"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="688462959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="688462959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="688088991"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -15400,6 +15827,46 @@
 </file>
 
 <file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -17244,6 +17711,509 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx2"/>
     </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -21523,6 +22493,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF47C3FE-1D93-FA4B-90CE-EB786D8CB8CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -22538,7 +23549,57 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="建案" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="49">
+        <s v="和發大境"/>
+        <s v="鴻典"/>
+        <s v="樂捷市"/>
+        <s v="奇幻莊園"/>
+        <s v="樂田田"/>
+        <s v="玉子園"/>
+        <s v="台北國際村"/>
+        <s v="富宇上城"/>
+        <s v="禾悅花園"/>
+        <s v="耀台北"/>
+        <s v="皇普MVP"/>
+        <s v="富宇敦峰"/>
+        <s v="玄泰V1"/>
+        <s v="和耀恆美"/>
+        <s v="允將大作"/>
+        <s v="欣時代"/>
+        <s v="新潤翡麗"/>
+        <s v="新潤鉑麗"/>
+        <s v="根津苑"/>
+        <s v="華悅城"/>
+        <s v="富宇悅峰"/>
+        <s v="合遠新天地"/>
+        <s v="友文化"/>
+        <s v="水悅青青"/>
+        <s v="文華天際"/>
+        <s v="竹城甲子園"/>
+        <s v="金捷市"/>
+        <s v="鴻築捷市達"/>
+        <s v="詠勝市中欣"/>
+        <s v="新A7"/>
+        <s v="富御捷境"/>
+        <s v="富宇哈佛苑"/>
+        <s v="頤昌豐岳"/>
+        <s v="新未來2"/>
+        <s v="新未來3"/>
+        <s v="和洲金剛"/>
+        <s v="君邑丘比特"/>
+        <s v="頤昌璞岳"/>
+        <s v="合謙學"/>
+        <s v="大亮時代A7"/>
+        <s v="新未來1"/>
+        <s v="富宇天匯"/>
+        <s v="竹城明治"/>
+        <s v="竹城宇治"/>
+        <s v="櫻花澍"/>
+        <s v="遠雄文青"/>
+        <s v="皇翔歡喜城"/>
+        <s v="名軒快樂家"/>
+        <s v="麗寶快樂家"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="N建案" numFmtId="0">
       <sharedItems/>
@@ -22661,10 +23722,62 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="車位配比" numFmtId="49">
-      <sharedItems containsBlank="1"/>
+      <sharedItems containsBlank="1" count="25">
+        <s v="1:1.09"/>
+        <s v="1:1.03"/>
+        <s v="1:1"/>
+        <s v="1:0.98"/>
+        <s v="1:0.87"/>
+        <s v="1:0.99"/>
+        <s v="1:1.12"/>
+        <s v="1:1.02"/>
+        <s v="1:1.01"/>
+        <s v="1:1.04"/>
+        <s v="1:1.05"/>
+        <s v="1:0.91"/>
+        <s v="1:0.73"/>
+        <s v="1:0.9"/>
+        <s v="1:0.86"/>
+        <s v="1:0.88"/>
+        <s v="1:1.06"/>
+        <s v="1:0.97"/>
+        <s v="1:1.17"/>
+        <s v="1:1.14"/>
+        <s v="1:1.07"/>
+        <s v="1:0.36"/>
+        <s v="1:0.89"/>
+        <s v="1:0.75"/>
+        <m/>
+      </sharedItems>
     </cacheField>
     <cacheField name="車位分配率" numFmtId="178">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.36" maxValue="1.17"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.36" maxValue="1.17" count="25">
+        <n v="1.0900000000000001"/>
+        <n v="1.03"/>
+        <n v="1"/>
+        <n v="0.98"/>
+        <n v="0.87"/>
+        <n v="0.99"/>
+        <n v="1.1200000000000001"/>
+        <n v="1.02"/>
+        <n v="1.01"/>
+        <n v="1.04"/>
+        <n v="1.05"/>
+        <n v="0.91"/>
+        <n v="0.73"/>
+        <n v="0.9"/>
+        <n v="0.86"/>
+        <n v="0.88"/>
+        <n v="1.06"/>
+        <n v="0.97"/>
+        <n v="1.17"/>
+        <n v="1.1399999999999999"/>
+        <n v="1.07"/>
+        <n v="0.36"/>
+        <n v="0.89"/>
+        <n v="0.75"/>
+        <m/>
+      </sharedItems>
     </cacheField>
     <cacheField name="結構工程" numFmtId="0">
       <sharedItems/>
@@ -22679,7 +23792,13 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="土地分區" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="5">
+        <s v="第四種住宅區"/>
+        <s v="產業專用區"/>
+        <s v="第五種住宅區"/>
+        <s v="中心商業區"/>
+        <s v="第三種住宅區"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="物業公司" numFmtId="0">
       <sharedItems containsBlank="1"/>
@@ -25516,7 +26635,7 @@
   <r>
     <s v="101"/>
     <s v="1.樂善國小生活圈"/>
-    <s v="和發大境"/>
+    <x v="0"/>
     <s v="101 和發大境"/>
     <s v="fig/AiCity-939-和發大境.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=125726"/>
@@ -25557,13 +26676,13 @@
     <n v="15"/>
     <s v="平面式318個"/>
     <s v="待定"/>
-    <s v="1:1.09"/>
-    <n v="1.0900000000000001"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="RC"/>
     <s v="1586.57坪"/>
     <n v="1586.57"/>
     <s v="住商用"/>
-    <s v="第四種住宅區"/>
+    <x v="0"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第00546-01號"/>
@@ -25574,7 +26693,7 @@
   <r>
     <s v="102"/>
     <s v="1.樂善國小生活圈"/>
-    <s v="鴻典"/>
+    <x v="1"/>
     <s v="102 鴻典"/>
     <s v="fig/AiCity-939-鴻典.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122584&amp;v=720"/>
@@ -25615,13 +26734,13 @@
     <n v="15"/>
     <s v="平面式214個"/>
     <s v="60元/坪/月"/>
-    <s v="1:1.03"/>
-    <n v="1.03"/>
+    <x v="1"/>
+    <x v="1"/>
     <s v="RC"/>
     <s v="1062.93坪"/>
     <n v="1062.93"/>
     <s v="住商用"/>
-    <s v="第四種住宅區"/>
+    <x v="0"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="107桃市都建執照字第01412-01號等1個"/>
@@ -25632,7 +26751,7 @@
   <r>
     <s v="103"/>
     <s v="1.樂善國小生活圈"/>
-    <s v="樂捷市"/>
+    <x v="2"/>
     <s v="103 樂捷市"/>
     <s v="fig/AiCity-939-樂捷市.jpeg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=116751&amp;v=720"/>
@@ -25673,13 +26792,13 @@
     <n v="15"/>
     <s v="平面式285個、機械式61個"/>
     <s v="待定"/>
-    <s v="1:1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="RC"/>
     <s v="1848.44坪"/>
     <n v="1848.44"/>
     <s v="住商用"/>
-    <s v="第四種住宅區"/>
+    <x v="0"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="（106)桃市都建執照字第00372號等1個"/>
@@ -25690,7 +26809,7 @@
   <r>
     <s v="104"/>
     <s v="1.樂善國小生活圈"/>
-    <s v="奇幻莊園"/>
+    <x v="3"/>
     <s v="104 奇幻莊園"/>
     <s v="fig/AiCity-939-奇幻莊園.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=116476&amp;v=720"/>
@@ -25731,13 +26850,13 @@
     <n v="14"/>
     <s v="平面式181個、機械式61個"/>
     <s v="55元/坪/月"/>
-    <s v="1:0.98"/>
-    <n v="0.98"/>
+    <x v="3"/>
+    <x v="3"/>
     <s v="RC"/>
     <s v="954.46坪"/>
     <n v="954.46"/>
     <s v="住商用"/>
-    <s v="第四種住宅區"/>
+    <x v="0"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="106桃市都建執照字第01160-01號"/>
@@ -25748,7 +26867,7 @@
   <r>
     <s v="105"/>
     <s v="1.樂善國小生活圈"/>
-    <s v="樂田田"/>
+    <x v="4"/>
     <s v="105 樂田田"/>
     <s v="fig/AiCity-939-樂甜甜.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=121200&amp;v=720"/>
@@ -25789,13 +26908,13 @@
     <n v="14"/>
     <s v="平面式173個"/>
     <s v="55元/坪/月"/>
-    <s v="1:0.87"/>
-    <n v="0.87"/>
+    <x v="4"/>
+    <x v="4"/>
     <s v="RC"/>
     <s v="907.61坪"/>
     <n v="907.61"/>
     <s v="住商用"/>
-    <s v="第四種住宅區"/>
+    <x v="0"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第00290-01號"/>
@@ -25806,7 +26925,7 @@
   <r>
     <s v="106"/>
     <s v="1.樂善國小生活圈"/>
-    <s v="玉子園"/>
+    <x v="5"/>
     <s v="106 玉子園"/>
     <s v="fig/AiCity-939-玉子園.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=119531&amp;v=720"/>
@@ -25847,13 +26966,13 @@
     <n v="15"/>
     <s v="平面式178個、機械式14個"/>
     <s v="待定"/>
-    <s v="1:0.99"/>
-    <n v="0.99"/>
+    <x v="5"/>
+    <x v="5"/>
     <s v="RC"/>
     <s v="1042.98坪"/>
     <n v="1042.98"/>
     <s v="住商用"/>
-    <s v="第四種住宅區"/>
+    <x v="0"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(106)桃市都建執照字第會龜00880-01號等1個"/>
@@ -25864,7 +26983,7 @@
   <r>
     <s v="107"/>
     <s v="1.樂善國小生活圈"/>
-    <s v="台北國際村"/>
+    <x v="6"/>
     <s v="107 台北國際村"/>
     <s v="fig/AiCity-939-台北國際村.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=118714&amp;v=720"/>
@@ -25905,13 +27024,13 @@
     <n v="15"/>
     <s v="平面式206個"/>
     <s v="待定"/>
-    <s v="1:1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="RC"/>
     <s v="1054.47坪"/>
     <n v="1054.47"/>
     <s v="住商用"/>
-    <s v="第四種住宅區"/>
+    <x v="0"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(107)桃市都建執照字第會龜01092-01號等1個"/>
@@ -25922,7 +27041,7 @@
   <r>
     <s v="201"/>
     <s v="2.樂善園區周邊"/>
-    <s v="富宇上城"/>
+    <x v="7"/>
     <s v="201 富宇上城"/>
     <s v="fig/AiCity-939-富宇上城.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=121156&amp;v=720"/>
@@ -25963,13 +27082,13 @@
     <n v="24"/>
     <s v="平面式933個"/>
     <s v="75元/坪/月"/>
-    <s v="1:1.12"/>
-    <n v="1.1200000000000001"/>
+    <x v="6"/>
+    <x v="6"/>
     <s v="RC"/>
     <s v="4046.9坪"/>
     <n v="4046.9"/>
     <s v="住商用"/>
-    <s v="產業專用區"/>
+    <x v="1"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(107)桃市都建執照字第會龜00519-01號等1個"/>
@@ -25980,7 +27099,7 @@
   <r>
     <s v="202"/>
     <s v="2.樂善園區周邊"/>
-    <s v="禾悅花園"/>
+    <x v="8"/>
     <s v="202 禾悅花園"/>
     <s v="fig/AiCity-939-禾悅花園.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122734&amp;v=720"/>
@@ -26021,13 +27140,13 @@
     <n v="15"/>
     <s v="平面式1068個"/>
     <s v="65元/坪/月"/>
-    <s v="1:1.02"/>
-    <n v="1.02"/>
+    <x v="7"/>
+    <x v="7"/>
     <s v="RC"/>
     <s v="4720.89坪"/>
     <n v="4720.8900000000003"/>
     <s v="住商用"/>
-    <s v="產業專用區"/>
+    <x v="1"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="109桃市都建執照字第00083號等1個"/>
@@ -26038,7 +27157,7 @@
   <r>
     <s v="203"/>
     <s v="2.樂善園區周邊"/>
-    <s v="耀台北"/>
+    <x v="9"/>
     <s v="203 耀台北"/>
     <s v="fig/AiCity-939-耀台北.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=118336&amp;v=720"/>
@@ -26079,13 +27198,13 @@
     <n v="15"/>
     <s v="平面式139個、機械式65個"/>
     <s v="待定"/>
-    <s v="1:1.01"/>
-    <n v="1.01"/>
+    <x v="8"/>
+    <x v="8"/>
     <s v="RC"/>
     <s v="909.91坪"/>
     <n v="909.91"/>
     <s v="住商用"/>
-    <s v="第四種住宅區"/>
+    <x v="0"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(107)桃市都建執照字第會龜00614號等1個"/>
@@ -26096,7 +27215,7 @@
   <r>
     <s v="204"/>
     <s v="2.樂善園區周邊"/>
-    <s v="皇普MVP"/>
+    <x v="10"/>
     <s v="204 皇普MVP"/>
     <s v="fig/AiCity-939-皇普MVP.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=118186"/>
@@ -26137,13 +27256,13 @@
     <n v="15"/>
     <s v="平面式276個、機械式45個"/>
     <s v="50元/坪/月"/>
-    <s v="1:1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="RC"/>
     <s v="1390.39坪"/>
     <n v="1390.39"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(107)桃市都建執照字第會龜01075號"/>
@@ -26154,7 +27273,7 @@
   <r>
     <s v="205"/>
     <s v="2.樂善園區周邊"/>
-    <s v="富宇敦峰"/>
+    <x v="11"/>
     <s v="205 富宇敦峰"/>
     <s v="fig/AiCity-939-富宇敦峰.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=116430&amp;v=720"/>
@@ -26195,13 +27314,13 @@
     <n v="15"/>
     <s v="平面式465個"/>
     <s v="65元/坪/月"/>
-    <s v="1:1.04"/>
-    <n v="1.04"/>
+    <x v="9"/>
+    <x v="9"/>
     <s v="RC"/>
     <s v="2727.34坪"/>
     <n v="2727.34"/>
     <s v="住商用"/>
-    <s v="第四種住宅區"/>
+    <x v="0"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="107桃市都建執照0680號等1個"/>
@@ -26212,7 +27331,7 @@
   <r>
     <s v="206"/>
     <s v="2.樂善園區周邊"/>
-    <s v="玄泰V1"/>
+    <x v="12"/>
     <s v="206 玄泰V1"/>
     <s v="fig/AiCity-939-玄泰V1.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=120098&amp;v=720"/>
@@ -26253,13 +27372,13 @@
     <n v="24"/>
     <s v="平面式284個"/>
     <s v="待定"/>
-    <s v="1:1.05"/>
-    <n v="1.05"/>
+    <x v="10"/>
+    <x v="10"/>
     <s v="RC"/>
     <s v="911.52坪"/>
     <n v="911.52"/>
     <s v="住商用"/>
-    <s v="中心商業區"/>
+    <x v="3"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(108)桃市都建執照字第會龜00216號等1個"/>
@@ -26270,7 +27389,7 @@
   <r>
     <s v="207"/>
     <s v="2.樂善園區周邊"/>
-    <s v="和耀恆美"/>
+    <x v="13"/>
     <s v="207 和耀恆美"/>
     <s v="fig/AiCity-939-和耀恆美.jpeg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122650&amp;v=720"/>
@@ -26311,13 +27430,13 @@
     <n v="15"/>
     <s v="平面式236個、機械式59個"/>
     <s v="待定"/>
-    <s v="1:1.01"/>
-    <n v="1.01"/>
+    <x v="8"/>
+    <x v="8"/>
     <s v="RC"/>
     <s v="1309.14坪"/>
     <n v="1309.1400000000001"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <m/>
     <s v="暫無"/>
     <s v="107桃市都建執照字第00925-01號"/>
@@ -26328,7 +27447,7 @@
   <r>
     <s v="301"/>
     <s v="3.華亞園區周邊"/>
-    <s v="允將大作"/>
+    <x v="14"/>
     <s v="301 允將大作"/>
     <s v="fig/AiCity-939-允將大作.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=124450"/>
@@ -26369,13 +27488,13 @@
     <n v="31"/>
     <s v="平面式563個"/>
     <s v="80元/坪/月"/>
-    <s v="1:1.01"/>
-    <n v="1.01"/>
+    <x v="8"/>
+    <x v="8"/>
     <s v="RC"/>
     <s v="1554.48坪"/>
     <n v="1554.48"/>
     <s v="住商用"/>
-    <s v="中心商業區"/>
+    <x v="3"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="106桃市都建執照字第00391-01號"/>
@@ -26386,7 +27505,7 @@
   <r>
     <s v="302"/>
     <s v="3.華亞園區周邊"/>
-    <s v="欣時代"/>
+    <x v="15"/>
     <s v="302 欣時代"/>
     <s v="fig/AiCity-939-欣時代.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=118905"/>
@@ -26427,13 +27546,13 @@
     <n v="30"/>
     <s v="平面式235個"/>
     <s v="待定"/>
-    <s v="1:0.91"/>
-    <n v="0.91"/>
+    <x v="11"/>
+    <x v="11"/>
     <s v="RC"/>
     <s v="713.17坪"/>
     <n v="713.17"/>
     <s v="住商用"/>
-    <s v="中心商業區"/>
+    <x v="3"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(106)桃市都建執照字第會龜00288-02號等1個"/>
@@ -26444,7 +27563,7 @@
   <r>
     <s v="303"/>
     <s v="3.華亞園區周邊"/>
-    <s v="新潤翡麗"/>
+    <x v="16"/>
     <s v="303 新潤翡麗"/>
     <s v="fig/AiCity-939-新潤翡麗.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=117434&amp;v=720"/>
@@ -26485,13 +27604,13 @@
     <n v="24"/>
     <s v="平面式330個"/>
     <s v="待定"/>
-    <s v="1:0.73"/>
-    <n v="0.73"/>
+    <x v="12"/>
+    <x v="12"/>
     <s v="RC"/>
     <s v="1083.97坪"/>
     <n v="1083.97"/>
     <s v="住商用"/>
-    <s v="中心商業區"/>
+    <x v="3"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(106)桃市都建執照字第會龜00984-01號等1個"/>
@@ -26502,7 +27621,7 @@
   <r>
     <s v="304"/>
     <s v="3.華亞園區周邊"/>
-    <s v="新潤鉑麗"/>
+    <x v="17"/>
     <s v="304 新潤鉑麗"/>
     <s v="fig/AiCity-939-新潤鉑麗.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=119614"/>
@@ -26543,13 +27662,13 @@
     <n v="15"/>
     <s v="平面式243個"/>
     <s v="80元/坪/月"/>
-    <s v="1:0.87"/>
-    <n v="0.87"/>
+    <x v="4"/>
+    <x v="4"/>
     <s v="RC"/>
     <s v="1137.47坪"/>
     <n v="1137.47"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="107桃市都建執照字第龜01089-01號"/>
@@ -26560,7 +27679,7 @@
   <r>
     <s v="305"/>
     <s v="3.華亞園區周邊"/>
-    <s v="根津苑"/>
+    <x v="18"/>
     <s v="305 根津苑"/>
     <s v="fig/AiCity-939-根津苑.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=118143&amp;v=720"/>
@@ -26601,13 +27720,13 @@
     <n v="15"/>
     <s v="平面式228個"/>
     <s v="待定"/>
-    <s v="1:1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="RC"/>
     <s v="1848.44坪"/>
     <n v="1848.44"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(107)桃市都建執照字第會龜00667號等1個"/>
@@ -26618,7 +27737,7 @@
   <r>
     <s v="306"/>
     <s v="3.華亞園區周邊"/>
-    <s v="華悅城"/>
+    <x v="19"/>
     <s v="306 華悅城"/>
     <s v="fig/AiCity-939-華悅城.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=120741"/>
@@ -26659,13 +27778,13 @@
     <n v="18"/>
     <s v="平面式590個、機械式119個"/>
     <s v="待定"/>
-    <s v="1:0.9"/>
-    <n v="0.9"/>
+    <x v="13"/>
+    <x v="13"/>
     <s v="RC"/>
     <s v="2751.33坪"/>
     <n v="2751.33"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(108)桃市都建執照字第會龜00410-01號"/>
@@ -26676,7 +27795,7 @@
   <r>
     <s v="307"/>
     <s v="3.華亞園區周邊"/>
-    <s v="富宇悅峰"/>
+    <x v="20"/>
     <s v="307 富宇悅峰"/>
     <s v="fig/AiCity-939-富宇悅峰.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=119483&amp;v=720"/>
@@ -26717,13 +27836,13 @@
     <n v="14"/>
     <s v="平面式227個"/>
     <s v="70元/坪/月"/>
-    <s v="1:0.86"/>
-    <n v="0.86"/>
+    <x v="14"/>
+    <x v="14"/>
     <s v="RC"/>
     <s v="1266.01坪"/>
     <n v="1266.01"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(108)桃市都建執照字第會龜00334號等1個"/>
@@ -26734,7 +27853,7 @@
   <r>
     <s v="308"/>
     <s v="3.華亞園區周邊"/>
-    <s v="合遠新天地"/>
+    <x v="21"/>
     <s v="308 合遠新天地"/>
     <s v="fig/AiCity-939-合遠新天地.jpeg"/>
     <m/>
@@ -26775,13 +27894,13 @@
     <n v="15"/>
     <s v="平面式104個、機械式14個"/>
     <s v="待定"/>
-    <s v="1:1.02"/>
-    <n v="1.02"/>
+    <x v="7"/>
+    <x v="7"/>
     <s v="RC"/>
     <s v="642.92坪"/>
     <n v="642.91999999999996"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(106)桃市都建執照字第會龜01161-01號等1個"/>
@@ -26792,7 +27911,7 @@
   <r>
     <s v="309"/>
     <s v="3.華亞園區周邊"/>
-    <s v="友文化"/>
+    <x v="22"/>
     <s v="309 友文化"/>
     <s v="fig/AiCity-939-友文化.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/info?hid=121155"/>
@@ -26833,13 +27952,13 @@
     <n v="15"/>
     <s v="平面式279個、機械式26個"/>
     <s v="50元/坪/月"/>
-    <s v="1:1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="RC"/>
     <s v="1426.7坪"/>
     <n v="1426.7"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(108)桃市都建執照字第會龜00050號"/>
@@ -26850,7 +27969,7 @@
   <r>
     <s v="310"/>
     <s v="3.華亞園區周邊"/>
-    <s v="水悅青青"/>
+    <x v="23"/>
     <s v="310 水悅青青"/>
     <s v="fig/AiCity-939-水悅青青.webp"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=125625"/>
@@ -26891,13 +28010,13 @@
     <n v="14"/>
     <s v="平面式211個"/>
     <s v="待定"/>
-    <s v="1:1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="RC"/>
     <s v="910.52坪"/>
     <n v="910.52"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <m/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第00167號"/>
@@ -26908,7 +28027,7 @@
   <r>
     <s v="311"/>
     <s v="3.華亞園區周邊"/>
-    <s v="文華天際"/>
+    <x v="24"/>
     <s v="311 文華天際"/>
     <s v="fig/AiCity-939-文華天際.png"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=127139"/>
@@ -26949,13 +28068,13 @@
     <n v="22"/>
     <s v="平面式440個、機械式46個"/>
     <s v="待定"/>
-    <s v="1:1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="RC"/>
     <s v="1998.07坪"/>
     <n v="1998.07"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <m/>
     <s v="暫無"/>
     <s v="109桃市都建執照字第00376-01號"/>
@@ -26966,7 +28085,7 @@
   <r>
     <s v="401"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="竹城甲子園"/>
+    <x v="25"/>
     <s v="401 竹城甲子園"/>
     <s v="fig/AiCity-939-竹城甲子園.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=119261&amp;v=720"/>
@@ -27007,13 +28126,13 @@
     <n v="24"/>
     <s v="平面式1063個"/>
     <s v="待定"/>
-    <s v="1:0.88"/>
-    <n v="0.88"/>
+    <x v="15"/>
+    <x v="15"/>
     <s v="RC"/>
     <s v="4352.46坪"/>
     <n v="4352.46"/>
     <s v="住商用"/>
-    <s v="中心商業區"/>
+    <x v="3"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(106)桃市都建執照字第會龜01249-02號等1個"/>
@@ -27024,7 +28143,7 @@
   <r>
     <s v="402"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="金捷市"/>
+    <x v="26"/>
     <s v="402 金捷市"/>
     <s v="fig/AiCity-939-金捷市.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=116107&amp;v=720"/>
@@ -27065,13 +28184,13 @@
     <n v="28"/>
     <s v="平面式822個"/>
     <s v="待定"/>
-    <s v="1:1.06"/>
-    <n v="1.06"/>
+    <x v="16"/>
+    <x v="16"/>
     <s v="RC"/>
     <s v="2090.31坪"/>
     <n v="2090.31"/>
     <s v="住商用"/>
-    <s v="中心商業區"/>
+    <x v="3"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(106)桃市都建執照字第會龜00822號等1個"/>
@@ -27082,7 +28201,7 @@
   <r>
     <s v="403"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="鴻築捷市達"/>
+    <x v="27"/>
     <s v="403 鴻築捷市達"/>
     <s v="fig/AiCity-939-鴻築捷市達.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122649&amp;v=720"/>
@@ -27123,13 +28242,13 @@
     <n v="29"/>
     <s v="平面式778個"/>
     <s v="待定"/>
-    <s v="1:0.97"/>
-    <n v="0.97"/>
+    <x v="17"/>
+    <x v="17"/>
     <s v="RC"/>
     <s v="2067.24坪"/>
     <n v="2067.2399999999998"/>
     <s v="住商用"/>
-    <s v="中心商業區"/>
+    <x v="3"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第00438-01號等1個"/>
@@ -27140,7 +28259,7 @@
   <r>
     <s v="404"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="詠勝市中欣"/>
+    <x v="28"/>
     <s v="404 詠勝市中欣"/>
     <s v="fig/AiCity-939-詠勝市中欣.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=120096&amp;v=720"/>
@@ -27181,13 +28300,13 @@
     <n v="22"/>
     <s v="平面式298個"/>
     <s v="待定"/>
-    <s v="1:1.01"/>
-    <n v="1.01"/>
+    <x v="8"/>
+    <x v="8"/>
     <s v="RC"/>
     <s v="926.66坪"/>
     <n v="926.66"/>
     <s v="住商用"/>
-    <s v="中心商業區"/>
+    <x v="3"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(106)桃市都建執照字第會龜00159-01號等1個"/>
@@ -27198,7 +28317,7 @@
   <r>
     <s v="405"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="新A7"/>
+    <x v="29"/>
     <s v="405 新A7"/>
     <s v="fig/AiCity-939-新A7.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122651"/>
@@ -27239,13 +28358,13 @@
     <n v="15"/>
     <s v="平面式143個、機械式232個"/>
     <s v="待定"/>
-    <s v="1:1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="RC"/>
     <s v="1538.68坪"/>
     <n v="1538.68"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第00568-02號"/>
@@ -27256,7 +28375,7 @@
   <r>
     <s v="406"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="富御捷境"/>
+    <x v="30"/>
     <s v="406 富御捷境"/>
     <s v="fig/AiCity-939-富御捷境.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=116475"/>
@@ -27297,13 +28416,13 @@
     <n v="15"/>
     <s v="平面式180個、機械式125個"/>
     <s v="待定"/>
-    <s v="1:0.9"/>
-    <n v="0.9"/>
+    <x v="13"/>
+    <x v="13"/>
     <s v="RC"/>
     <s v="1359.03坪"/>
     <n v="1359.03"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(106)桃市都建執照字第會龜01237 號等1個"/>
@@ -27314,7 +28433,7 @@
   <r>
     <s v="407"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="富宇哈佛苑"/>
+    <x v="31"/>
     <s v="407 富宇哈佛苑"/>
     <s v="fig/AiCity-939-富宇哈佛苑.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=121157&amp;v=720"/>
@@ -27355,13 +28474,13 @@
     <n v="24"/>
     <s v="平面式495個"/>
     <s v="70元/坪/月"/>
-    <s v="1:1.01"/>
-    <n v="1.01"/>
+    <x v="8"/>
+    <x v="8"/>
     <s v="RC"/>
     <s v="2155.85坪"/>
     <n v="2155.85"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第00961號等1個"/>
@@ -27372,7 +28491,7 @@
   <r>
     <s v="408"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="頤昌豐岳"/>
+    <x v="32"/>
     <s v="408 頤昌豐岳"/>
     <s v="fig/AiCity-939-頤昌豐岳.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/info?hid=122055"/>
@@ -27413,13 +28532,13 @@
     <n v="15"/>
     <s v="平面式190個"/>
     <s v="待定"/>
-    <s v="1:1.17"/>
-    <n v="1.17"/>
+    <x v="18"/>
+    <x v="18"/>
     <s v="RC"/>
     <s v="933.78坪"/>
     <n v="933.78"/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第01005-01號"/>
@@ -27430,7 +28549,7 @@
   <r>
     <s v="409"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="新未來2"/>
+    <x v="33"/>
     <s v="409 新未來2"/>
     <s v="fig/AiCity-939-新未來2.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/info?hid=118904"/>
@@ -27471,13 +28590,13 @@
     <n v="22"/>
     <s v="平面式438個"/>
     <s v="待定"/>
-    <s v="1:1.14"/>
-    <n v="1.1399999999999999"/>
+    <x v="19"/>
+    <x v="19"/>
     <s v="RC"/>
     <s v="1955.56坪"/>
     <n v="1955.56"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(107)桃市字第會龜00687號"/>
@@ -27488,7 +28607,7 @@
   <r>
     <s v="410"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="新未來3"/>
+    <x v="34"/>
     <s v="410 新未來3"/>
     <s v="fig/AiCity-939-新未來3.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/info?hid=122831"/>
@@ -27529,13 +28648,13 @@
     <n v="22"/>
     <s v="平面式598個"/>
     <s v="待定"/>
-    <s v="1:1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="RC"/>
     <s v="2513.22坪"/>
     <n v="2513.2199999999998"/>
     <s v="住商用"/>
-    <s v="第五種住宅區"/>
+    <x v="2"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="109桃市都建執照字第00076號"/>
@@ -27546,7 +28665,7 @@
   <r>
     <s v="411"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="和洲金剛"/>
+    <x v="35"/>
     <s v="411 和洲金剛"/>
     <s v="fig/AiCity-939-和洲金剛.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122486&amp;v=720"/>
@@ -27587,13 +28706,13 @@
     <n v="15"/>
     <s v="平面式226個"/>
     <s v="待定"/>
-    <s v="1:1.02"/>
-    <n v="1.02"/>
+    <x v="7"/>
+    <x v="7"/>
     <s v="RC"/>
     <s v="1359.03坪"/>
     <n v="1359.03"/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <s v="國原保全"/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第00611號等1個"/>
@@ -27604,7 +28723,7 @@
   <r>
     <s v="412"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="君邑丘比特"/>
+    <x v="36"/>
     <s v="412 君邑丘比特"/>
     <s v="fig/AiCity-939-邱比特.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=121781&amp;"/>
@@ -27645,13 +28764,13 @@
     <n v="15"/>
     <s v="平面式190個"/>
     <s v="待定"/>
-    <s v="1:1.07"/>
-    <n v="1.07"/>
+    <x v="20"/>
+    <x v="20"/>
     <s v="RC"/>
     <s v="1030.74坪"/>
     <n v="1030.74"/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第00488-01號等1個"/>
@@ -27662,7 +28781,7 @@
   <r>
     <s v="413"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="頤昌璞岳"/>
+    <x v="37"/>
     <s v="413 頤昌璞岳"/>
     <s v="fig/AiCity-939-頤昌璞岳.jpeg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=124978"/>
@@ -27703,13 +28822,13 @@
     <n v="14"/>
     <s v="平面式136個"/>
     <s v="待定"/>
-    <s v="1:1.01"/>
-    <n v="1.01"/>
+    <x v="8"/>
+    <x v="8"/>
     <s v="RC"/>
     <s v="595.29坪"/>
     <n v="595.29"/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="109桃市都建執照字第00379-01號"/>
@@ -27720,7 +28839,7 @@
   <r>
     <s v="414"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="合謙學"/>
+    <x v="38"/>
     <s v="414 合謙學"/>
     <s v="fig/AiCity-939-合謙學.webp"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=126450"/>
@@ -27761,13 +28880,13 @@
     <n v="14"/>
     <s v="平面式96個"/>
     <s v="70元/坪/月"/>
-    <s v="1:0.91"/>
-    <n v="0.91"/>
+    <x v="11"/>
+    <x v="11"/>
     <s v="RC"/>
     <s v="1030.74坪"/>
     <n v="1030.74"/>
     <s v="住家用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <m/>
     <m/>
     <m/>
@@ -27778,7 +28897,7 @@
   <r>
     <s v="415"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
-    <s v="大亮時代A7"/>
+    <x v="39"/>
     <s v="415 大亮時代A7"/>
     <s v="fig/AiCity-939-大亮時代A7.jpeg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=125949"/>
@@ -27819,13 +28938,13 @@
     <n v="15"/>
     <s v="平面式49個"/>
     <s v="30元/坪/月"/>
-    <s v="1:0.36"/>
-    <n v="0.36"/>
+    <x v="21"/>
+    <x v="21"/>
     <s v="RC"/>
     <s v="332.5坪"/>
     <n v="332.5"/>
     <s v="住商用"/>
-    <s v="中心商業區"/>
+    <x v="3"/>
     <m/>
     <m/>
     <s v="110桃市都建執照字第00147號"/>
@@ -27836,7 +28955,7 @@
   <r>
     <s v="501"/>
     <s v="5.合宜住宅區"/>
-    <s v="新未來1"/>
+    <x v="40"/>
     <s v="501 新未來1"/>
     <s v="fig/AiCity-939-新未來1.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=113056"/>
@@ -27877,13 +28996,13 @@
     <n v="28"/>
     <s v="平面式648個、機械式84個"/>
     <s v="60元/坪/月"/>
-    <s v="1:0.89"/>
-    <n v="0.89"/>
+    <x v="22"/>
+    <x v="22"/>
     <s v="RC"/>
     <s v="2890坪"/>
     <n v="2890"/>
     <s v="住商用"/>
-    <s v="中心商業區"/>
+    <x v="3"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(106)桃市都建執照字第會龜00035號"/>
@@ -27894,7 +29013,7 @@
   <r>
     <s v="502"/>
     <s v="5.合宜住宅區"/>
-    <s v="富宇天匯"/>
+    <x v="41"/>
     <s v="502 富宇天匯"/>
     <s v="fig/AiCity-939-富宇天匯.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=121159&amp;v=720"/>
@@ -27935,13 +29054,13 @@
     <n v="15"/>
     <s v="平面式260個、機械式18個"/>
     <s v="70元/坪/月"/>
-    <s v="1:1.03"/>
-    <n v="1.03"/>
+    <x v="1"/>
+    <x v="1"/>
     <s v="RC"/>
     <s v="1471.38坪"/>
     <n v="1471.38"/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第01027號"/>
@@ -27952,7 +29071,7 @@
   <r>
     <s v="503"/>
     <s v="5.合宜住宅區"/>
-    <s v="竹城明治"/>
+    <x v="42"/>
     <s v="503 竹城明治"/>
     <s v="fig/AiCity-939-竹城明治.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=120762"/>
@@ -27993,13 +29112,13 @@
     <n v="13"/>
     <s v="平面式81個、機械式68個"/>
     <s v="待定"/>
-    <s v="1:0.86"/>
-    <n v="0.86"/>
+    <x v="14"/>
+    <x v="14"/>
     <s v="RC"/>
     <s v="961.25坪"/>
     <n v="961.25"/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <s v="暫無"/>
     <s v="暫無"/>
     <s v="(107)桃市都建執照字第會龜00995-01號等1個"/>
@@ -28010,7 +29129,7 @@
   <r>
     <s v="504"/>
     <s v="5.合宜住宅區"/>
-    <s v="竹城宇治"/>
+    <x v="43"/>
     <s v="504 竹城宇治"/>
     <s v="fig/AiCity-939-竹城宇治.jpg"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=115863"/>
@@ -28051,13 +29170,13 @@
     <n v="13"/>
     <s v="平面式82個"/>
     <s v="80元/坪/月"/>
-    <s v="1:0.75"/>
-    <n v="0.75"/>
+    <x v="23"/>
+    <x v="23"/>
     <s v="RC"/>
     <s v="638.13坪"/>
     <n v="638.13"/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <m/>
     <m/>
     <s v="(106)桃市都建執照字第會龜01145 號等2個"/>
@@ -28068,7 +29187,7 @@
   <r>
     <s v="505"/>
     <s v="5.合宜住宅區"/>
-    <s v="櫻花澍"/>
+    <x v="44"/>
     <s v="505 櫻花澍"/>
     <s v="fig/AiCity-939-櫻花澍.webp"/>
     <s v="https://newhouse.591.com.tw/home/housing/detail?hid=124447"/>
@@ -28109,13 +29228,13 @@
     <n v="14"/>
     <s v="平面式108個"/>
     <s v="65元/坪/月"/>
-    <s v="1:1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="RC"/>
     <s v="602.07坪"/>
     <n v="602.07000000000005"/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <m/>
     <s v="暫無"/>
     <s v="108桃市都建執照字第00713-01號"/>
@@ -28126,7 +29245,7 @@
   <r>
     <s v="506"/>
     <s v="5.合宜住宅區"/>
-    <s v="遠雄文青"/>
+    <x v="45"/>
     <s v="506 遠雄文青"/>
     <s v="fig/AiCity-939-遠雄文青.jpg"/>
     <s v="https://www.farglory-land.com.tw/leasehold/%E9%81%A0%E9%9B%84%E6%99%82%E4%BB%A3%E7%B8%BD%E9%83%A8-2/"/>
@@ -28167,13 +29286,13 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <x v="24"/>
+    <x v="24"/>
     <s v="RC"/>
     <m/>
     <m/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <m/>
     <m/>
     <m/>
@@ -28184,7 +29303,7 @@
   <r>
     <s v="507"/>
     <s v="5.合宜住宅區"/>
-    <s v="皇翔歡喜城"/>
+    <x v="46"/>
     <s v="507 皇翔歡喜城"/>
     <s v="fig/AiCity-939-皇翔歡喜城.jpg"/>
     <s v="https://www.uppercity.tw/"/>
@@ -28225,13 +29344,13 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <x v="24"/>
+    <x v="24"/>
     <s v="RC"/>
     <m/>
     <m/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <m/>
     <m/>
     <m/>
@@ -28242,7 +29361,7 @@
   <r>
     <s v="508"/>
     <s v="5.合宜住宅區"/>
-    <s v="名軒快樂家"/>
+    <x v="47"/>
     <s v="508 名軒快樂家"/>
     <s v="fig/AiCity-939-名軒快樂家.jpg"/>
     <s v="https://www.advancetek.com.tw/%E7%86%B1%E9%8A%B7%E5%80%8B%E6%A1%88/%E5%90%8D%E8%BB%92%E5%BF%AB%E6%A8%82%E5%AE%B6%E5%90%88%E5%AE%9C%E4%BD%8F%E5%AE%85a7_c%E5%9F%BA%E5%9C%B0/"/>
@@ -28283,13 +29402,13 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <x v="24"/>
+    <x v="24"/>
     <s v="RC"/>
     <m/>
     <m/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <m/>
     <m/>
     <m/>
@@ -28300,7 +29419,7 @@
   <r>
     <s v="509"/>
     <s v="5.合宜住宅區"/>
-    <s v="麗寶快樂家"/>
+    <x v="48"/>
     <s v="509 麗寶快樂家"/>
     <s v="fig/AiCity-939-麗寶快樂家.jpg"/>
     <s v="http://lihpao.com.tw/appropriate/build.html"/>
@@ -28341,13 +29460,13 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <x v="24"/>
+    <x v="24"/>
     <s v="RC"/>
     <m/>
     <m/>
     <s v="住商用"/>
-    <s v="第三種住宅區"/>
+    <x v="4"/>
     <m/>
     <m/>
     <m/>
@@ -28359,7 +29478,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A3CA2B-B6E6-A64B-BB28-39916B3C266F}" name="樞紐分析表1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A3CA2B-B6E6-A64B-BB28-39916B3C266F}" name="樞紐分析表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:C49" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -28732,7 +29851,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F52A0184-F9FB-7249-BCA8-2F8B6C3580F3}" name="樞紐分析表1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F52A0184-F9FB-7249-BCA8-2F8B6C3580F3}" name="樞紐分析表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -29345,154 +30464,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7019A1B8-C948-9248-8ABA-BFD05B6AA01A}" name="樞紐分析表1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="55">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField axis="axisPage" dataField="1" numFmtId="177" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="20">
-        <item h="1" x="18"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="17"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="12"/>
-        <item x="5"/>
-        <item x="15"/>
-        <item x="13"/>
-        <item x="9"/>
-        <item x="16"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="49"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="9" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="181"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A05ECE1-698D-3F42-A1F5-015F41A70879}" name="樞紐分析表2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A05ECE1-698D-3F42-A1F5-015F41A70879}" name="樞紐分析表2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A37:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -29674,8 +30646,155 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7019A1B8-C948-9248-8ABA-BFD05B6AA01A}" name="樞紐分析表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="55">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" numFmtId="177" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="20">
+        <item h="1" x="18"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="49"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="9" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="181"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{458FE396-6E8A-064D-96E2-0847BBE52133}" name="樞紐分析表7" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="3ㄒㄧ1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{458FE396-6E8A-064D-96E2-0847BBE52133}" name="樞紐分析表7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="3ㄒㄧ1">
   <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="56">
     <pivotField dataField="1" showAll="0"/>
@@ -29794,8 +30913,244 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B833B209-0CFF-0548-B5A9-F2903FE4CB01}" name="樞紐分析表1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="56">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="50">
+        <item h="1" x="39"/>
+        <item x="14"/>
+        <item x="22"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="38"/>
+        <item x="47"/>
+        <item x="25"/>
+        <item x="43"/>
+        <item x="42"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="46"/>
+        <item x="18"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="31"/>
+        <item x="20"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="19"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="40"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="45"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="37"/>
+        <item x="32"/>
+        <item x="1"/>
+        <item x="27"/>
+        <item x="48"/>
+        <item x="9"/>
+        <item x="44"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="26">
+        <item x="21"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="14"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="22"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="17"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="16"/>
+        <item x="20"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="24"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="26">
+        <item x="21"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="14"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="22"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="17"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="16"/>
+        <item x="20"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="24"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="49"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - 車位分配率" fld="44" subtotal="average" baseField="0" baseItem="0" numFmtId="178"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D90A3B06-44FC-DF47-95B9-374674E5983F}" name="樞紐分析表2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D90A3B06-44FC-DF47-95B9-374674E5983F}" name="樞紐分析表2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:C49" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -30154,7 +31509,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C48516-4469-E144-BC4C-C411D0731588}" name="樞紐分析表4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C48516-4469-E144-BC4C-C411D0731588}" name="樞紐分析表4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:C49" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -30492,7 +31847,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E3E605F-0935-CE47-93A7-EE637CD6D22D}" name="樞紐分析表3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E3E605F-0935-CE47-93A7-EE637CD6D22D}" name="樞紐分析表3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B60" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -30851,7 +32206,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCF300E8-2DA3-FD4D-8DB5-C4AF4C0B2B4D}" name="樞紐分析表5" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCF300E8-2DA3-FD4D-8DB5-C4AF4C0B2B4D}" name="樞紐分析表5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -31260,7 +32615,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{537918C9-6258-454A-9359-2B209B13DC90}" name="樞紐分析表6" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{537918C9-6258-454A-9359-2B209B13DC90}" name="樞紐分析表6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -31600,7 +32955,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A78E8CA-AA2E-4542-B594-47B469B1ECF7}" name="樞紐分析表7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A78E8CA-AA2E-4542-B594-47B469B1ECF7}" name="樞紐分析表7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -31912,7 +33267,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4AA391D-DCC2-A047-A23D-C8888E109D7F}" name="樞紐分析表8" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4AA391D-DCC2-A047-A23D-C8888E109D7F}" name="樞紐分析表8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -32227,7 +33582,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E436F8BC-6E9C-CD4C-8D5F-9F959847D2E8}" name="樞紐分析表9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E436F8BC-6E9C-CD4C-8D5F-9F959847D2E8}" name="樞紐分析表9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="55">
     <pivotField showAll="0"/>
@@ -33860,6 +35215,87 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3414B7A9-90AD-6946-BC2E-E7215B1E7E4A}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="16" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="24">
+        <v>0.94555555555555548</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="24">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="B6" s="24">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="B7" s="24">
+        <v>0.98066666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="24">
+        <v>1.0011111111111111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="17" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B9" s="24">
+        <v>0.98159090909090907</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89EF37-C3F3-8243-B091-96A26EC57E26}">
   <dimension ref="A1:BD113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>

--- a/db/A7XLK-1102-HouseBigData.xlsx
+++ b/db/A7XLK-1102-HouseBigData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5CF497-4A5B-9446-A0EB-676344585C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1519AA-346A-3944-88C0-99D376B80291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="500" windowWidth="34180" windowHeight="22540" activeTab="14" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
   </bookViews>
@@ -36,8 +36,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="23" r:id="rId16"/>
-    <pivotCache cacheId="20" r:id="rId17"/>
+    <pivotCache cacheId="28" r:id="rId16"/>
+    <pivotCache cacheId="25" r:id="rId17"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="1159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2548" uniqueCount="1159">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4552,22 +4552,7 @@
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="8" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="0_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="0_ "/>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
     </dxf>
@@ -7809,6 +7794,757 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[A7XLK-1102-HouseBigData.xlsx]Figure-12!樞紐分析表2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="2800" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>A7 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2800" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>建商建案總戶數</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-12'!$C$48</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>加總 - 住家戶數</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FF0000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Figure-12'!$B$49:$B$64</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>寶佳集團</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>富宇建設</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>遠雄建設</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>竹城建設</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>禾聯建築</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>興富發建設</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>新潤建設</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>允將建設</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>頤昌建設</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>詠勝開發</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>君悅建設</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>玄泰建設</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>櫻花建設</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>合謙建設</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>大亮建築</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-12'!$C$49:$C$64</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_ </c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2286</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1765</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1415</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1044</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>776</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>686</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>278</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>87</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FFEF-104E-9D6D-EA44BCBE245D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-12'!$D$48</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>加總 - 商店戶數</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Figure-12'!$B$49:$B$64</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>寶佳集團</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>富宇建設</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>遠雄建設</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>竹城建設</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>禾聯建築</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>興富發建設</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>新潤建設</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>允將建設</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>頤昌建設</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>詠勝開發</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>君悅建設</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>玄泰建設</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>櫻花建設</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>合謙建設</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>大亮建築</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-12'!$D$49:$D$64</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_ </c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FFEF-104E-9D6D-EA44BCBE245D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="95"/>
+        <c:overlap val="100"/>
+        <c:axId val="728079440"/>
+        <c:axId val="728301072"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="728079440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="728301072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="728301072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-TW" altLang="en-US" sz="1400" baseline="0">
+                    <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  </a:rPr>
+                  <a:t>戶數</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0_ " sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="728079440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -16466,6 +17202,46 @@
 </file>
 
 <file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -19288,6 +20064,511 @@
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -23674,6 +24955,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13AAE213-4B38-D345-A185-D3E1FDBEC4DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -24465,10 +25782,76 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="住家戶數" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="87" maxValue="1780"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="87" maxValue="1780" count="45">
+        <n v="280"/>
+        <n v="196"/>
+        <n v="326"/>
+        <n v="173"/>
+        <n v="187"/>
+        <n v="186"/>
+        <n v="198"/>
+        <n v="832"/>
+        <n v="1044"/>
+        <n v="199"/>
+        <n v="308"/>
+        <n v="441"/>
+        <n v="138"/>
+        <n v="530"/>
+        <n v="235"/>
+        <n v="420"/>
+        <n v="266"/>
+        <n v="225"/>
+        <n v="776"/>
+        <n v="264"/>
+        <n v="112"/>
+        <n v="305"/>
+        <n v="204"/>
+        <n v="478"/>
+        <n v="1144"/>
+        <n v="754"/>
+        <n v="771"/>
+        <n v="257"/>
+        <n v="371"/>
+        <n v="337"/>
+        <n v="483"/>
+        <n v="154"/>
+        <n v="376"/>
+        <n v="582"/>
+        <n v="210"/>
+        <n v="124"/>
+        <n v="106"/>
+        <n v="87"/>
+        <n v="807"/>
+        <n v="168"/>
+        <n v="103"/>
+        <n v="1272"/>
+        <n v="1780"/>
+        <n v="514"/>
+        <n v="897"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="商店戶數" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="31"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="31" count="19">
+        <n v="12"/>
+        <n v="11"/>
+        <n v="20"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="0"/>
+        <n v="2"/>
+        <n v="13"/>
+        <n v="5"/>
+        <n v="4"/>
+        <n v="3"/>
+        <n v="30"/>
+        <n v="23"/>
+        <n v="31"/>
+        <n v="9"/>
+        <n v="16"/>
+        <n v="14"/>
+        <n v="6"/>
+        <m/>
+      </sharedItems>
     </cacheField>
     <cacheField name="建蔽率" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="0.3347" maxValue="0.59850000000000003"/>
@@ -25043,8 +26426,8 @@
     <n v="0.33"/>
     <n v="0.33"/>
     <s v="3幢，8棟，280戶住家，12戶店面"/>
-    <n v="280"/>
-    <n v="12"/>
+    <x v="0"/>
+    <x v="0"/>
     <n v="0.40899999999999997"/>
     <n v="0.40899999999999997"/>
     <s v="地上15層，地下4層"/>
@@ -25102,8 +26485,8 @@
     <s v="32%"/>
     <n v="0.32"/>
     <s v="1幢，2棟，196戶住家，11戶店面"/>
-    <n v="196"/>
-    <n v="11"/>
+    <x v="1"/>
+    <x v="1"/>
     <s v="39.8%"/>
     <n v="0.39800000000000002"/>
     <s v="地上15層，地下3層"/>
@@ -25161,8 +26544,8 @@
     <s v="31.5%"/>
     <n v="0.315"/>
     <s v="1幢，8棟，326戶住家，20戶店面"/>
-    <n v="326"/>
-    <n v="20"/>
+    <x v="2"/>
+    <x v="2"/>
     <s v="49.56%"/>
     <n v="0.49559999999999998"/>
     <s v="地上15層，地下3層"/>
@@ -25220,8 +26603,8 @@
     <s v="32%"/>
     <n v="0.32"/>
     <s v="1幢，3棟，173戶住家，11戶店面"/>
-    <n v="173"/>
-    <n v="11"/>
+    <x v="3"/>
+    <x v="1"/>
     <s v="48.26%"/>
     <n v="0.48259999999999997"/>
     <s v="地上13,14層，地下4層"/>
@@ -25279,8 +26662,8 @@
     <n v="0.32600000000000001"/>
     <n v="0.32600000000000001"/>
     <s v="2幢，4棟，187戶住家，12戶店面"/>
-    <n v="187"/>
-    <n v="12"/>
+    <x v="4"/>
+    <x v="0"/>
     <n v="0.44269999999999998"/>
     <n v="0.44269999999999998"/>
     <s v="地上13、14層，地下4層"/>
@@ -25338,8 +26721,8 @@
     <s v="31~32%"/>
     <n v="0.315"/>
     <s v="5棟，186戶住家，7戶店面"/>
-    <n v="186"/>
-    <n v="7"/>
+    <x v="5"/>
+    <x v="3"/>
     <s v="44.23%"/>
     <n v="0.44230000000000003"/>
     <s v="地上15層，地下3層"/>
@@ -25397,8 +26780,8 @@
     <s v="31~32%"/>
     <n v="0.315"/>
     <s v="4棟，198戶住家，8戶店面"/>
-    <n v="198"/>
-    <n v="8"/>
+    <x v="6"/>
+    <x v="4"/>
     <s v="45.67%"/>
     <n v="0.45669999999999999"/>
     <s v="地上15層，地下4層"/>
@@ -25456,8 +26839,8 @@
     <s v="33.5%"/>
     <n v="0.33500000000000002"/>
     <s v="4幢，6棟，832戶住家"/>
-    <n v="832"/>
-    <n v="0"/>
+    <x v="7"/>
+    <x v="5"/>
     <s v="31.07%"/>
     <n v="0.31069999999999998"/>
     <s v="地上24層，地下4層"/>
@@ -25515,8 +26898,8 @@
     <s v="33.5%"/>
     <n v="0.33500000000000002"/>
     <s v="1幢，13棟，1044戶住家"/>
-    <n v="1044"/>
-    <n v="0"/>
+    <x v="8"/>
+    <x v="5"/>
     <s v="52.94%"/>
     <n v="0.52939999999999998"/>
     <s v="地上14~15層，地下4層"/>
@@ -25574,8 +26957,8 @@
     <s v="31.5%"/>
     <n v="0.315"/>
     <s v="5棟，199戶住家，2戶店面"/>
-    <n v="199"/>
-    <n v="2"/>
+    <x v="9"/>
+    <x v="6"/>
     <s v="46.14%"/>
     <n v="0.46139999999999998"/>
     <s v="地上15層，地下4層"/>
@@ -25633,8 +27016,8 @@
     <n v="0.31859999999999999"/>
     <n v="0.31859999999999999"/>
     <s v="6棟，308戶住家，13戶店面"/>
-    <n v="308"/>
-    <n v="13"/>
+    <x v="10"/>
+    <x v="7"/>
     <n v="0.47989999999999999"/>
     <n v="0.47989999999999999"/>
     <s v="地上15層，地下4層"/>
@@ -25692,8 +27075,8 @@
     <s v="33.35%"/>
     <n v="0.33350000000000002"/>
     <s v="8棟，441戶住家，7戶店面"/>
-    <n v="441"/>
-    <n v="7"/>
+    <x v="11"/>
+    <x v="3"/>
     <s v="43.92%"/>
     <n v="0.43919999999999998"/>
     <s v="地上15層，地下3層"/>
@@ -25751,8 +27134,8 @@
     <s v="31.9%"/>
     <n v="0.31900000000000001"/>
     <s v="2棟，138戶住家，8戶店面，125戶一般事務所"/>
-    <n v="138"/>
-    <n v="8"/>
+    <x v="12"/>
+    <x v="4"/>
     <s v="60.16%"/>
     <n v="0.60160000000000002"/>
     <s v="地上24層，地下5層"/>
@@ -25810,8 +27193,8 @@
     <s v="32~32.5%"/>
     <n v="0.32250000000000001"/>
     <s v="1幢，7棟，280戶住家，11戶店面"/>
-    <n v="280"/>
-    <n v="11"/>
+    <x v="0"/>
+    <x v="1"/>
     <n v="0.4743"/>
     <n v="0.4743"/>
     <s v="地上15層，地下4層"/>
@@ -25869,8 +27252,8 @@
     <n v="0.33800000000000002"/>
     <n v="0.33800000000000002"/>
     <s v="1幢，7棟，530戶住家，5戶店面，20戶事務所，1戶管委會空間"/>
-    <n v="530"/>
-    <n v="5"/>
+    <x v="13"/>
+    <x v="8"/>
     <n v="0.45529999999999998"/>
     <n v="0.45529999999999998"/>
     <s v="地上31層，地下6層"/>
@@ -25928,8 +27311,8 @@
     <s v="33.5%"/>
     <n v="0.33500000000000002"/>
     <s v="5棟，235戶住家，4戶店面，19戶一般事務所"/>
-    <n v="235"/>
-    <n v="4"/>
+    <x v="14"/>
+    <x v="9"/>
     <s v="57.49%"/>
     <n v="0.57489999999999997"/>
     <s v="地上30層，地下6層"/>
@@ -25987,8 +27370,8 @@
     <s v="33.5~34.5%"/>
     <n v="0.33750000000000002"/>
     <s v="1幢，2棟，420戶住家，20戶店面，11戶一般事務所"/>
-    <n v="420"/>
-    <n v="20"/>
+    <x v="15"/>
+    <x v="2"/>
     <s v="65.02%"/>
     <n v="0.6502"/>
     <s v="地上24層，地下5層"/>
@@ -26046,8 +27429,8 @@
     <n v="0.33500000000000002"/>
     <n v="0.33500000000000002"/>
     <s v="2幢，3棟，266戶住家，13戶店面"/>
-    <n v="266"/>
-    <n v="13"/>
+    <x v="16"/>
+    <x v="7"/>
     <n v="0.59850000000000003"/>
     <n v="0.59850000000000003"/>
     <s v="地上15層，地下4層"/>
@@ -26105,8 +27488,8 @@
     <s v="32%"/>
     <n v="0.32"/>
     <s v="4棟，225戶住家，3戶店面"/>
-    <n v="225"/>
-    <n v="3"/>
+    <x v="17"/>
+    <x v="10"/>
     <s v="50.54%"/>
     <n v="0.50539999999999996"/>
     <s v="地上15層，地下4層"/>
@@ -26164,8 +27547,8 @@
     <n v="0.34"/>
     <n v="0.34"/>
     <s v="3棟，776戶住家，8戶店面"/>
-    <n v="776"/>
-    <n v="8"/>
+    <x v="18"/>
+    <x v="4"/>
     <n v="0.44359999999999999"/>
     <n v="0.44359999999999999"/>
     <s v="地上18層，地下4層"/>
@@ -26223,8 +27606,8 @@
     <s v="33.5~40%"/>
     <n v="0.36799999999999999"/>
     <s v="5棟，264戶住家"/>
-    <n v="264"/>
-    <n v="0"/>
+    <x v="19"/>
+    <x v="5"/>
     <s v="40.21%"/>
     <n v="0.40210000000000001"/>
     <s v="地上14層，地下4層"/>
@@ -26282,8 +27665,8 @@
     <s v="31~32%"/>
     <n v="0.315"/>
     <s v="2棟，112戶住家，4戶店面"/>
-    <n v="112"/>
-    <n v="4"/>
+    <x v="20"/>
+    <x v="9"/>
     <s v="33.97%"/>
     <n v="0.3397"/>
     <s v="地上15層，地下4層"/>
@@ -26341,8 +27724,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="3幢，7棟，305戶住家"/>
-    <n v="305"/>
-    <n v="0"/>
+    <x v="21"/>
+    <x v="5"/>
     <n v="0.44209999999999999"/>
     <n v="0.44209999999999999"/>
     <s v="地上15層，地下4層"/>
@@ -26400,8 +27783,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="1幢，3棟，204戶住家，7戶店面"/>
-    <n v="204"/>
-    <n v="7"/>
+    <x v="22"/>
+    <x v="3"/>
     <n v="0.55610000000000004"/>
     <n v="0.55610000000000004"/>
     <s v="地上13、14層，地下5層"/>
@@ -26459,8 +27842,8 @@
     <n v="0.32500000000000001"/>
     <n v="0.33"/>
     <s v="1幢，2棟，478戶住家，8戶店面"/>
-    <n v="478"/>
-    <n v="8"/>
+    <x v="23"/>
+    <x v="4"/>
     <n v="0.3347"/>
     <n v="0.3347"/>
     <s v="地上22層，地下4層"/>
@@ -26518,8 +27901,8 @@
     <s v="32.5%"/>
     <n v="0.32500000000000001"/>
     <s v="8棟，1144戶住家，30戶店面，33戶一般事務所，2戶商場"/>
-    <n v="1144"/>
-    <n v="30"/>
+    <x v="24"/>
+    <x v="11"/>
     <s v="50.21%"/>
     <n v="0.50209999999999999"/>
     <s v="地上24層，地下4層"/>
@@ -26577,8 +27960,8 @@
     <s v="31.9%"/>
     <n v="0.31900000000000001"/>
     <s v="4幢，754戶住家，23戶店面, 1商場"/>
-    <n v="754"/>
-    <n v="23"/>
+    <x v="25"/>
+    <x v="12"/>
     <s v="50.74%"/>
     <n v="0.50739999999999996"/>
     <s v="地上28層，地下6層"/>
@@ -26636,8 +28019,8 @@
     <s v="32%"/>
     <n v="0.32"/>
     <s v="1幢，4棟，771戶住家，31戶店面，1戶商場"/>
-    <n v="771"/>
-    <n v="31"/>
+    <x v="26"/>
+    <x v="13"/>
     <s v="49.53%"/>
     <n v="0.49530000000000002"/>
     <s v="地上29層，地下5層"/>
@@ -26695,8 +28078,8 @@
     <s v="33%"/>
     <n v="0.33"/>
     <s v="1棟，257戶住家，7戶店面，32戶一般事務所"/>
-    <n v="257"/>
-    <n v="7"/>
+    <x v="27"/>
+    <x v="3"/>
     <s v="53.26%"/>
     <n v="0.53259999999999996"/>
     <s v="地上22層，地下5層"/>
@@ -26754,8 +28137,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="4幢，7棟，371戶住家，3戶店面"/>
-    <n v="371"/>
-    <n v="3"/>
+    <x v="28"/>
+    <x v="10"/>
     <n v="0.46450000000000002"/>
     <n v="0.46450000000000002"/>
     <s v="地上15層，地下4層"/>
@@ -26813,8 +28196,8 @@
     <s v="31.5%"/>
     <n v="0.315"/>
     <s v="5棟，337戶住家，2戶店面"/>
-    <n v="337"/>
-    <n v="2"/>
+    <x v="29"/>
+    <x v="6"/>
     <s v="47.5%"/>
     <n v="0.47499999999999998"/>
     <s v="地上14~15層，地下4層"/>
@@ -26872,8 +28255,8 @@
     <s v="33.5%"/>
     <n v="0.33500000000000002"/>
     <s v="1幢，3棟，483戶住家，8戶店面"/>
-    <n v="483"/>
-    <n v="8"/>
+    <x v="30"/>
+    <x v="4"/>
     <s v="44.18%"/>
     <n v="0.44180000000000003"/>
     <s v="地上24層，地下4層"/>
@@ -26931,8 +28314,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="2棟，154戶住家，9戶店面"/>
-    <n v="154"/>
-    <n v="9"/>
+    <x v="31"/>
+    <x v="14"/>
     <n v="0.4622"/>
     <n v="0.4622"/>
     <s v="地上15層，地下4層"/>
@@ -26990,8 +28373,8 @@
     <n v="0.33"/>
     <n v="0.33"/>
     <s v="2棟，376戶住家，9戶店面"/>
-    <n v="376"/>
-    <n v="9"/>
+    <x v="32"/>
+    <x v="14"/>
     <n v="0.36220000000000002"/>
     <n v="0.36220000000000002"/>
     <s v="地上22層，地下4層"/>
@@ -27049,8 +28432,8 @@
     <n v="0.3327"/>
     <n v="0.3327"/>
     <s v="2幢，3棟，582戶住家，16戶店面"/>
-    <n v="582"/>
-    <n v="16"/>
+    <x v="33"/>
+    <x v="15"/>
     <n v="0.38300000000000001"/>
     <n v="0.38300000000000001"/>
     <s v="地上19、22層，地下5層"/>
@@ -27108,8 +28491,8 @@
     <s v="32%"/>
     <n v="0.32"/>
     <s v="3幢，3棟，210戶住家，11戶店面"/>
-    <n v="210"/>
-    <n v="11"/>
+    <x v="34"/>
+    <x v="1"/>
     <s v="45.54%"/>
     <n v="0.45540000000000003"/>
     <s v="地上15層，地下3~4層"/>
@@ -27167,8 +28550,8 @@
     <s v="32.46~33.79%"/>
     <n v="0.33129999999999998"/>
     <s v="1幢，4棟，173戶住家，5戶店面"/>
-    <n v="173"/>
-    <n v="5"/>
+    <x v="3"/>
+    <x v="8"/>
     <n v="0.46150000000000002"/>
     <n v="0.46150000000000002"/>
     <s v="地上15層，地下4層"/>
@@ -27226,8 +28609,8 @@
     <n v="0.32100000000000001"/>
     <n v="0.32100000000000001"/>
     <s v="1幢，2棟，124戶住家，11戶店面"/>
-    <n v="124"/>
-    <n v="11"/>
+    <x v="35"/>
+    <x v="1"/>
     <n v="0.51349999999999996"/>
     <n v="0.51349999999999996"/>
     <s v="地上14層，地下4層"/>
@@ -27285,8 +28668,8 @@
     <n v="0.32500000000000001"/>
     <n v="0.32500000000000001"/>
     <s v="1幢，2棟，106戶住家"/>
-    <n v="106"/>
-    <n v="0"/>
+    <x v="36"/>
+    <x v="5"/>
     <n v="0.45660000000000001"/>
     <n v="0.45660000000000001"/>
     <s v="地上14層，地下4層"/>
@@ -27344,8 +28727,8 @@
     <n v="0.33900000000000002"/>
     <n v="0.33900000000000002"/>
     <s v="1幢，1棟，87戶一般事務所，3戶店面，45戶住家"/>
-    <n v="87"/>
-    <n v="3"/>
+    <x v="37"/>
+    <x v="10"/>
     <n v="0.50270000000000004"/>
     <n v="0.50270000000000004"/>
     <s v="地上15層，地下4層"/>
@@ -27403,8 +28786,8 @@
     <n v="0.33"/>
     <n v="0.33"/>
     <s v="3棟，807戶住家，14戶店面，3個商場"/>
-    <n v="807"/>
-    <n v="14"/>
+    <x v="38"/>
+    <x v="16"/>
     <n v="0.57020000000000004"/>
     <n v="0.57020000000000004"/>
     <s v="地上28層，地下5層"/>
@@ -27462,8 +28845,8 @@
     <n v="0.33500000000000002"/>
     <n v="0.33500000000000002"/>
     <s v="2幢，4棟，266戶住家，4戶店面"/>
-    <n v="266"/>
-    <n v="4"/>
+    <x v="16"/>
+    <x v="9"/>
     <n v="0.49540000000000001"/>
     <n v="0.49540000000000001"/>
     <s v="地上15層，地下4層"/>
@@ -27521,8 +28904,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="1幢，6棟，168戶住家，5戶店面"/>
-    <n v="168"/>
-    <n v="5"/>
+    <x v="39"/>
+    <x v="8"/>
     <s v="45.56%"/>
     <n v="0.4556"/>
     <s v="地上13層，地下3層"/>
@@ -27580,8 +28963,8 @@
     <n v="0.315"/>
     <n v="0.315"/>
     <s v="3棟，103戶住家，6戶店面"/>
-    <n v="103"/>
-    <n v="6"/>
+    <x v="40"/>
+    <x v="17"/>
     <n v="0.45700000000000002"/>
     <n v="0.45700000000000002"/>
     <s v="地上13層，地下3層"/>
@@ -27639,8 +29022,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="1幢，2棟，106戶住家，2戶店面"/>
-    <n v="106"/>
-    <n v="2"/>
+    <x v="36"/>
+    <x v="6"/>
     <n v="0.38140000000000002"/>
     <n v="0.38140000000000002"/>
     <s v="地上14層，地下4層"/>
@@ -27698,8 +29081,8 @@
     <m/>
     <m/>
     <m/>
-    <n v="1272"/>
-    <m/>
+    <x v="41"/>
+    <x v="18"/>
     <m/>
     <m/>
     <m/>
@@ -27757,8 +29140,8 @@
     <m/>
     <m/>
     <m/>
-    <n v="1780"/>
-    <m/>
+    <x v="42"/>
+    <x v="18"/>
     <m/>
     <m/>
     <m/>
@@ -27816,8 +29199,8 @@
     <m/>
     <m/>
     <m/>
-    <n v="514"/>
-    <m/>
+    <x v="43"/>
+    <x v="18"/>
     <m/>
     <m/>
     <m/>
@@ -27875,8 +29258,8 @@
     <m/>
     <m/>
     <m/>
-    <n v="897"/>
-    <m/>
+    <x v="44"/>
+    <x v="18"/>
     <m/>
     <m/>
     <m/>
@@ -30748,7 +32131,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A3CA2B-B6E6-A64B-BB28-39916B3C266F}" name="樞紐分析表1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A3CA2B-B6E6-A64B-BB28-39916B3C266F}" name="樞紐分析表1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:C53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -31137,7 +32520,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F52A0184-F9FB-7249-BCA8-2F8B6C3580F3}" name="樞紐分析表1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F52A0184-F9FB-7249-BCA8-2F8B6C3580F3}" name="樞紐分析表1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -31751,7 +33134,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A05ECE1-698D-3F42-A1F5-015F41A70879}" name="樞紐分析表2" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A05ECE1-698D-3F42-A1F5-015F41A70879}" name="樞紐分析表2" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A37:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -31935,7 +33318,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7019A1B8-C948-9248-8ABA-BFD05B6AA01A}" name="樞紐分析表1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7019A1B8-C948-9248-8ABA-BFD05B6AA01A}" name="樞紐分析表1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -32083,7 +33466,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{458FE396-6E8A-064D-96E2-0847BBE52133}" name="樞紐分析表7" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="3ㄒㄧ1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{458FE396-6E8A-064D-96E2-0847BBE52133}" name="樞紐分析表7" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="3ㄒㄧ1">
   <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="57">
     <pivotField dataField="1" showAll="0"/>
@@ -32204,7 +33587,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B833B209-0CFF-0548-B5A9-F2903FE4CB01}" name="樞紐分析表1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B833B209-0CFF-0548-B5A9-F2903FE4CB01}" name="樞紐分析表1" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="57">
     <pivotField showAll="0"/>
@@ -32383,7 +33766,335 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34FE811F-B077-FD42-9008-279DB01289D2}" name="樞紐分析表1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4D14CAE-2C58-9D43-B1F7-B8BBC66C68B5}" name="樞紐分析表2" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="B48:D64" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="57">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField axis="axisPage" numFmtId="177" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="20">
+        <item h="1" x="18"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="20">
+        <item x="14"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="17"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item h="1" x="5"/>
+        <item x="16"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="46">
+        <item x="37"/>
+        <item x="40"/>
+        <item x="36"/>
+        <item x="20"/>
+        <item x="35"/>
+        <item x="12"/>
+        <item x="31"/>
+        <item x="39"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="22"/>
+        <item x="34"/>
+        <item x="17"/>
+        <item x="14"/>
+        <item x="27"/>
+        <item x="19"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item x="21"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="32"/>
+        <item x="15"/>
+        <item x="11"/>
+        <item x="23"/>
+        <item x="30"/>
+        <item x="43"/>
+        <item x="13"/>
+        <item x="33"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="18"/>
+        <item x="38"/>
+        <item x="7"/>
+        <item x="44"/>
+        <item x="8"/>
+        <item x="24"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="20">
+        <item x="5"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="17"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="16"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="29"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="9" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="加總 - 住家戶數" fld="36" baseField="0" baseItem="0" numFmtId="180"/>
+    <dataField name="加總 - 商店戶數" fld="37" baseField="0" baseItem="0" numFmtId="180"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34FE811F-B077-FD42-9008-279DB01289D2}" name="樞紐分析表1" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="57">
     <pivotField showAll="0"/>
@@ -32628,7 +34339,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D90A3B06-44FC-DF47-95B9-374674E5983F}" name="樞紐分析表2" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D90A3B06-44FC-DF47-95B9-374674E5983F}" name="樞紐分析表2" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:C49" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -32933,10 +34644,10 @@
     <dataField name="平均值 - 每坪價-最高" fld="8" subtotal="average" baseField="0" baseItem="0" numFmtId="176"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="9">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="3">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -32945,7 +34656,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="2">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -32988,7 +34699,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C48516-4469-E144-BC4C-C411D0731588}" name="樞紐分析表4" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C48516-4469-E144-BC4C-C411D0731588}" name="樞紐分析表4" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:C49" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -33283,7 +34994,7 @@
     <dataField name="平均值 - 建蔽比率" fld="39" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="6">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2" selected="0">
@@ -33327,7 +35038,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E3E605F-0935-CE47-93A7-EE637CD6D22D}" name="樞紐分析表3" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E3E605F-0935-CE47-93A7-EE637CD6D22D}" name="樞紐分析表3" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B60" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -33687,7 +35398,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCF300E8-2DA3-FD4D-8DB5-C4AF4C0B2B4D}" name="樞紐分析表5" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCF300E8-2DA3-FD4D-8DB5-C4AF4C0B2B4D}" name="樞紐分析表5" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -34098,7 +35809,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{537918C9-6258-454A-9359-2B209B13DC90}" name="樞紐分析表6" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{537918C9-6258-454A-9359-2B209B13DC90}" name="樞紐分析表6" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -34411,7 +36122,7 @@
     <dataField name="加總 - 建築面積" fld="48" baseField="0" baseItem="0" numFmtId="179"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="5">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -34439,7 +36150,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A78E8CA-AA2E-4542-B594-47B469B1ECF7}" name="樞紐分析表7" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A78E8CA-AA2E-4542-B594-47B469B1ECF7}" name="樞紐分析表7" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -34752,7 +36463,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4AA391D-DCC2-A047-A23D-C8888E109D7F}" name="樞紐分析表8" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4AA391D-DCC2-A047-A23D-C8888E109D7F}" name="樞紐分析表8" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -35068,7 +36779,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E436F8BC-6E9C-CD4C-8D5F-9F959847D2E8}" name="樞紐分析表9" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E436F8BC-6E9C-CD4C-8D5F-9F959847D2E8}" name="樞紐分析表9" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -45044,11 +46755,11 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F3EDA-67FF-1141-88FB-67CF8719809C}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -45195,10 +46906,205 @@
         <v>29.815909090909091</v>
       </c>
     </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="16" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" s="16" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" s="17" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C49" s="25">
+        <v>6100</v>
+      </c>
+      <c r="D49" s="25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" s="25">
+        <v>2286</v>
+      </c>
+      <c r="D50" s="25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="17" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C51" s="25">
+        <v>1765</v>
+      </c>
+      <c r="D51" s="25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="C52" s="25">
+        <v>1415</v>
+      </c>
+      <c r="D52" s="25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="17" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C53" s="25">
+        <v>1044</v>
+      </c>
+      <c r="D53" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="17" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C54" s="25">
+        <v>776</v>
+      </c>
+      <c r="D54" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="C55" s="25">
+        <v>686</v>
+      </c>
+      <c r="D55" s="25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C56" s="25">
+        <v>530</v>
+      </c>
+      <c r="D56" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" s="17" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C57" s="25">
+        <v>278</v>
+      </c>
+      <c r="D57" s="25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="C58" s="25">
+        <v>257</v>
+      </c>
+      <c r="D58" s="25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" s="17" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C59" s="25">
+        <v>173</v>
+      </c>
+      <c r="D59" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="17" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C60" s="25">
+        <v>138</v>
+      </c>
+      <c r="D60" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="17" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C61" s="25">
+        <v>106</v>
+      </c>
+      <c r="D61" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" s="17" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C62" s="25">
+        <v>106</v>
+      </c>
+      <c r="D62" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" s="17" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C63" s="25">
+        <v>87</v>
+      </c>
+      <c r="D63" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="17" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C64" s="25">
+        <v>15747</v>
+      </c>
+      <c r="D64" s="25">
+        <v>389</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 

--- a/db/A7XLK-1102-HouseBigData.xlsx
+++ b/db/A7XLK-1102-HouseBigData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1519AA-346A-3944-88C0-99D376B80291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3108B735-695F-E14C-A873-C70930040D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="500" windowWidth="34180" windowHeight="22540" activeTab="14" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
   </bookViews>
@@ -36,8 +36,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="28" r:id="rId16"/>
-    <pivotCache cacheId="25" r:id="rId17"/>
+    <pivotCache cacheId="31" r:id="rId16"/>
+    <pivotCache cacheId="30" r:id="rId17"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2548" uniqueCount="1159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2584" uniqueCount="1171">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4387,6 +4387,42 @@
   </si>
   <si>
     <t>(全部)</t>
+  </si>
+  <si>
+    <t>建設公司</t>
+  </si>
+  <si>
+    <t>新A7</t>
+  </si>
+  <si>
+    <t>和耀恆美</t>
+  </si>
+  <si>
+    <t>耀台北</t>
+  </si>
+  <si>
+    <t>水悅青青</t>
+  </si>
+  <si>
+    <t>友文化</t>
+  </si>
+  <si>
+    <t>文華天際</t>
+  </si>
+  <si>
+    <t>玉子園</t>
+  </si>
+  <si>
+    <t>台北國際村</t>
+  </si>
+  <si>
+    <t>和發大境</t>
+  </si>
+  <si>
+    <t>皇普MVP</t>
+  </si>
+  <si>
+    <t>樂田田</t>
   </si>
 </sst>
 </file>
@@ -7956,6 +7992,47 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -8180,7 +8257,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -8545,6 +8676,571 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[A7XLK-1102-HouseBigData.xlsx]Figure-12!樞紐分析表3</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="2800" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>A7 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2800" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>寶佳集團建案比較</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="1800" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>(</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="1800" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>每坪單價）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-12'!$C$86</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>合計</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Figure-12'!$B$87:$B$118</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="20"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>新A7</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>鴻築捷市達</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>金捷市</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>鴻典</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>樂捷市</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>和耀恆美</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>耀台北</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>富御捷境</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>水悅青青</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>根津苑</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>友文化</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>文華天際</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>合遠新天地</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>玉子園</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>和發大境</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>台北國際村</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>和洲金剛</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>皇普MVP</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>樂田田</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>奇幻莊園</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>鴻廣建設</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>鴻築建設</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>和耀建設</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>和峻建設</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>鴻承建設</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>合遠建設</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>協勝建設</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>和發建設</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>和洲建設</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>皇普建設</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>佳晟建設</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-12'!$C$87:$C$118</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00_ </c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D62A-E54B-A9F6-759B35FEAEDC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
+        <c:axId val="1214159568"/>
+        <c:axId val="775473696"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1214159568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="775473696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="775473696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="#,##0.00_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1214159568"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -17242,6 +17938,46 @@
 </file>
 
 <file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -20569,6 +21305,509 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -24986,6 +26225,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>641350</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="圖表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C352F853-6070-714F-B57B-DE5132822D38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -32131,7 +33406,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A3CA2B-B6E6-A64B-BB28-39916B3C266F}" name="樞紐分析表1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A3CA2B-B6E6-A64B-BB28-39916B3C266F}" name="樞紐分析表1" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:C53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -32520,7 +33795,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F52A0184-F9FB-7249-BCA8-2F8B6C3580F3}" name="樞紐分析表1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F52A0184-F9FB-7249-BCA8-2F8B6C3580F3}" name="樞紐分析表1" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -33134,7 +34409,155 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A05ECE1-698D-3F42-A1F5-015F41A70879}" name="樞紐分析表2" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7019A1B8-C948-9248-8ABA-BFD05B6AA01A}" name="樞紐分析表1" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="56">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" numFmtId="177" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="20">
+        <item h="1" x="18"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="50"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="9" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="181"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A05ECE1-698D-3F42-A1F5-015F41A70879}" name="樞紐分析表2" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A37:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -33317,156 +34740,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7019A1B8-C948-9248-8ABA-BFD05B6AA01A}" name="樞紐分析表1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="56">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField axis="axisPage" dataField="1" numFmtId="177" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="20">
-        <item h="1" x="18"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="17"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="12"/>
-        <item x="5"/>
-        <item x="15"/>
-        <item x="13"/>
-        <item x="9"/>
-        <item x="16"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="50"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="9" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="181"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{458FE396-6E8A-064D-96E2-0847BBE52133}" name="樞紐分析表7" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="3ㄒㄧ1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{458FE396-6E8A-064D-96E2-0847BBE52133}" name="樞紐分析表7" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="3ㄒㄧ1">
   <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="57">
     <pivotField dataField="1" showAll="0"/>
@@ -33587,7 +34862,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B833B209-0CFF-0548-B5A9-F2903FE4CB01}" name="樞紐分析表1" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B833B209-0CFF-0548-B5A9-F2903FE4CB01}" name="樞紐分析表1" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="57">
     <pivotField showAll="0"/>
@@ -33766,7 +35041,363 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4D14CAE-2C58-9D43-B1F7-B8BBC66C68B5}" name="樞紐分析表2" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8299DB4-79E1-2840-954E-122EFC07C81F}" name="樞紐分析表3" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="B86:C118" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="57">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="50">
+        <item x="39"/>
+        <item x="14"/>
+        <item x="22"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="38"/>
+        <item x="47"/>
+        <item x="25"/>
+        <item x="43"/>
+        <item x="42"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="46"/>
+        <item x="18"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="31"/>
+        <item x="20"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="19"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="40"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="45"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="37"/>
+        <item x="32"/>
+        <item x="1"/>
+        <item x="27"/>
+        <item x="48"/>
+        <item x="9"/>
+        <item x="44"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0">
+      <items count="20">
+        <item x="18"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="31">
+        <item x="25"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="24"/>
+        <item x="28"/>
+        <item x="16"/>
+        <item x="23"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="22"/>
+        <item x="19"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="27"/>
+        <item x="4"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="1"/>
+        <item x="29"/>
+        <item x="26"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="20">
+        <item h="1" x="14"/>
+        <item h="1" x="4"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="13"/>
+        <item h="1" x="17"/>
+        <item h="1" x="8"/>
+        <item h="1" x="12"/>
+        <item h="1" x="5"/>
+        <item h="1" x="16"/>
+        <item h="1" x="1"/>
+        <item h="1" x="9"/>
+        <item h="1" x="6"/>
+        <item h="1" x="11"/>
+        <item h="1" x="7"/>
+        <item h="1" x="10"/>
+        <item h="1" x="18"/>
+        <item x="0"/>
+        <item h="1" x="15"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="28"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="32">
+    <i>
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="45"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+    </i>
+    <i r="1">
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="40"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="29" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="179"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4D14CAE-2C58-9D43-B1F7-B8BBC66C68B5}" name="樞紐分析表2" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="B48:D64" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="57">
     <pivotField showAll="0"/>
@@ -34093,8 +35724,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34FE811F-B077-FD42-9008-279DB01289D2}" name="樞紐分析表1" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34FE811F-B077-FD42-9008-279DB01289D2}" name="樞紐分析表1" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="57">
     <pivotField showAll="0"/>
@@ -34339,7 +35970,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D90A3B06-44FC-DF47-95B9-374674E5983F}" name="樞紐分析表2" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D90A3B06-44FC-DF47-95B9-374674E5983F}" name="樞紐分析表2" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:C49" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -34699,7 +36330,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C48516-4469-E144-BC4C-C411D0731588}" name="樞紐分析表4" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C48516-4469-E144-BC4C-C411D0731588}" name="樞紐分析表4" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:C49" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -35038,7 +36669,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E3E605F-0935-CE47-93A7-EE637CD6D22D}" name="樞紐分析表3" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E3E605F-0935-CE47-93A7-EE637CD6D22D}" name="樞紐分析表3" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B60" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -35398,7 +37029,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCF300E8-2DA3-FD4D-8DB5-C4AF4C0B2B4D}" name="樞紐分析表5" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCF300E8-2DA3-FD4D-8DB5-C4AF4C0B2B4D}" name="樞紐分析表5" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -35809,7 +37440,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{537918C9-6258-454A-9359-2B209B13DC90}" name="樞紐分析表6" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{537918C9-6258-454A-9359-2B209B13DC90}" name="樞紐分析表6" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -36150,7 +37781,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A78E8CA-AA2E-4542-B594-47B469B1ECF7}" name="樞紐分析表7" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A78E8CA-AA2E-4542-B594-47B469B1ECF7}" name="樞紐分析表7" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -36463,7 +38094,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4AA391D-DCC2-A047-A23D-C8888E109D7F}" name="樞紐分析表8" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4AA391D-DCC2-A047-A23D-C8888E109D7F}" name="樞紐分析表8" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -36779,7 +38410,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E436F8BC-6E9C-CD4C-8D5F-9F959847D2E8}" name="樞紐分析表9" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E436F8BC-6E9C-CD4C-8D5F-9F959847D2E8}" name="樞紐分析表9" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="56">
     <pivotField showAll="0"/>
@@ -46755,11 +48386,13 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F3EDA-67FF-1141-88FB-67CF8719809C}">
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -47101,10 +48734,282 @@
         <v>389</v>
       </c>
     </row>
+    <row r="84" spans="2:3">
+      <c r="B84" s="16" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3">
+      <c r="B86" s="16" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3">
+      <c r="B87" s="17" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C87" s="23">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3">
+      <c r="B88" s="21" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C88" s="23">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3">
+      <c r="B89" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C89" s="23">
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3">
+      <c r="B90" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="C90" s="23">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3">
+      <c r="B91" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="C91" s="23">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3">
+      <c r="B92" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C92" s="23">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3">
+      <c r="B93" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C93" s="23">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3">
+      <c r="B94" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C94" s="23">
+        <v>28.75</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3">
+      <c r="B95" s="21" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C95" s="23">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3">
+      <c r="B96" s="21" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C96" s="23">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3">
+      <c r="B97" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="C97" s="23">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3">
+      <c r="B98" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="C98" s="23">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3">
+      <c r="B99" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="C99" s="23">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3">
+      <c r="B100" s="21" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C100" s="23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3">
+      <c r="B101" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C101" s="23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3">
+      <c r="B102" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="C102" s="23">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3">
+      <c r="B103" s="21" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C103" s="23">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3">
+      <c r="B104" s="21" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C104" s="23">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3">
+      <c r="B105" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3">
+      <c r="B106" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C106" s="23">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3">
+      <c r="B107" s="21" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C107" s="23">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3">
+      <c r="B108" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C108" s="23">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3">
+      <c r="B109" s="21" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C109" s="23">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3">
+      <c r="B110" s="21" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C110" s="23">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3">
+      <c r="B111" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="C111" s="23">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3">
+      <c r="B112" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="C112" s="23">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3">
+      <c r="B113" s="17" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C113" s="23">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3">
+      <c r="B114" s="21" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C114" s="23">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3">
+      <c r="B115" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C115" s="23">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3">
+      <c r="B116" s="21" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C116" s="23">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3">
+      <c r="B117" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C117" s="23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3">
+      <c r="B118" s="17" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C118" s="23">
+        <v>27.85</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 

--- a/db/A7XLK-1102-HouseBigData.xlsx
+++ b/db/A7XLK-1102-HouseBigData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC61000-BEB6-B449-B34A-B4D4DE83A6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC8625-AFC8-E34D-957D-1A5946903BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17180" yWindow="-21080" windowWidth="27880" windowHeight="14620" activeTab="13" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
+    <workbookView xWindow="-11020" yWindow="-21080" windowWidth="28060" windowHeight="17440" firstSheet="4" activeTab="13" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure-1" sheetId="2" r:id="rId1"/>
@@ -26,8 +26,9 @@
     <sheet name="Figure-11" sheetId="12" r:id="rId11"/>
     <sheet name="Analysis-01" sheetId="13" r:id="rId12"/>
     <sheet name="車位分配" sheetId="14" r:id="rId13"/>
-    <sheet name="建案資料" sheetId="1" r:id="rId14"/>
-    <sheet name="Figure-12" sheetId="15" r:id="rId15"/>
+    <sheet name="Figure-21" sheetId="16" r:id="rId14"/>
+    <sheet name="建案資料" sheetId="1" r:id="rId15"/>
+    <sheet name="Figure-12" sheetId="15" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'Figure-8'!$E$4:$E$48</definedName>
@@ -36,8 +37,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId16"/>
-    <pivotCache cacheId="4" r:id="rId17"/>
+    <pivotCache cacheId="55" r:id="rId17"/>
+    <pivotCache cacheId="56" r:id="rId18"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="1199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="1244">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4530,10 +4531,147 @@
   </si>
   <si>
     <t>不變</t>
+  </si>
+  <si>
+    <t>不變</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大亮時代A7</t>
+  </si>
+  <si>
+    <t>允將大作</t>
+  </si>
+  <si>
+    <t>合謙學</t>
+  </si>
+  <si>
+    <t>君邑丘比特</t>
+  </si>
+  <si>
+    <t>富宇天匯</t>
+  </si>
+  <si>
+    <t>富宇哈佛苑</t>
+  </si>
+  <si>
+    <t>富宇悅峰</t>
+  </si>
+  <si>
+    <t>華悅城</t>
+  </si>
+  <si>
+    <t>新未來2</t>
+  </si>
+  <si>
+    <t>新未來3</t>
+  </si>
+  <si>
+    <t>頤昌璞岳</t>
+  </si>
+  <si>
+    <t>頤昌豐岳</t>
+  </si>
+  <si>
+    <t>(空白)</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>平均值 - 每坪價2022-平均</t>
+  </si>
+  <si>
+    <t>增幅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>平均漲幅</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -7482,6 +7620,1181 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
+    <c:name>[A7XLK-1102-HouseBigData.xlsx]Figure-21!樞紐分析表1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2400"/>
+              <a:t>A7</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" sz="2400"/>
+              <a:t>重劃區 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="2400"/>
+              <a:t>2020 - 2022 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" sz="2400"/>
+              <a:t>年房價漲幅</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="2400"/>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW"/>
+              <a:t>每坪均價為 建案最高與最低價的平均 </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-21'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平均值 - 每坪價-平均</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Figure-21'!$A$4:$A$66</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="31"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>和發大境</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>鴻典</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>台北國際村</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>富宇上城</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>禾悅花園</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>皇普MVP</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>富宇敦峰</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>和耀恆美</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>允將大作</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>新潤翡麗</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>根津苑</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>華悅城</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>富宇悅峰</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>友文化</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>水悅青青</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>文華天際</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>竹城甲子園</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>金捷市</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>鴻築捷市達</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>新A7</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>富御捷境</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>富宇哈佛苑</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>頤昌豐岳</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>新未來2</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>新未來3</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>和洲金剛</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>君邑丘比特</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>頤昌璞岳</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>合謙學</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>大亮時代A7</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>富宇天匯</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>101</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>102</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>107</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>201</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>202</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>204</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>205</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>207</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>301</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>303</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>305</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>306</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>307</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>309</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>310</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>311</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>401</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>402</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>403</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>405</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>406</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>407</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>408</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>409</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>410</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>411</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>412</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>413</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>414</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>415</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>502</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-21'!$B$4:$B$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>29.9</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>41</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5F27-8E4E-9147-8DFB66A1F8E6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-21'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平均值 - 每坪價2022-平均</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Figure-21'!$A$4:$A$66</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="31"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>和發大境</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>鴻典</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>台北國際村</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>富宇上城</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>禾悅花園</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>皇普MVP</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>富宇敦峰</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>和耀恆美</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>允將大作</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>新潤翡麗</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>根津苑</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>華悅城</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>富宇悅峰</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>友文化</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>水悅青青</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>文華天際</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>竹城甲子園</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>金捷市</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>鴻築捷市達</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>新A7</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>富御捷境</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>富宇哈佛苑</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>頤昌豐岳</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>新未來2</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>新未來3</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>和洲金剛</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>君邑丘比特</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>頤昌璞岳</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>合謙學</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>大亮時代A7</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>富宇天匯</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>101</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>102</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>107</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>201</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>202</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>204</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>205</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>207</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>301</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>303</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>305</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>306</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>307</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>309</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>310</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>311</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>401</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>402</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>403</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>405</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>406</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>407</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>408</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>409</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>410</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>411</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>412</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>413</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>414</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>415</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>502</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-21'!$C$4:$C$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>40.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>47.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5F27-8E4E-9147-8DFB66A1F8E6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
+        <c:axId val="932012447"/>
+        <c:axId val="1023164527"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="932012447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1023164527"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1023164527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="932012447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+          <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
     <c:name>[A7XLK-1102-HouseBigData.xlsx]Figure-12!樞紐分析表1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
@@ -7954,7 +9267,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -8800,7 +10113,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -18090,6 +19403,46 @@
 </file>
 
 <file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -20442,6 +21795,511 @@
 </file>
 
 <file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -20944,7 +22802,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -21449,7 +23307,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -26272,6 +28130,47 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3386B352-5316-014B-9F78-2DD6179F268A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>400050</xdr:colOff>
       <xdr:row>6</xdr:row>
@@ -26934,13 +28833,63 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tai-Chung Wang" refreshedDate="44472.289513310185" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="49" xr:uid="{78A0FC35-D0DC-F040-ACE8-196B93C53EDE}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44602.137552893517" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="49" xr:uid="{78A0FC35-D0DC-F040-ACE8-196B93C53EDE}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:BJ50" sheet="建案資料"/>
   </cacheSource>
-  <cacheFields count="57">
+  <cacheFields count="62">
     <cacheField name="no" numFmtId="49">
-      <sharedItems/>
+      <sharedItems count="49">
+        <s v="101"/>
+        <s v="102"/>
+        <s v="103"/>
+        <s v="104"/>
+        <s v="105"/>
+        <s v="106"/>
+        <s v="107"/>
+        <s v="201"/>
+        <s v="202"/>
+        <s v="203"/>
+        <s v="204"/>
+        <s v="205"/>
+        <s v="206"/>
+        <s v="207"/>
+        <s v="301"/>
+        <s v="302"/>
+        <s v="303"/>
+        <s v="304"/>
+        <s v="305"/>
+        <s v="306"/>
+        <s v="307"/>
+        <s v="308"/>
+        <s v="309"/>
+        <s v="310"/>
+        <s v="311"/>
+        <s v="401"/>
+        <s v="402"/>
+        <s v="403"/>
+        <s v="404"/>
+        <s v="405"/>
+        <s v="406"/>
+        <s v="407"/>
+        <s v="408"/>
+        <s v="409"/>
+        <s v="410"/>
+        <s v="411"/>
+        <s v="412"/>
+        <s v="413"/>
+        <s v="414"/>
+        <s v="415"/>
+        <s v="501"/>
+        <s v="502"/>
+        <s v="503"/>
+        <s v="504"/>
+        <s v="505"/>
+        <s v="506"/>
+        <s v="507"/>
+        <s v="508"/>
+        <s v="509"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="區域" numFmtId="49">
       <sharedItems/>
@@ -27037,6 +28986,52 @@
         <n v="41"/>
         <n v="29"/>
         <n v="15"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="單價2022" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="每坪價2022-最低" numFmtId="177">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="15" maxValue="45"/>
+    </cacheField>
+    <cacheField name="每坪價2022-最高" numFmtId="177">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="15" maxValue="50"/>
+    </cacheField>
+    <cacheField name="每坪價2022-平均" numFmtId="177">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="15" maxValue="47.5" count="27">
+        <n v="35"/>
+        <n v="29"/>
+        <n v="26"/>
+        <n v="25"/>
+        <n v="27"/>
+        <n v="28"/>
+        <n v="46.5"/>
+        <n v="36"/>
+        <n v="27.5"/>
+        <n v="40"/>
+        <n v="37.5"/>
+        <n v="40.5"/>
+        <n v="34.5"/>
+        <n v="36.5"/>
+        <n v="33"/>
+        <n v="39.5"/>
+        <n v="30.5"/>
+        <n v="24.5"/>
+        <n v="33.5"/>
+        <n v="31"/>
+        <n v="30"/>
+        <n v="35.5"/>
+        <n v="34"/>
+        <n v="32.5"/>
+        <n v="38.5"/>
+        <n v="47.5"/>
+        <n v="15"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="不變" numFmtId="177">
+      <sharedItems containsBlank="1" count="2">
+        <m/>
+        <s v="Y"/>
       </sharedItems>
     </cacheField>
     <cacheField name="FacebookName" numFmtId="0">
@@ -27169,76 +29164,10 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="住家戶數" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="87" maxValue="1780" count="45">
-        <n v="280"/>
-        <n v="196"/>
-        <n v="326"/>
-        <n v="173"/>
-        <n v="187"/>
-        <n v="186"/>
-        <n v="198"/>
-        <n v="832"/>
-        <n v="1044"/>
-        <n v="199"/>
-        <n v="308"/>
-        <n v="441"/>
-        <n v="138"/>
-        <n v="530"/>
-        <n v="235"/>
-        <n v="420"/>
-        <n v="266"/>
-        <n v="225"/>
-        <n v="776"/>
-        <n v="264"/>
-        <n v="112"/>
-        <n v="305"/>
-        <n v="204"/>
-        <n v="478"/>
-        <n v="1144"/>
-        <n v="754"/>
-        <n v="771"/>
-        <n v="257"/>
-        <n v="371"/>
-        <n v="337"/>
-        <n v="483"/>
-        <n v="154"/>
-        <n v="376"/>
-        <n v="582"/>
-        <n v="210"/>
-        <n v="124"/>
-        <n v="106"/>
-        <n v="87"/>
-        <n v="807"/>
-        <n v="168"/>
-        <n v="103"/>
-        <n v="1272"/>
-        <n v="1780"/>
-        <n v="514"/>
-        <n v="897"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="87" maxValue="1780"/>
     </cacheField>
     <cacheField name="商店戶數" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="31" count="19">
-        <n v="12"/>
-        <n v="11"/>
-        <n v="20"/>
-        <n v="7"/>
-        <n v="8"/>
-        <n v="0"/>
-        <n v="2"/>
-        <n v="13"/>
-        <n v="5"/>
-        <n v="4"/>
-        <n v="3"/>
-        <n v="30"/>
-        <n v="23"/>
-        <n v="31"/>
-        <n v="9"/>
-        <n v="16"/>
-        <n v="14"/>
-        <n v="6"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="31"/>
     </cacheField>
     <cacheField name="建蔽率" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="0.3347" maxValue="0.59850000000000003"/>
@@ -27318,11 +29247,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tai-Chung Wang" refreshedDate="44472.289513773147" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="49" xr:uid="{B403CB59-CB11-6E4E-BA2E-0EB34E557D07}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44602.13755324074" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="49" xr:uid="{B403CB59-CB11-6E4E-BA2E-0EB34E557D07}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:BI50" sheet="建案資料"/>
   </cacheSource>
-  <cacheFields count="56">
+  <cacheFields count="61">
     <cacheField name="no" numFmtId="49">
       <sharedItems/>
     </cacheField>
@@ -27445,6 +29374,21 @@
         <n v="29"/>
         <n v="15"/>
       </sharedItems>
+    </cacheField>
+    <cacheField name="單價2022" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="每坪價2022-最低" numFmtId="177">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="15" maxValue="45"/>
+    </cacheField>
+    <cacheField name="每坪價2022-最高" numFmtId="177">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="15" maxValue="50"/>
+    </cacheField>
+    <cacheField name="每坪價2022-平均" numFmtId="177">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="15" maxValue="47.5"/>
+    </cacheField>
+    <cacheField name="不變" numFmtId="177">
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="FacebookName" numFmtId="0">
       <sharedItems containsBlank="1"/>
@@ -27777,7 +29721,7 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="49">
   <r>
-    <s v="101"/>
+    <x v="0"/>
     <s v="1.樂善國小生活圈"/>
     <x v="0"/>
     <s v="101 和發大境"/>
@@ -27786,6 +29730,11 @@
     <s v="28~29 萬/坪"/>
     <n v="28"/>
     <n v="29"/>
+    <x v="0"/>
+    <s v="34~36 萬/坪"/>
+    <n v="34"/>
+    <n v="36"/>
+    <x v="0"/>
     <x v="0"/>
     <m/>
     <m/>
@@ -27813,8 +29762,8 @@
     <n v="0.33"/>
     <n v="0.33"/>
     <s v="3幢，8棟，280戶住家，12戶店面"/>
-    <x v="0"/>
-    <x v="0"/>
+    <n v="280"/>
+    <n v="12"/>
     <n v="0.40899999999999997"/>
     <n v="0.40899999999999997"/>
     <s v="地上15層，地下4層"/>
@@ -27836,7 +29785,7 @@
     <x v="0"/>
   </r>
   <r>
-    <s v="102"/>
+    <x v="1"/>
     <s v="1.樂善國小生活圈"/>
     <x v="1"/>
     <s v="102 鴻典"/>
@@ -27846,6 +29795,11 @@
     <n v="26"/>
     <n v="26"/>
     <x v="1"/>
+    <s v="29萬元/坪"/>
+    <n v="29"/>
+    <n v="29"/>
+    <x v="1"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -27872,8 +29826,8 @@
     <s v="32%"/>
     <n v="0.32"/>
     <s v="1幢，2棟，196戶住家，11戶店面"/>
-    <x v="1"/>
-    <x v="1"/>
+    <n v="196"/>
+    <n v="11"/>
     <s v="39.8%"/>
     <n v="0.39800000000000002"/>
     <s v="地上15層，地下3層"/>
@@ -27895,7 +29849,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="103"/>
+    <x v="2"/>
     <s v="1.樂善國小生活圈"/>
     <x v="2"/>
     <s v="103 樂捷市"/>
@@ -27904,6 +29858,11 @@
     <s v="26萬元/坪"/>
     <n v="26"/>
     <n v="26"/>
+    <x v="1"/>
+    <s v="26萬元/坪"/>
+    <n v="26"/>
+    <n v="26"/>
+    <x v="2"/>
     <x v="1"/>
     <s v="樂捷市好鄰居"/>
     <s v="https://www.facebook.com/groups/324107612343329"/>
@@ -27931,8 +29890,8 @@
     <s v="31.5%"/>
     <n v="0.315"/>
     <s v="1幢，8棟，326戶住家，20戶店面"/>
-    <x v="2"/>
-    <x v="2"/>
+    <n v="326"/>
+    <n v="20"/>
     <s v="49.56%"/>
     <n v="0.49559999999999998"/>
     <s v="地上15層，地下3層"/>
@@ -27954,7 +29913,7 @@
     <x v="0"/>
   </r>
   <r>
-    <s v="104"/>
+    <x v="3"/>
     <s v="1.樂善國小生活圈"/>
     <x v="3"/>
     <s v="104 奇幻莊園"/>
@@ -27964,6 +29923,11 @@
     <n v="24.5"/>
     <n v="25.5"/>
     <x v="2"/>
+    <s v="24.5~25.5萬元/坪"/>
+    <n v="24.5"/>
+    <n v="25.5"/>
+    <x v="3"/>
+    <x v="1"/>
     <s v="龜山A7-奇幻莊園住戶"/>
     <s v="https://www.facebook.com/groups/588376114975687"/>
     <m/>
@@ -27990,8 +29954,8 @@
     <s v="32%"/>
     <n v="0.32"/>
     <s v="1幢，3棟，173戶住家，11戶店面"/>
-    <x v="3"/>
-    <x v="1"/>
+    <n v="173"/>
+    <n v="11"/>
     <s v="48.26%"/>
     <n v="0.48259999999999997"/>
     <s v="地上13,14層，地下4層"/>
@@ -28013,7 +29977,7 @@
     <x v="0"/>
   </r>
   <r>
-    <s v="105"/>
+    <x v="4"/>
     <s v="1.樂善國小生活圈"/>
     <x v="4"/>
     <s v="105 樂田田"/>
@@ -28023,6 +29987,11 @@
     <n v="25"/>
     <n v="26"/>
     <x v="3"/>
+    <s v="25~26 萬/坪"/>
+    <n v="26"/>
+    <n v="26"/>
+    <x v="2"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -28049,8 +30018,8 @@
     <n v="0.32600000000000001"/>
     <n v="0.32600000000000001"/>
     <s v="2幢，4棟，187戶住家，12戶店面"/>
-    <x v="4"/>
-    <x v="0"/>
+    <n v="187"/>
+    <n v="12"/>
     <n v="0.44269999999999998"/>
     <n v="0.44269999999999998"/>
     <s v="地上13、14層，地下4層"/>
@@ -28072,7 +30041,7 @@
     <x v="0"/>
   </r>
   <r>
-    <s v="106"/>
+    <x v="5"/>
     <s v="1.樂善國小生活圈"/>
     <x v="5"/>
     <s v="106 玉子園"/>
@@ -28082,6 +30051,11 @@
     <n v="26"/>
     <n v="28"/>
     <x v="4"/>
+    <s v="26~28萬元/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <x v="4"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -28108,8 +30082,8 @@
     <s v="31~32%"/>
     <n v="0.315"/>
     <s v="5棟，186戶住家，7戶店面"/>
-    <x v="5"/>
-    <x v="3"/>
+    <n v="186"/>
+    <n v="7"/>
     <s v="44.23%"/>
     <n v="0.44230000000000003"/>
     <s v="地上15層，地下3層"/>
@@ -28131,7 +30105,7 @@
     <x v="0"/>
   </r>
   <r>
-    <s v="107"/>
+    <x v="6"/>
     <s v="1.樂善國小生活圈"/>
     <x v="6"/>
     <s v="107 台北國際村"/>
@@ -28141,6 +30115,11 @@
     <n v="25"/>
     <n v="26"/>
     <x v="3"/>
+    <s v="27~29 萬/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <x v="5"/>
+    <x v="0"/>
     <s v="台北國際村住戶交流園區_林口A7"/>
     <s v="https://www.facebook.com/groups/2397202740545114"/>
     <m/>
@@ -28167,8 +30146,8 @@
     <s v="31~32%"/>
     <n v="0.315"/>
     <s v="4棟，198戶住家，8戶店面"/>
-    <x v="6"/>
-    <x v="4"/>
+    <n v="198"/>
+    <n v="8"/>
     <s v="45.67%"/>
     <n v="0.45669999999999999"/>
     <s v="地上15層，地下4層"/>
@@ -28190,7 +30169,7 @@
     <x v="0"/>
   </r>
   <r>
-    <s v="201"/>
+    <x v="7"/>
     <s v="2.樂善園區周邊"/>
     <x v="7"/>
     <s v="201 富宇上城"/>
@@ -28200,6 +30179,11 @@
     <n v="30"/>
     <n v="35"/>
     <x v="5"/>
+    <s v="44~49 萬/坪"/>
+    <n v="44"/>
+    <n v="49"/>
+    <x v="6"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -28226,8 +30210,8 @@
     <s v="33.5%"/>
     <n v="0.33500000000000002"/>
     <s v="4幢，6棟，832戶住家"/>
-    <x v="7"/>
-    <x v="5"/>
+    <n v="832"/>
+    <n v="0"/>
     <s v="31.07%"/>
     <n v="0.31069999999999998"/>
     <s v="地上24層，地下4層"/>
@@ -28249,7 +30233,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="202"/>
+    <x v="8"/>
     <s v="2.樂善園區周邊"/>
     <x v="8"/>
     <s v="202 禾悅花園"/>
@@ -28258,6 +30242,11 @@
     <s v="28~29萬元/坪"/>
     <n v="28"/>
     <n v="29"/>
+    <x v="0"/>
+    <s v="35~37 萬/坪"/>
+    <n v="35"/>
+    <n v="37"/>
+    <x v="7"/>
     <x v="0"/>
     <m/>
     <m/>
@@ -28285,8 +30274,8 @@
     <s v="33.5%"/>
     <n v="0.33500000000000002"/>
     <s v="1幢，13棟，1044戶住家"/>
-    <x v="8"/>
-    <x v="5"/>
+    <n v="1044"/>
+    <n v="0"/>
     <s v="52.94%"/>
     <n v="0.52939999999999998"/>
     <s v="地上14~15層，地下4層"/>
@@ -28308,7 +30297,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="203"/>
+    <x v="9"/>
     <s v="2.樂善園區周邊"/>
     <x v="9"/>
     <s v="203 耀台北"/>
@@ -28318,6 +30307,11 @@
     <n v="26"/>
     <n v="28"/>
     <x v="4"/>
+    <s v="26~28萬元/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <x v="4"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -28344,8 +30338,8 @@
     <s v="31.5%"/>
     <n v="0.315"/>
     <s v="5棟，199戶住家，2戶店面"/>
-    <x v="9"/>
-    <x v="6"/>
+    <n v="199"/>
+    <n v="2"/>
     <s v="46.14%"/>
     <n v="0.46139999999999998"/>
     <s v="地上15層，地下4層"/>
@@ -28367,7 +30361,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="204"/>
+    <x v="10"/>
     <s v="2.樂善園區周邊"/>
     <x v="10"/>
     <s v="204 皇普MVP"/>
@@ -28377,6 +30371,11 @@
     <n v="25"/>
     <n v="26"/>
     <x v="3"/>
+    <s v="27~28 萬/坪"/>
+    <n v="27"/>
+    <n v="28"/>
+    <x v="8"/>
+    <x v="0"/>
     <s v="A7皇普MVP屋主交流團"/>
     <s v="https://www.facebook.com/groups/800873736965340"/>
     <m/>
@@ -28403,8 +30402,8 @@
     <n v="0.31859999999999999"/>
     <n v="0.31859999999999999"/>
     <s v="6棟，308戶住家，13戶店面"/>
-    <x v="10"/>
-    <x v="7"/>
+    <n v="308"/>
+    <n v="13"/>
     <n v="0.47989999999999999"/>
     <n v="0.47989999999999999"/>
     <s v="地上15層，地下4層"/>
@@ -28426,7 +30425,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="205"/>
+    <x v="11"/>
     <s v="2.樂善園區周邊"/>
     <x v="11"/>
     <s v="205 富宇敦峰"/>
@@ -28436,6 +30435,11 @@
     <n v="30"/>
     <n v="32"/>
     <x v="6"/>
+    <s v="38~42 萬/坪"/>
+    <n v="38"/>
+    <n v="42"/>
+    <x v="9"/>
+    <x v="0"/>
     <s v="富宇敦峰住戶社團"/>
     <s v="https://www.facebook.com/groups/124542338433380"/>
     <m/>
@@ -28462,8 +30466,8 @@
     <s v="33.35%"/>
     <n v="0.33350000000000002"/>
     <s v="8棟，441戶住家，7戶店面"/>
-    <x v="11"/>
-    <x v="3"/>
+    <n v="441"/>
+    <n v="7"/>
     <s v="43.92%"/>
     <n v="0.43919999999999998"/>
     <s v="地上15層，地下3層"/>
@@ -28485,7 +30489,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="206"/>
+    <x v="12"/>
     <s v="2.樂善園區周邊"/>
     <x v="12"/>
     <s v="206 玄泰V1"/>
@@ -28495,6 +30499,11 @@
     <n v="27"/>
     <n v="29"/>
     <x v="7"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <x v="5"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -28521,8 +30530,8 @@
     <s v="31.9%"/>
     <n v="0.31900000000000001"/>
     <s v="2棟，138戶住家，8戶店面，125戶一般事務所"/>
-    <x v="12"/>
-    <x v="4"/>
+    <n v="138"/>
+    <n v="8"/>
     <s v="60.16%"/>
     <n v="0.60160000000000002"/>
     <s v="地上24層，地下5層"/>
@@ -28544,7 +30553,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="207"/>
+    <x v="13"/>
     <s v="2.樂善園區周邊"/>
     <x v="13"/>
     <s v="207 和耀恆美"/>
@@ -28554,6 +30563,11 @@
     <n v="28"/>
     <n v="33"/>
     <x v="8"/>
+    <s v="35~40 萬/坪"/>
+    <n v="35"/>
+    <n v="40"/>
+    <x v="10"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -28580,8 +30594,8 @@
     <s v="32~32.5%"/>
     <n v="0.32250000000000001"/>
     <s v="1幢，7棟，280戶住家，11戶店面"/>
-    <x v="0"/>
-    <x v="1"/>
+    <n v="280"/>
+    <n v="11"/>
     <n v="0.4743"/>
     <n v="0.4743"/>
     <s v="地上15層，地下4層"/>
@@ -28603,7 +30617,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="301"/>
+    <x v="14"/>
     <s v="3.華亞園區周邊"/>
     <x v="14"/>
     <s v="301 允將大作"/>
@@ -28613,6 +30627,11 @@
     <n v="35"/>
     <n v="38"/>
     <x v="9"/>
+    <s v="38~43 萬/坪"/>
+    <n v="38"/>
+    <n v="43"/>
+    <x v="11"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -28639,8 +30658,8 @@
     <n v="0.33800000000000002"/>
     <n v="0.33800000000000002"/>
     <s v="1幢，7棟，530戶住家，5戶店面，20戶事務所，1戶管委會空間"/>
-    <x v="13"/>
-    <x v="8"/>
+    <n v="530"/>
+    <n v="5"/>
     <n v="0.45529999999999998"/>
     <n v="0.45529999999999998"/>
     <s v="地上31層，地下6層"/>
@@ -28662,7 +30681,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="302"/>
+    <x v="15"/>
     <s v="3.華亞園區周邊"/>
     <x v="15"/>
     <s v="302 欣時代"/>
@@ -28672,6 +30691,11 @@
     <n v="27"/>
     <n v="29"/>
     <x v="7"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <x v="5"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -28698,8 +30722,8 @@
     <s v="33.5%"/>
     <n v="0.33500000000000002"/>
     <s v="5棟，235戶住家，4戶店面，19戶一般事務所"/>
-    <x v="14"/>
-    <x v="9"/>
+    <n v="235"/>
+    <n v="4"/>
     <s v="57.49%"/>
     <n v="0.57489999999999997"/>
     <s v="地上30層，地下6層"/>
@@ -28721,7 +30745,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="303"/>
+    <x v="16"/>
     <s v="3.華亞園區周邊"/>
     <x v="16"/>
     <s v="303 新潤翡麗"/>
@@ -28731,6 +30755,11 @@
     <n v="26"/>
     <n v="28"/>
     <x v="4"/>
+    <s v="33~36 萬/坪"/>
+    <n v="33"/>
+    <n v="36"/>
+    <x v="12"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -28757,8 +30786,8 @@
     <s v="33.5~34.5%"/>
     <n v="0.33750000000000002"/>
     <s v="1幢，2棟，420戶住家，20戶店面，11戶一般事務所"/>
-    <x v="15"/>
-    <x v="2"/>
+    <n v="420"/>
+    <n v="20"/>
     <s v="65.02%"/>
     <n v="0.6502"/>
     <s v="地上24層，地下5層"/>
@@ -28780,7 +30809,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="304"/>
+    <x v="17"/>
     <s v="3.華亞園區周邊"/>
     <x v="17"/>
     <s v="304 新潤鉑麗"/>
@@ -28790,6 +30819,11 @@
     <n v="27"/>
     <n v="29"/>
     <x v="7"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <x v="5"/>
+    <x v="1"/>
     <s v="新潤翡麗住戶天地"/>
     <s v="https://www.facebook.com/groups/321511928734593"/>
     <m/>
@@ -28816,8 +30850,8 @@
     <n v="0.33500000000000002"/>
     <n v="0.33500000000000002"/>
     <s v="2幢，3棟，266戶住家，13戶店面"/>
-    <x v="16"/>
-    <x v="7"/>
+    <n v="266"/>
+    <n v="13"/>
     <n v="0.59850000000000003"/>
     <n v="0.59850000000000003"/>
     <s v="地上15層，地下4層"/>
@@ -28839,7 +30873,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="305"/>
+    <x v="18"/>
     <s v="3.華亞園區周邊"/>
     <x v="18"/>
     <s v="305 根津苑"/>
@@ -28849,6 +30883,11 @@
     <n v="24"/>
     <n v="26"/>
     <x v="2"/>
+    <s v="26~28 萬/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <x v="4"/>
+    <x v="0"/>
     <s v="根津苑"/>
     <s v="https://www.facebook.com/%E6%A0%B9%E6%B4%A5%E8%8B%91-102597158541363"/>
     <m/>
@@ -28875,8 +30914,8 @@
     <s v="32%"/>
     <n v="0.32"/>
     <s v="4棟，225戶住家，3戶店面"/>
-    <x v="17"/>
-    <x v="10"/>
+    <n v="225"/>
+    <n v="3"/>
     <s v="50.54%"/>
     <n v="0.50539999999999996"/>
     <s v="地上15層，地下4層"/>
@@ -28898,7 +30937,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="306"/>
+    <x v="19"/>
     <s v="3.華亞園區周邊"/>
     <x v="19"/>
     <s v="306 華悅城"/>
@@ -28908,6 +30947,11 @@
     <n v="26"/>
     <n v="30"/>
     <x v="7"/>
+    <s v="26~30萬元/坪"/>
+    <n v="26"/>
+    <n v="30"/>
+    <x v="5"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -28934,8 +30978,8 @@
     <n v="0.34"/>
     <n v="0.34"/>
     <s v="3棟，776戶住家，8戶店面"/>
-    <x v="18"/>
-    <x v="4"/>
+    <n v="776"/>
+    <n v="8"/>
     <n v="0.44359999999999999"/>
     <n v="0.44359999999999999"/>
     <s v="地上18層，地下4層"/>
@@ -28957,7 +31001,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="307"/>
+    <x v="20"/>
     <s v="3.華亞園區周邊"/>
     <x v="20"/>
     <s v="307 富宇悅峰"/>
@@ -28967,6 +31011,11 @@
     <n v="28"/>
     <n v="32"/>
     <x v="10"/>
+    <s v="34~36 萬/坪"/>
+    <n v="34"/>
+    <n v="36"/>
+    <x v="0"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -28993,8 +31042,8 @@
     <s v="33.5~40%"/>
     <n v="0.36799999999999999"/>
     <s v="5棟，264戶住家"/>
-    <x v="19"/>
-    <x v="5"/>
+    <n v="264"/>
+    <n v="0"/>
     <s v="40.21%"/>
     <n v="0.40210000000000001"/>
     <s v="地上14層，地下4層"/>
@@ -29016,7 +31065,7 @@
     <x v="2"/>
   </r>
   <r>
-    <s v="308"/>
+    <x v="21"/>
     <s v="3.華亞園區周邊"/>
     <x v="21"/>
     <s v="308 合遠新天地"/>
@@ -29026,6 +31075,11 @@
     <n v="24"/>
     <n v="26"/>
     <x v="2"/>
+    <s v="24~26萬元/坪"/>
+    <n v="24"/>
+    <n v="26"/>
+    <x v="3"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -29052,8 +31106,8 @@
     <s v="31~32%"/>
     <n v="0.315"/>
     <s v="2棟，112戶住家，4戶店面"/>
-    <x v="20"/>
-    <x v="9"/>
+    <n v="112"/>
+    <n v="4"/>
     <s v="33.97%"/>
     <n v="0.3397"/>
     <s v="地上15層，地下4層"/>
@@ -29075,7 +31129,7 @@
     <x v="2"/>
   </r>
   <r>
-    <s v="309"/>
+    <x v="22"/>
     <s v="3.華亞園區周邊"/>
     <x v="22"/>
     <s v="309 友文化"/>
@@ -29085,6 +31139,11 @@
     <n v="30"/>
     <n v="31"/>
     <x v="8"/>
+    <s v="28萬元/坪"/>
+    <n v="28"/>
+    <n v="28"/>
+    <x v="5"/>
+    <x v="0"/>
     <s v="友文化"/>
     <s v="https://www.facebook.com/groups/710305099774047"/>
     <m/>
@@ -29111,8 +31170,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="3幢，7棟，305戶住家"/>
-    <x v="21"/>
-    <x v="5"/>
+    <n v="305"/>
+    <n v="0"/>
     <n v="0.44209999999999999"/>
     <n v="0.44209999999999999"/>
     <s v="地上15層，地下4層"/>
@@ -29134,7 +31193,7 @@
     <x v="2"/>
   </r>
   <r>
-    <s v="310"/>
+    <x v="23"/>
     <s v="3.華亞園區周邊"/>
     <x v="23"/>
     <s v="310 水悅青青"/>
@@ -29144,6 +31203,11 @@
     <n v="29"/>
     <n v="31"/>
     <x v="10"/>
+    <s v="34~39 萬/坪"/>
+    <n v="34"/>
+    <n v="39"/>
+    <x v="13"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29170,8 +31234,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="1幢，3棟，204戶住家，7戶店面"/>
-    <x v="22"/>
-    <x v="3"/>
+    <n v="204"/>
+    <n v="7"/>
     <n v="0.55610000000000004"/>
     <n v="0.55610000000000004"/>
     <s v="地上13、14層，地下5層"/>
@@ -29193,7 +31257,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="311"/>
+    <x v="24"/>
     <s v="3.華亞園區周邊"/>
     <x v="24"/>
     <s v="311 文華天際"/>
@@ -29203,6 +31267,11 @@
     <n v="27"/>
     <n v="27"/>
     <x v="4"/>
+    <s v="32~34 萬/坪"/>
+    <n v="32"/>
+    <n v="34"/>
+    <x v="14"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29229,8 +31298,8 @@
     <n v="0.32500000000000001"/>
     <n v="0.33"/>
     <s v="1幢，2棟，478戶住家，8戶店面"/>
-    <x v="23"/>
-    <x v="4"/>
+    <n v="478"/>
+    <n v="8"/>
     <n v="0.3347"/>
     <n v="0.3347"/>
     <s v="地上22層，地下4層"/>
@@ -29252,7 +31321,7 @@
     <x v="2"/>
   </r>
   <r>
-    <s v="401"/>
+    <x v="25"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="25"/>
     <s v="401 竹城甲子園"/>
@@ -29262,6 +31331,11 @@
     <n v="26"/>
     <n v="28"/>
     <x v="4"/>
+    <s v="38~41 萬/坪"/>
+    <n v="38"/>
+    <n v="41"/>
+    <x v="15"/>
+    <x v="0"/>
     <s v="竹城甲子園住戶交流區"/>
     <s v="https://www.facebook.com/groups/1127911624065990"/>
     <m/>
@@ -29288,8 +31362,8 @@
     <s v="32.5%"/>
     <n v="0.32500000000000001"/>
     <s v="8棟，1144戶住家，30戶店面，33戶一般事務所，2戶商場"/>
-    <x v="24"/>
-    <x v="11"/>
+    <n v="1144"/>
+    <n v="30"/>
     <s v="50.21%"/>
     <n v="0.50209999999999999"/>
     <s v="地上24層，地下4層"/>
@@ -29311,7 +31385,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="402"/>
+    <x v="26"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="26"/>
     <s v="402 金捷市"/>
@@ -29321,6 +31395,11 @@
     <n v="30.5"/>
     <n v="30.5"/>
     <x v="8"/>
+    <s v="30.5萬元/坪"/>
+    <n v="30.5"/>
+    <n v="30.5"/>
+    <x v="16"/>
+    <x v="0"/>
     <s v="金捷市準鄰居交流園地"/>
     <s v="https://www.facebook.com/groups/238626460426128"/>
     <m/>
@@ -29347,8 +31426,8 @@
     <s v="31.9%"/>
     <n v="0.31900000000000001"/>
     <s v="4幢，754戶住家，23戶店面, 1商場"/>
-    <x v="25"/>
-    <x v="12"/>
+    <n v="754"/>
+    <n v="23"/>
     <s v="50.74%"/>
     <n v="0.50739999999999996"/>
     <s v="地上28層，地下6層"/>
@@ -29370,7 +31449,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="403"/>
+    <x v="27"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="27"/>
     <s v="403 鴻築捷市達"/>
@@ -29380,6 +31459,11 @@
     <n v="35"/>
     <n v="38"/>
     <x v="9"/>
+    <s v="45~48 萬/坪"/>
+    <n v="45"/>
+    <n v="48"/>
+    <x v="6"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29406,8 +31490,8 @@
     <s v="32%"/>
     <n v="0.32"/>
     <s v="1幢，4棟，771戶住家，31戶店面，1戶商場"/>
-    <x v="26"/>
-    <x v="13"/>
+    <n v="771"/>
+    <n v="31"/>
     <s v="49.53%"/>
     <n v="0.49530000000000002"/>
     <s v="地上29層，地下5層"/>
@@ -29429,7 +31513,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="404"/>
+    <x v="28"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="28"/>
     <s v="404 詠勝市中欣"/>
@@ -29439,6 +31523,11 @@
     <n v="27"/>
     <n v="32"/>
     <x v="11"/>
+    <s v="24~25 萬/坪"/>
+    <n v="24"/>
+    <n v="25"/>
+    <x v="17"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -29465,8 +31554,8 @@
     <s v="33%"/>
     <n v="0.33"/>
     <s v="1棟，257戶住家，7戶店面，32戶一般事務所"/>
-    <x v="27"/>
-    <x v="3"/>
+    <n v="257"/>
+    <n v="7"/>
     <s v="53.26%"/>
     <n v="0.53259999999999996"/>
     <s v="地上22層，地下5層"/>
@@ -29488,7 +31577,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="405"/>
+    <x v="29"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="29"/>
     <s v="405 新A7"/>
@@ -29498,6 +31587,11 @@
     <n v="31"/>
     <n v="33"/>
     <x v="12"/>
+    <s v="32~35 萬/坪"/>
+    <n v="32"/>
+    <n v="35"/>
+    <x v="18"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29524,8 +31618,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="4幢，7棟，371戶住家，3戶店面"/>
-    <x v="28"/>
-    <x v="10"/>
+    <n v="371"/>
+    <n v="3"/>
     <n v="0.46450000000000002"/>
     <n v="0.46450000000000002"/>
     <s v="地上15層，地下4層"/>
@@ -29547,7 +31641,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="406"/>
+    <x v="30"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="30"/>
     <s v="406 富御捷境"/>
@@ -29557,6 +31651,11 @@
     <n v="27"/>
     <n v="29"/>
     <x v="7"/>
+    <s v="30~32 萬/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <x v="19"/>
+    <x v="0"/>
     <s v="A7 富御捷境好鄰居交流團"/>
     <s v="https://www.facebook.com/groups/1970564956581068"/>
     <m/>
@@ -29583,8 +31682,8 @@
     <s v="31.5%"/>
     <n v="0.315"/>
     <s v="5棟，337戶住家，2戶店面"/>
-    <x v="29"/>
-    <x v="6"/>
+    <n v="337"/>
+    <n v="2"/>
     <s v="47.5%"/>
     <n v="0.47499999999999998"/>
     <s v="地上14~15層，地下4層"/>
@@ -29606,7 +31705,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="407"/>
+    <x v="31"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="31"/>
     <s v="407 富宇哈佛苑"/>
@@ -29616,6 +31715,11 @@
     <n v="33"/>
     <n v="38"/>
     <x v="13"/>
+    <s v="44~49 萬/坪"/>
+    <n v="44"/>
+    <n v="49"/>
+    <x v="6"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29642,8 +31746,8 @@
     <s v="33.5%"/>
     <n v="0.33500000000000002"/>
     <s v="1幢，3棟，483戶住家，8戶店面"/>
-    <x v="30"/>
-    <x v="4"/>
+    <n v="483"/>
+    <n v="8"/>
     <s v="44.18%"/>
     <n v="0.44180000000000003"/>
     <s v="地上24層，地下4層"/>
@@ -29665,7 +31769,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="408"/>
+    <x v="32"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="32"/>
     <s v="408 頤昌豐岳"/>
@@ -29675,6 +31779,11 @@
     <n v="30"/>
     <n v="30"/>
     <x v="10"/>
+    <s v="30萬元/坪"/>
+    <n v="30"/>
+    <n v="30"/>
+    <x v="20"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29701,8 +31810,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="2棟，154戶住家，9戶店面"/>
-    <x v="31"/>
-    <x v="14"/>
+    <n v="154"/>
+    <n v="9"/>
     <n v="0.4622"/>
     <n v="0.4622"/>
     <s v="地上15層，地下4層"/>
@@ -29724,7 +31833,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="409"/>
+    <x v="33"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="33"/>
     <s v="409 新未來2"/>
@@ -29734,6 +31843,11 @@
     <n v="30"/>
     <n v="32"/>
     <x v="6"/>
+    <s v="30~32萬元/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <x v="19"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29760,8 +31874,8 @@
     <n v="0.33"/>
     <n v="0.33"/>
     <s v="2棟，376戶住家，9戶店面"/>
-    <x v="32"/>
-    <x v="14"/>
+    <n v="376"/>
+    <n v="9"/>
     <n v="0.36220000000000002"/>
     <n v="0.36220000000000002"/>
     <s v="地上22層，地下4層"/>
@@ -29783,7 +31897,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="410"/>
+    <x v="34"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="34"/>
     <s v="410 新未來3"/>
@@ -29793,6 +31907,11 @@
     <n v="33"/>
     <n v="38"/>
     <x v="13"/>
+    <s v="33~38萬元/坪"/>
+    <n v="33"/>
+    <n v="38"/>
+    <x v="21"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29819,8 +31938,8 @@
     <n v="0.3327"/>
     <n v="0.3327"/>
     <s v="2幢，3棟，582戶住家，16戶店面"/>
-    <x v="33"/>
-    <x v="15"/>
+    <n v="582"/>
+    <n v="16"/>
     <n v="0.38300000000000001"/>
     <n v="0.38300000000000001"/>
     <s v="地上19、22層，地下5層"/>
@@ -29842,7 +31961,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="411"/>
+    <x v="35"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="35"/>
     <s v="411 和洲金剛"/>
@@ -29852,6 +31971,11 @@
     <n v="25"/>
     <n v="27"/>
     <x v="1"/>
+    <s v="30~32 萬/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <x v="19"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29878,8 +32002,8 @@
     <s v="32%"/>
     <n v="0.32"/>
     <s v="3幢，3棟，210戶住家，11戶店面"/>
-    <x v="34"/>
-    <x v="1"/>
+    <n v="210"/>
+    <n v="11"/>
     <s v="45.54%"/>
     <n v="0.45540000000000003"/>
     <s v="地上15層，地下3~4層"/>
@@ -29901,7 +32025,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="412"/>
+    <x v="36"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="36"/>
     <s v="412 君邑丘比特"/>
@@ -29911,6 +32035,11 @@
     <n v="27.8"/>
     <n v="32"/>
     <x v="14"/>
+    <s v="29.8~38.2 萬/坪"/>
+    <n v="29.8"/>
+    <n v="38.200000000000003"/>
+    <x v="22"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29937,8 +32066,8 @@
     <s v="32.46~33.79%"/>
     <n v="0.33129999999999998"/>
     <s v="1幢，4棟，173戶住家，5戶店面"/>
-    <x v="3"/>
-    <x v="8"/>
+    <n v="173"/>
+    <n v="5"/>
     <n v="0.46150000000000002"/>
     <n v="0.46150000000000002"/>
     <s v="地上15層，地下4層"/>
@@ -29960,7 +32089,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="413"/>
+    <x v="37"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="37"/>
     <s v="413 頤昌璞岳"/>
@@ -29970,6 +32099,11 @@
     <n v="32"/>
     <n v="33"/>
     <x v="5"/>
+    <s v="32~33 萬/坪"/>
+    <n v="32"/>
+    <n v="33"/>
+    <x v="23"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -29996,8 +32130,8 @@
     <n v="0.32100000000000001"/>
     <n v="0.32100000000000001"/>
     <s v="1幢，2棟，124戶住家，11戶店面"/>
-    <x v="35"/>
-    <x v="1"/>
+    <n v="124"/>
+    <n v="11"/>
     <n v="0.51349999999999996"/>
     <n v="0.51349999999999996"/>
     <s v="地上14層，地下4層"/>
@@ -30019,7 +32153,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="414"/>
+    <x v="38"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="38"/>
     <s v="414 合謙學"/>
@@ -30029,6 +32163,11 @@
     <n v="32"/>
     <n v="35"/>
     <x v="15"/>
+    <s v="35~42 萬/坪"/>
+    <n v="35"/>
+    <n v="42"/>
+    <x v="24"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -30055,8 +32194,8 @@
     <n v="0.32500000000000001"/>
     <n v="0.32500000000000001"/>
     <s v="1幢，2棟，106戶住家"/>
-    <x v="36"/>
-    <x v="5"/>
+    <n v="106"/>
+    <n v="0"/>
     <n v="0.45660000000000001"/>
     <n v="0.45660000000000001"/>
     <s v="地上14層，地下4層"/>
@@ -30078,7 +32217,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="415"/>
+    <x v="39"/>
     <s v="4.中心商業區及文青國中小生活圈"/>
     <x v="39"/>
     <s v="415 大亮時代A7"/>
@@ -30088,6 +32227,11 @@
     <n v="35"/>
     <n v="36"/>
     <x v="13"/>
+    <s v="35~36 萬/坪"/>
+    <n v="35"/>
+    <n v="36"/>
+    <x v="21"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -30114,8 +32258,8 @@
     <n v="0.33900000000000002"/>
     <n v="0.33900000000000002"/>
     <s v="1幢，1棟，87戶一般事務所，3戶店面，45戶住家"/>
-    <x v="37"/>
-    <x v="10"/>
+    <n v="87"/>
+    <n v="3"/>
     <n v="0.50270000000000004"/>
     <n v="0.50270000000000004"/>
     <s v="地上15層，地下4層"/>
@@ -30137,7 +32281,7 @@
     <x v="1"/>
   </r>
   <r>
-    <s v="501"/>
+    <x v="40"/>
     <s v="5.合宜住宅區"/>
     <x v="40"/>
     <s v="501 新未來1"/>
@@ -30147,6 +32291,11 @@
     <n v="33"/>
     <n v="38"/>
     <x v="13"/>
+    <s v="33~38萬元/坪"/>
+    <n v="33"/>
+    <n v="38"/>
+    <x v="21"/>
+    <x v="1"/>
     <s v="A7 遠雄新未來1 幸福住戶討論區"/>
     <s v="https://www.facebook.com/groups/254570162464632"/>
     <m/>
@@ -30173,8 +32322,8 @@
     <n v="0.33"/>
     <n v="0.33"/>
     <s v="3棟，807戶住家，14戶店面，3個商場"/>
-    <x v="38"/>
-    <x v="16"/>
+    <n v="807"/>
+    <n v="14"/>
     <n v="0.57020000000000004"/>
     <n v="0.57020000000000004"/>
     <s v="地上28層，地下5層"/>
@@ -30196,7 +32345,7 @@
     <x v="3"/>
   </r>
   <r>
-    <s v="502"/>
+    <x v="41"/>
     <s v="5.合宜住宅區"/>
     <x v="41"/>
     <s v="502 富宇天匯"/>
@@ -30206,6 +32355,11 @@
     <n v="39"/>
     <n v="43"/>
     <x v="16"/>
+    <s v="45~50 萬/坪"/>
+    <n v="45"/>
+    <n v="50"/>
+    <x v="25"/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -30232,8 +32386,8 @@
     <n v="0.33500000000000002"/>
     <n v="0.33500000000000002"/>
     <s v="2幢，4棟，266戶住家，4戶店面"/>
-    <x v="16"/>
-    <x v="9"/>
+    <n v="266"/>
+    <n v="4"/>
     <n v="0.49540000000000001"/>
     <n v="0.49540000000000001"/>
     <s v="地上15層，地下4層"/>
@@ -30255,7 +32409,7 @@
     <x v="3"/>
   </r>
   <r>
-    <s v="503"/>
+    <x v="42"/>
     <s v="5.合宜住宅區"/>
     <x v="42"/>
     <s v="503 竹城明治"/>
@@ -30265,6 +32419,11 @@
     <n v="28"/>
     <n v="30"/>
     <x v="17"/>
+    <s v="28~30萬元/坪"/>
+    <n v="28"/>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -30291,8 +32450,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="1幢，6棟，168戶住家，5戶店面"/>
-    <x v="39"/>
-    <x v="8"/>
+    <n v="168"/>
+    <n v="5"/>
     <s v="45.56%"/>
     <n v="0.4556"/>
     <s v="地上13層，地下3層"/>
@@ -30314,7 +32473,7 @@
     <x v="3"/>
   </r>
   <r>
-    <s v="504"/>
+    <x v="43"/>
     <s v="5.合宜住宅區"/>
     <x v="43"/>
     <s v="504 竹城宇治"/>
@@ -30324,6 +32483,11 @@
     <n v="30"/>
     <n v="30"/>
     <x v="10"/>
+    <s v="30 萬/坪 "/>
+    <n v="30"/>
+    <n v="30"/>
+    <x v="20"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -30350,8 +32514,8 @@
     <n v="0.315"/>
     <n v="0.315"/>
     <s v="3棟，103戶住家，6戶店面"/>
-    <x v="40"/>
-    <x v="17"/>
+    <n v="103"/>
+    <n v="6"/>
     <n v="0.45700000000000002"/>
     <n v="0.45700000000000002"/>
     <s v="地上13層，地下3層"/>
@@ -30373,7 +32537,7 @@
     <x v="3"/>
   </r>
   <r>
-    <s v="505"/>
+    <x v="44"/>
     <s v="5.合宜住宅區"/>
     <x v="44"/>
     <s v="505 櫻花澍"/>
@@ -30383,6 +32547,11 @@
     <n v="28"/>
     <n v="32"/>
     <x v="10"/>
+    <s v="28~32 萬/坪"/>
+    <n v="28"/>
+    <n v="32"/>
+    <x v="20"/>
+    <x v="1"/>
     <s v="A7櫻花澍已購戶討論區"/>
     <s v="https://www.facebook.com/groups/1271297159886163"/>
     <m/>
@@ -30409,8 +32578,8 @@
     <n v="0.32"/>
     <n v="0.32"/>
     <s v="1幢，2棟，106戶住家，2戶店面"/>
-    <x v="36"/>
-    <x v="6"/>
+    <n v="106"/>
+    <n v="2"/>
     <n v="0.38140000000000002"/>
     <n v="0.38140000000000002"/>
     <s v="地上14層，地下4層"/>
@@ -30432,7 +32601,7 @@
     <x v="3"/>
   </r>
   <r>
-    <s v="506"/>
+    <x v="45"/>
     <s v="5.合宜住宅區"/>
     <x v="45"/>
     <s v="506 遠雄文青"/>
@@ -30442,6 +32611,11 @@
     <n v="15"/>
     <n v="15"/>
     <x v="18"/>
+    <s v="2021/8:22.7萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <x v="26"/>
+    <x v="1"/>
     <s v="A7 遠雄文青 住戶討論區"/>
     <s v="https://www.facebook.com/groups/675455015969962"/>
     <m/>
@@ -30468,8 +32642,8 @@
     <m/>
     <m/>
     <m/>
-    <x v="41"/>
-    <x v="18"/>
+    <n v="1272"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -30491,7 +32665,7 @@
     <x v="3"/>
   </r>
   <r>
-    <s v="507"/>
+    <x v="46"/>
     <s v="5.合宜住宅區"/>
     <x v="46"/>
     <s v="507 皇翔歡喜城"/>
@@ -30501,6 +32675,11 @@
     <n v="15"/>
     <n v="15"/>
     <x v="18"/>
+    <s v="2021/8:20.0萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <x v="26"/>
+    <x v="1"/>
     <s v="A7皇翔歡喜城"/>
     <s v="https://www.facebook.com/groups/521969711190884"/>
     <m/>
@@ -30527,8 +32706,8 @@
     <m/>
     <m/>
     <m/>
-    <x v="42"/>
-    <x v="18"/>
+    <n v="1780"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -30550,7 +32729,7 @@
     <x v="3"/>
   </r>
   <r>
-    <s v="508"/>
+    <x v="47"/>
     <s v="5.合宜住宅區"/>
     <x v="47"/>
     <s v="508 名軒快樂家"/>
@@ -30560,6 +32739,11 @@
     <n v="15"/>
     <n v="15"/>
     <x v="18"/>
+    <s v="2021/8:21.7萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <x v="26"/>
+    <x v="1"/>
     <s v="名軒快樂家-住戶專區"/>
     <s v="https://www.facebook.com/groups/671624019658641"/>
     <m/>
@@ -30586,8 +32770,8 @@
     <m/>
     <m/>
     <m/>
-    <x v="43"/>
-    <x v="18"/>
+    <n v="514"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -30609,7 +32793,7 @@
     <x v="3"/>
   </r>
   <r>
-    <s v="509"/>
+    <x v="48"/>
     <s v="5.合宜住宅區"/>
     <x v="48"/>
     <s v="509 麗寶快樂家"/>
@@ -30619,6 +32803,11 @@
     <n v="15"/>
     <n v="15"/>
     <x v="18"/>
+    <s v="2021/8:21.0萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <x v="26"/>
+    <x v="1"/>
     <s v="A7 麗寶快樂家社區~住戶專區"/>
     <s v="https://www.facebook.com/groups/A7happyhome"/>
     <m/>
@@ -30645,8 +32834,8 @@
     <m/>
     <m/>
     <m/>
-    <x v="44"/>
-    <x v="18"/>
+    <n v="897"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -30683,6 +32872,11 @@
     <x v="0"/>
     <n v="29"/>
     <x v="0"/>
+    <s v="34~36 萬/坪"/>
+    <n v="34"/>
+    <n v="36"/>
+    <n v="35"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -30741,6 +32935,11 @@
     <x v="1"/>
     <n v="26"/>
     <x v="1"/>
+    <s v="29萬元/坪"/>
+    <n v="29"/>
+    <n v="29"/>
+    <n v="29"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -30799,6 +32998,11 @@
     <x v="1"/>
     <n v="26"/>
     <x v="1"/>
+    <s v="26萬元/坪"/>
+    <n v="26"/>
+    <n v="26"/>
+    <n v="26"/>
+    <s v="Y"/>
     <s v="樂捷市好鄰居"/>
     <s v="https://www.facebook.com/groups/324107612343329"/>
     <m/>
@@ -30857,6 +33061,11 @@
     <x v="2"/>
     <n v="25.5"/>
     <x v="2"/>
+    <s v="24.5~25.5萬元/坪"/>
+    <n v="24.5"/>
+    <n v="25.5"/>
+    <n v="25"/>
+    <s v="Y"/>
     <s v="龜山A7-奇幻莊園住戶"/>
     <s v="https://www.facebook.com/groups/588376114975687"/>
     <m/>
@@ -30915,6 +33124,11 @@
     <x v="3"/>
     <n v="26"/>
     <x v="3"/>
+    <s v="25~26 萬/坪"/>
+    <n v="26"/>
+    <n v="26"/>
+    <n v="26"/>
+    <s v="Y"/>
     <m/>
     <m/>
     <m/>
@@ -30973,6 +33187,11 @@
     <x v="1"/>
     <n v="28"/>
     <x v="4"/>
+    <s v="26~28萬元/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <n v="27"/>
+    <s v="Y"/>
     <m/>
     <m/>
     <m/>
@@ -31031,6 +33250,11 @@
     <x v="3"/>
     <n v="26"/>
     <x v="3"/>
+    <s v="27~29 萬/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="28"/>
+    <m/>
     <s v="台北國際村住戶交流園區_林口A7"/>
     <s v="https://www.facebook.com/groups/2397202740545114"/>
     <m/>
@@ -31089,6 +33313,11 @@
     <x v="4"/>
     <n v="35"/>
     <x v="5"/>
+    <s v="44~49 萬/坪"/>
+    <n v="44"/>
+    <n v="49"/>
+    <n v="46.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -31147,6 +33376,11 @@
     <x v="0"/>
     <n v="29"/>
     <x v="0"/>
+    <s v="35~37 萬/坪"/>
+    <n v="35"/>
+    <n v="37"/>
+    <n v="36"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -31205,6 +33439,11 @@
     <x v="1"/>
     <n v="28"/>
     <x v="4"/>
+    <s v="26~28萬元/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <n v="27"/>
+    <s v="Y"/>
     <m/>
     <m/>
     <m/>
@@ -31263,6 +33502,11 @@
     <x v="3"/>
     <n v="26"/>
     <x v="3"/>
+    <s v="27~28 萬/坪"/>
+    <n v="27"/>
+    <n v="28"/>
+    <n v="27.5"/>
+    <m/>
     <s v="A7皇普MVP屋主交流團"/>
     <s v="https://www.facebook.com/groups/800873736965340"/>
     <m/>
@@ -31321,6 +33565,11 @@
     <x v="4"/>
     <n v="32"/>
     <x v="6"/>
+    <s v="38~42 萬/坪"/>
+    <n v="38"/>
+    <n v="42"/>
+    <n v="40"/>
+    <m/>
     <s v="富宇敦峰住戶社團"/>
     <s v="https://www.facebook.com/groups/124542338433380"/>
     <m/>
@@ -31379,6 +33628,11 @@
     <x v="5"/>
     <n v="29"/>
     <x v="7"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="28"/>
+    <s v="Y"/>
     <m/>
     <m/>
     <m/>
@@ -31437,6 +33691,11 @@
     <x v="0"/>
     <n v="33"/>
     <x v="8"/>
+    <s v="35~40 萬/坪"/>
+    <n v="35"/>
+    <n v="40"/>
+    <n v="37.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -31495,6 +33754,11 @@
     <x v="6"/>
     <n v="38"/>
     <x v="9"/>
+    <s v="38~43 萬/坪"/>
+    <n v="38"/>
+    <n v="43"/>
+    <n v="40.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -31553,6 +33817,11 @@
     <x v="5"/>
     <n v="29"/>
     <x v="7"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="28"/>
+    <s v="Y"/>
     <m/>
     <m/>
     <m/>
@@ -31611,6 +33880,11 @@
     <x v="1"/>
     <n v="28"/>
     <x v="4"/>
+    <s v="33~36 萬/坪"/>
+    <n v="33"/>
+    <n v="36"/>
+    <n v="34.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -31669,6 +33943,11 @@
     <x v="5"/>
     <n v="29"/>
     <x v="7"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="28"/>
+    <s v="Y"/>
     <s v="新潤翡麗住戶天地"/>
     <s v="https://www.facebook.com/groups/321511928734593"/>
     <m/>
@@ -31727,6 +34006,11 @@
     <x v="7"/>
     <n v="26"/>
     <x v="2"/>
+    <s v="26~28 萬/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <n v="27"/>
+    <m/>
     <s v="根津苑"/>
     <s v="https://www.facebook.com/%E6%A0%B9%E6%B4%A5%E8%8B%91-102597158541363"/>
     <m/>
@@ -31785,6 +34069,11 @@
     <x v="1"/>
     <n v="30"/>
     <x v="7"/>
+    <s v="26~30萬元/坪"/>
+    <n v="26"/>
+    <n v="30"/>
+    <n v="28"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -31843,6 +34132,11 @@
     <x v="0"/>
     <n v="32"/>
     <x v="10"/>
+    <s v="34~36 萬/坪"/>
+    <n v="34"/>
+    <n v="36"/>
+    <n v="35"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -31901,6 +34195,11 @@
     <x v="7"/>
     <n v="26"/>
     <x v="2"/>
+    <s v="24~26萬元/坪"/>
+    <n v="24"/>
+    <n v="26"/>
+    <n v="25"/>
+    <s v="Y"/>
     <m/>
     <m/>
     <m/>
@@ -31959,6 +34258,11 @@
     <x v="4"/>
     <n v="31"/>
     <x v="8"/>
+    <s v="28萬元/坪"/>
+    <n v="28"/>
+    <n v="28"/>
+    <n v="28"/>
+    <m/>
     <s v="友文化"/>
     <s v="https://www.facebook.com/groups/710305099774047"/>
     <m/>
@@ -32017,6 +34321,11 @@
     <x v="8"/>
     <n v="31"/>
     <x v="10"/>
+    <s v="34~39 萬/坪"/>
+    <n v="34"/>
+    <n v="39"/>
+    <n v="36.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32075,6 +34384,11 @@
     <x v="5"/>
     <n v="27"/>
     <x v="4"/>
+    <s v="32~34 萬/坪"/>
+    <n v="32"/>
+    <n v="34"/>
+    <n v="33"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32133,6 +34447,11 @@
     <x v="1"/>
     <n v="28"/>
     <x v="4"/>
+    <s v="38~41 萬/坪"/>
+    <n v="38"/>
+    <n v="41"/>
+    <n v="39.5"/>
+    <m/>
     <s v="竹城甲子園住戶交流區"/>
     <s v="https://www.facebook.com/groups/1127911624065990"/>
     <m/>
@@ -32191,6 +34510,11 @@
     <x v="9"/>
     <n v="30.5"/>
     <x v="8"/>
+    <s v="30.5萬元/坪"/>
+    <n v="30.5"/>
+    <n v="30.5"/>
+    <n v="30.5"/>
+    <m/>
     <s v="金捷市準鄰居交流園地"/>
     <s v="https://www.facebook.com/groups/238626460426128"/>
     <m/>
@@ -32249,6 +34573,11 @@
     <x v="6"/>
     <n v="38"/>
     <x v="9"/>
+    <s v="45~48 萬/坪"/>
+    <n v="45"/>
+    <n v="48"/>
+    <n v="46.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32307,6 +34636,11 @@
     <x v="5"/>
     <n v="32"/>
     <x v="11"/>
+    <s v="24~25 萬/坪"/>
+    <n v="24"/>
+    <n v="25"/>
+    <n v="24.5"/>
+    <s v="Y"/>
     <m/>
     <m/>
     <m/>
@@ -32365,6 +34699,11 @@
     <x v="10"/>
     <n v="33"/>
     <x v="12"/>
+    <s v="32~35 萬/坪"/>
+    <n v="32"/>
+    <n v="35"/>
+    <n v="33.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32423,6 +34762,11 @@
     <x v="5"/>
     <n v="29"/>
     <x v="7"/>
+    <s v="30~32 萬/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <n v="31"/>
+    <m/>
     <s v="A7 富御捷境好鄰居交流團"/>
     <s v="https://www.facebook.com/groups/1970564956581068"/>
     <m/>
@@ -32481,6 +34825,11 @@
     <x v="11"/>
     <n v="38"/>
     <x v="13"/>
+    <s v="44~49 萬/坪"/>
+    <n v="44"/>
+    <n v="49"/>
+    <n v="46.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32539,6 +34888,11 @@
     <x v="4"/>
     <n v="30"/>
     <x v="10"/>
+    <s v="30萬元/坪"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="30"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32597,6 +34951,11 @@
     <x v="4"/>
     <n v="32"/>
     <x v="6"/>
+    <s v="30~32萬元/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <n v="31"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32655,6 +35014,11 @@
     <x v="11"/>
     <n v="38"/>
     <x v="13"/>
+    <s v="33~38萬元/坪"/>
+    <n v="33"/>
+    <n v="38"/>
+    <n v="35.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32713,6 +35077,11 @@
     <x v="3"/>
     <n v="27"/>
     <x v="1"/>
+    <s v="30~32 萬/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <n v="31"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32771,6 +35140,11 @@
     <x v="12"/>
     <n v="32"/>
     <x v="14"/>
+    <s v="29.8~38.2 萬/坪"/>
+    <n v="29.8"/>
+    <n v="38.200000000000003"/>
+    <n v="34"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32829,6 +35203,11 @@
     <x v="13"/>
     <n v="33"/>
     <x v="5"/>
+    <s v="32~33 萬/坪"/>
+    <n v="32"/>
+    <n v="33"/>
+    <n v="32.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32887,6 +35266,11 @@
     <x v="13"/>
     <n v="35"/>
     <x v="15"/>
+    <s v="35~42 萬/坪"/>
+    <n v="35"/>
+    <n v="42"/>
+    <n v="38.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -32945,6 +35329,11 @@
     <x v="6"/>
     <n v="36"/>
     <x v="13"/>
+    <s v="35~36 萬/坪"/>
+    <n v="35"/>
+    <n v="36"/>
+    <n v="35.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -33003,6 +35392,11 @@
     <x v="11"/>
     <n v="38"/>
     <x v="13"/>
+    <s v="33~38萬元/坪"/>
+    <n v="33"/>
+    <n v="38"/>
+    <n v="35.5"/>
+    <s v="Y"/>
     <s v="A7 遠雄新未來1 幸福住戶討論區"/>
     <s v="https://www.facebook.com/groups/254570162464632"/>
     <m/>
@@ -33061,6 +35455,11 @@
     <x v="14"/>
     <n v="43"/>
     <x v="16"/>
+    <s v="45~50 萬/坪"/>
+    <n v="45"/>
+    <n v="50"/>
+    <n v="47.5"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -33119,6 +35518,11 @@
     <x v="0"/>
     <n v="30"/>
     <x v="17"/>
+    <s v="28~30萬元/坪"/>
+    <n v="28"/>
+    <n v="30"/>
+    <n v="29"/>
+    <s v="Y"/>
     <m/>
     <m/>
     <m/>
@@ -33177,6 +35581,11 @@
     <x v="4"/>
     <n v="30"/>
     <x v="10"/>
+    <s v="30 萬/坪 "/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="30"/>
+    <s v="Y"/>
     <m/>
     <m/>
     <m/>
@@ -33235,6 +35644,11 @@
     <x v="0"/>
     <n v="32"/>
     <x v="10"/>
+    <s v="28~32 萬/坪"/>
+    <n v="28"/>
+    <n v="32"/>
+    <n v="30"/>
+    <s v="Y"/>
     <s v="A7櫻花澍已購戶討論區"/>
     <s v="https://www.facebook.com/groups/1271297159886163"/>
     <m/>
@@ -33293,6 +35707,11 @@
     <x v="15"/>
     <n v="15"/>
     <x v="18"/>
+    <s v="2021/8:22.7萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="15"/>
+    <s v="Y"/>
     <s v="A7 遠雄文青 住戶討論區"/>
     <s v="https://www.facebook.com/groups/675455015969962"/>
     <m/>
@@ -33351,6 +35770,11 @@
     <x v="15"/>
     <n v="15"/>
     <x v="18"/>
+    <s v="2021/8:20.0萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="15"/>
+    <s v="Y"/>
     <s v="A7皇翔歡喜城"/>
     <s v="https://www.facebook.com/groups/521969711190884"/>
     <m/>
@@ -33409,6 +35833,11 @@
     <x v="15"/>
     <n v="15"/>
     <x v="18"/>
+    <s v="2021/8:21.7萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="15"/>
+    <s v="Y"/>
     <s v="名軒快樂家-住戶專區"/>
     <s v="https://www.facebook.com/groups/671624019658641"/>
     <m/>
@@ -33467,6 +35896,11 @@
     <x v="15"/>
     <n v="15"/>
     <x v="18"/>
+    <s v="2021/8:21.0萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="15"/>
+    <s v="Y"/>
     <s v="A7 麗寶快樂家社區~住戶專區"/>
     <s v="https://www.facebook.com/groups/A7happyhome"/>
     <m/>
@@ -33518,9 +35952,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A3CA2B-B6E6-A64B-BB28-39916B3C266F}" name="樞紐分析表1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A3CA2B-B6E6-A64B-BB28-39916B3C266F}" name="樞紐分析表1" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:C53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="56">
+  <pivotFields count="61">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0" sortType="descending">
@@ -33595,6 +36029,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -33857,11 +36296,11 @@
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="36" hier="-1"/>
+    <pageField fld="41" hier="-1"/>
   </pageFields>
   <dataFields count="2">
-    <dataField name="加總 - 住家戶數" fld="36" baseField="0" baseItem="0"/>
-    <dataField name="加總 - 商店戶數" fld="37" baseField="0" baseItem="0"/>
+    <dataField name="加總 - 住家戶數" fld="41" baseField="0" baseItem="0"/>
+    <dataField name="加總 - 商店戶數" fld="42" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="2">
     <chartFormat chart="2" format="2" series="1">
@@ -33907,9 +36346,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F52A0184-F9FB-7249-BCA8-2F8B6C3580F3}" name="樞紐分析表1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F52A0184-F9FB-7249-BCA8-2F8B6C3580F3}" name="樞紐分析表1" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="56">
+  <pivotFields count="61">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
@@ -33930,6 +36369,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -34011,8 +36455,8 @@
     </i>
   </colItems>
   <dataFields count="2">
-    <dataField name="加總 - 住家戶數" fld="36" baseField="0" baseItem="0" numFmtId="180"/>
-    <dataField name="加總 - 商店戶數" fld="37" baseField="0" baseItem="0"/>
+    <dataField name="加總 - 住家戶數" fld="41" baseField="0" baseItem="0" numFmtId="180"/>
+    <dataField name="加總 - 商店戶數" fld="42" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="43">
     <chartFormat chart="0" format="1" series="1">
@@ -34521,20 +36965,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A05ECE1-698D-3F42-A1F5-015F41A70879}" name="樞紐分析表2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A37:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="56">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7019A1B8-C948-9248-8ABA-BFD05B6AA01A}" name="樞紐分析表1" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="61">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -34566,6 +37001,173 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="55"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="9" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="181"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A05ECE1-698D-3F42-A1F5-015F41A70879}" name="樞紐分析表2" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A37:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="61">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" numFmtId="177" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="20">
+        <item h="1" x="18"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -34704,158 +37306,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7019A1B8-C948-9248-8ABA-BFD05B6AA01A}" name="樞紐分析表1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="56">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField axis="axisPage" dataField="1" numFmtId="177" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="20">
-        <item h="1" x="18"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="17"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="12"/>
-        <item x="5"/>
-        <item x="15"/>
-        <item x="13"/>
-        <item x="9"/>
-        <item x="16"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="50"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="9" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="181"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{458FE396-6E8A-064D-96E2-0847BBE52133}" name="樞紐分析表7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="3ㄒㄧ1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{458FE396-6E8A-064D-96E2-0847BBE52133}" name="樞紐分析表7" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="3ㄒㄧ1">
   <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="57">
+  <pivotFields count="62">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -34866,6 +37320,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -34923,7 +37382,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="56"/>
+    <field x="61"/>
   </rowFields>
   <rowItems count="5">
     <i>
@@ -34957,8 +37416,8 @@
     </i>
   </colItems>
   <dataFields count="3">
-    <dataField name="加總 - 住家戶數" fld="36" baseField="0" baseItem="0" numFmtId="180"/>
-    <dataField name="加總 - 商店戶數" fld="37" baseField="0" baseItem="0" numFmtId="180"/>
+    <dataField name="加總 - 住家戶數" fld="41" baseField="0" baseItem="0" numFmtId="180"/>
+    <dataField name="加總 - 商店戶數" fld="42" baseField="0" baseItem="0" numFmtId="180"/>
     <dataField name="計數 - no" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -34974,9 +37433,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B833B209-0CFF-0548-B5A9-F2903FE4CB01}" name="樞紐分析表1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B833B209-0CFF-0548-B5A9-F2903FE4CB01}" name="樞紐分析表1" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="57">
+  <pivotFields count="62">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -35041,6 +37500,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -35098,7 +37562,7 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="50"/>
+    <field x="55"/>
   </rowFields>
   <rowItems count="6">
     <i>
@@ -35127,7 +37591,7 @@
     <pageField fld="2" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="平均值 - 車位分配率" fld="45" subtotal="average" baseField="0" baseItem="0" numFmtId="178"/>
+    <dataField name="平均值 - 車位分配率" fld="50" subtotal="average" baseField="0" baseItem="0" numFmtId="178"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">
@@ -35153,12 +37617,65 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8299DB4-79E1-2840-954E-122EFC07C81F}" name="樞紐分析表3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="B86:C118" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="57">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7C0AAB9-C4B2-6E4F-822E-42DD3E7664C6}" name="樞紐分析表1" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:C66" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="62">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="50">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
       <items count="50">
         <item x="39"/>
         <item x="14"/>
@@ -35211,15 +37728,392 @@
         <item x="44"/>
         <item t="default"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="63">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i r="1">
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i r="1">
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i r="1">
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="14" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="平均值 - 每坪價2022-平均" fld="13" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="41"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="26"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EAAEFCC-9164-E944-82C8-7A061A3EB16F}" name="樞紐分析表2" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B76:D108" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="62">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="50">
+        <item x="39"/>
+        <item x="14"/>
+        <item x="22"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="38"/>
+        <item x="47"/>
+        <item x="25"/>
+        <item x="43"/>
+        <item x="42"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="46"/>
+        <item x="18"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="31"/>
+        <item x="20"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="19"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="40"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="45"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="37"/>
+        <item x="32"/>
+        <item x="1"/>
+        <item x="27"/>
+        <item x="48"/>
+        <item x="9"/>
+        <item x="44"/>
+        <item t="default"/>
+      </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -35252,91 +38146,67 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="31">
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0">
+      <items count="28">
+        <item x="26"/>
+        <item x="17"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="20"/>
+        <item x="16"/>
+        <item x="19"/>
+        <item x="23"/>
+        <item x="14"/>
+        <item x="18"/>
+        <item x="22"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="21"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="10"/>
+        <item x="24"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="6"/>
         <item x="25"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="5"/>
-        <item x="15"/>
-        <item x="24"/>
-        <item x="28"/>
-        <item x="16"/>
-        <item x="23"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="22"/>
-        <item x="19"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item x="27"/>
-        <item x="4"/>
-        <item x="17"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="21"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="1"/>
-        <item x="29"/>
-        <item x="26"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="20">
-        <item h="1" x="14"/>
-        <item h="1" x="4"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="13"/>
-        <item h="1" x="17"/>
-        <item h="1" x="8"/>
-        <item h="1" x="12"/>
-        <item h="1" x="5"/>
-        <item h="1" x="16"/>
-        <item h="1" x="1"/>
-        <item h="1" x="9"/>
-        <item h="1" x="6"/>
-        <item h="1" x="11"/>
-        <item h="1" x="7"/>
-        <item h="1" x="10"/>
-        <item h="1" x="18"/>
-        <item x="0"/>
-        <item h="1" x="15"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -35365,137 +38235,125 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="2">
-    <field x="28"/>
+  <rowFields count="1">
     <field x="2"/>
   </rowFields>
   <rowItems count="32">
     <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
       <x v="26"/>
-    </i>
-    <i r="1">
-      <x v="33"/>
     </i>
     <i>
       <x v="27"/>
     </i>
-    <i r="1">
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
       <x v="45"/>
-    </i>
-    <i r="1">
-      <x v="21"/>
-    </i>
-    <i r="1">
-      <x v="44"/>
-    </i>
-    <i r="1">
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i r="1">
-      <x v="18"/>
-    </i>
-    <i r="1">
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i r="1">
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i r="1">
-      <x v="17"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i r="1">
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="40"/>
-    </i>
-    <i r="1">
-      <x v="19"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="29" hier="-1"/>
+    <pageField fld="14" hier="-1"/>
   </pageFields>
-  <dataFields count="1">
-    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="179"/>
+  <dataFields count="2">
+    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="平均值 - 每坪價2022-平均" fld="13" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -35508,10 +38366,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4D14CAE-2C58-9D43-B1F7-B8BBC66C68B5}" name="樞紐分析表2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4D14CAE-2C58-9D43-B1F7-B8BBC66C68B5}" name="樞紐分析表2" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="B48:D64" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="57">
+  <pivotFields count="62">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -35545,6 +38403,11 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -35603,80 +38466,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="46">
-        <item x="37"/>
-        <item x="40"/>
-        <item x="36"/>
-        <item x="20"/>
-        <item x="35"/>
-        <item x="12"/>
-        <item x="31"/>
-        <item x="39"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="22"/>
-        <item x="34"/>
-        <item x="17"/>
-        <item x="14"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="16"/>
-        <item x="0"/>
-        <item x="21"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item x="32"/>
-        <item x="15"/>
-        <item x="11"/>
-        <item x="23"/>
-        <item x="30"/>
-        <item x="43"/>
-        <item x="13"/>
-        <item x="33"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="18"/>
-        <item x="38"/>
-        <item x="7"/>
-        <item x="44"/>
-        <item x="8"/>
-        <item x="24"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="20">
-        <item x="5"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="17"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="14"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="16"/>
-        <item x="15"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="11"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -35698,7 +38489,7 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="29"/>
+    <field x="34"/>
   </rowFields>
   <rowItems count="16">
     <i>
@@ -35765,8 +38556,8 @@
     <pageField fld="9" hier="-1"/>
   </pageFields>
   <dataFields count="2">
-    <dataField name="加總 - 住家戶數" fld="36" baseField="0" baseItem="0" numFmtId="180"/>
-    <dataField name="加總 - 商店戶數" fld="37" baseField="0" baseItem="0" numFmtId="180"/>
+    <dataField name="加總 - 住家戶數" fld="41" baseField="0" baseItem="0" numFmtId="180"/>
+    <dataField name="加總 - 商店戶數" fld="42" baseField="0" baseItem="0" numFmtId="180"/>
   </dataFields>
   <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
@@ -35836,10 +38627,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34FE811F-B077-FD42-9008-279DB01289D2}" name="樞紐分析表1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34FE811F-B077-FD42-9008-279DB01289D2}" name="樞紐分析表1" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="57">
+  <pivotFields count="62">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -35874,58 +38665,29 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="31">
-        <item x="25"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="5"/>
-        <item x="15"/>
-        <item x="24"/>
-        <item x="28"/>
-        <item x="16"/>
-        <item x="23"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="22"/>
-        <item x="19"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item x="27"/>
-        <item x="4"/>
-        <item x="17"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="21"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="1"/>
-        <item x="29"/>
-        <item x="26"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="20">
         <item x="14"/>
@@ -35988,7 +38750,7 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="29"/>
+    <field x="34"/>
   </rowFields>
   <rowItems count="16">
     <i>
@@ -36081,10 +38843,348 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8299DB4-79E1-2840-954E-122EFC07C81F}" name="樞紐分析表3" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="B86:C118" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="62">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="50">
+        <item x="39"/>
+        <item x="14"/>
+        <item x="22"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="38"/>
+        <item x="47"/>
+        <item x="25"/>
+        <item x="43"/>
+        <item x="42"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="46"/>
+        <item x="18"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="31"/>
+        <item x="20"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="19"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="40"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="45"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="37"/>
+        <item x="32"/>
+        <item x="1"/>
+        <item x="27"/>
+        <item x="48"/>
+        <item x="9"/>
+        <item x="44"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="31">
+        <item x="25"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="24"/>
+        <item x="28"/>
+        <item x="16"/>
+        <item x="23"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="22"/>
+        <item x="19"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="27"/>
+        <item x="4"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="1"/>
+        <item x="29"/>
+        <item x="26"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="20">
+        <item h="1" x="14"/>
+        <item h="1" x="4"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="13"/>
+        <item h="1" x="17"/>
+        <item h="1" x="8"/>
+        <item h="1" x="12"/>
+        <item h="1" x="5"/>
+        <item h="1" x="16"/>
+        <item h="1" x="1"/>
+        <item h="1" x="9"/>
+        <item h="1" x="6"/>
+        <item h="1" x="11"/>
+        <item h="1" x="7"/>
+        <item h="1" x="10"/>
+        <item h="1" x="18"/>
+        <item x="0"/>
+        <item h="1" x="15"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="33"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="32">
+    <i>
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="45"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+    </i>
+    <i r="1">
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="40"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="34" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - 每坪價-平均" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="179"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D90A3B06-44FC-DF47-95B9-374674E5983F}" name="樞紐分析表2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D90A3B06-44FC-DF47-95B9-374674E5983F}" name="樞紐分析表2" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:C49" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="56">
+  <pivotFields count="61">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0" sortType="descending">
@@ -36179,6 +39279,11 @@
     <pivotField dataField="1" numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -36442,9 +39547,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C48516-4469-E144-BC4C-C411D0731588}" name="樞紐分析表4" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C48516-4469-E144-BC4C-C411D0731588}" name="樞紐分析表4" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:C49" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="56">
+  <pivotFields count="61">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -36529,6 +39634,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -36733,8 +39843,8 @@
     <pageField fld="7" hier="-1"/>
   </pageFields>
   <dataFields count="2">
-    <dataField name="平均值 - 公設比例" fld="34" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
-    <dataField name="平均值 - 建蔽比率" fld="39" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
+    <dataField name="平均值 - 公設比例" fld="39" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
+    <dataField name="平均值 - 建蔽比率" fld="44" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="1">
     <format dxfId="1">
@@ -36781,9 +39891,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E3E605F-0935-CE47-93A7-EE637CD6D22D}" name="樞紐分析表3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E3E605F-0935-CE47-93A7-EE637CD6D22D}" name="樞紐分析表3" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B60" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="56">
+  <pivotFields count="61">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -36868,6 +39978,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -36932,7 +40047,7 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="2">
-    <field x="19"/>
+    <field x="24"/>
     <field x="3"/>
   </rowFields>
   <rowItems count="57">
@@ -37141,9 +40256,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCF300E8-2DA3-FD4D-8DB5-C4AF4C0B2B4D}" name="樞紐分析表5" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCF300E8-2DA3-FD4D-8DB5-C4AF4C0B2B4D}" name="樞紐分析表5" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="56">
+  <pivotFields count="61">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -37208,6 +40323,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -37291,7 +40411,7 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="2">
-    <field x="28"/>
+    <field x="33"/>
     <field x="3"/>
   </rowFields>
   <rowItems count="80">
@@ -37552,9 +40672,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{537918C9-6258-454A-9359-2B209B13DC90}" name="樞紐分析表6" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{537918C9-6258-454A-9359-2B209B13DC90}" name="樞紐分析表6" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="56">
+  <pivotFields count="61">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -37619,6 +40739,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -37859,10 +40984,10 @@
     <i/>
   </colItems>
   <pageFields count="1">
-    <pageField fld="48" hier="-1"/>
+    <pageField fld="53" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="加總 - 建築面積" fld="48" baseField="0" baseItem="0" numFmtId="179"/>
+    <dataField name="加總 - 建築面積" fld="53" baseField="0" baseItem="0" numFmtId="179"/>
   </dataFields>
   <formats count="1">
     <format dxfId="0">
@@ -37893,9 +41018,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A78E8CA-AA2E-4542-B594-47B469B1ECF7}" name="樞紐分析表7" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A78E8CA-AA2E-4542-B594-47B469B1ECF7}" name="樞紐分析表7" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="56">
+  <pivotFields count="61">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -37969,6 +41094,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -38177,10 +41307,10 @@
     <i/>
   </colItems>
   <pageFields count="1">
-    <pageField fld="41" hier="-1"/>
+    <pageField fld="46" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="加總 - 樓層數" fld="41" baseField="0" baseItem="0"/>
+    <dataField name="加總 - 樓層數" fld="46" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="1" series="1">
@@ -38206,9 +41336,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4AA391D-DCC2-A047-A23D-C8888E109D7F}" name="樞紐分析表8" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4AA391D-DCC2-A047-A23D-C8888E109D7F}" name="樞紐分析表8" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="56">
+  <pivotFields count="61">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -38282,6 +41412,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -38504,10 +41639,10 @@
     <i/>
   </colItems>
   <pageFields count="1">
-    <pageField fld="45" hier="-1"/>
+    <pageField fld="50" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="平均值 - 車位分配率" fld="45" subtotal="average" baseField="0" baseItem="0" numFmtId="178"/>
+    <dataField name="平均值 - 車位分配率" fld="50" subtotal="average" baseField="0" baseItem="0" numFmtId="178"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -38522,9 +41657,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E436F8BC-6E9C-CD4C-8D5F-9F959847D2E8}" name="樞紐分析表9" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E436F8BC-6E9C-CD4C-8D5F-9F959847D2E8}" name="樞紐分析表9" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="56">
+  <pivotFields count="61">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -38535,6 +41670,11 @@
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -38592,7 +41732,7 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="50"/>
+    <field x="55"/>
   </rowFields>
   <rowItems count="6">
     <i>
@@ -38636,7 +41776,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -38648,7 +41788,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="1"/>
           </reference>
         </references>
@@ -38660,7 +41800,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="2"/>
           </reference>
         </references>
@@ -38672,7 +41812,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="3"/>
           </reference>
         </references>
@@ -38684,7 +41824,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="4"/>
           </reference>
         </references>
@@ -38705,7 +41845,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -38717,7 +41857,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="1"/>
           </reference>
         </references>
@@ -38729,7 +41869,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="2"/>
           </reference>
         </references>
@@ -38741,7 +41881,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="3"/>
           </reference>
         </references>
@@ -38753,7 +41893,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="4"/>
           </reference>
         </references>
@@ -38774,7 +41914,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -38786,7 +41926,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="1"/>
           </reference>
         </references>
@@ -38798,7 +41938,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="2"/>
           </reference>
         </references>
@@ -38810,7 +41950,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="3"/>
           </reference>
         </references>
@@ -38822,7 +41962,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="4"/>
           </reference>
         </references>
@@ -38843,7 +41983,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -38855,7 +41995,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="1"/>
           </reference>
         </references>
@@ -38867,7 +42007,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="2"/>
           </reference>
         </references>
@@ -38879,7 +42019,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="3"/>
           </reference>
         </references>
@@ -38891,7 +42031,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="4"/>
           </reference>
         </references>
@@ -38912,7 +42052,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -38924,7 +42064,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="1"/>
           </reference>
         </references>
@@ -38936,7 +42076,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="2"/>
           </reference>
         </references>
@@ -38948,7 +42088,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="3"/>
           </reference>
         </references>
@@ -38960,7 +42100,7 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="50" count="1" selected="0">
+          <reference field="55" count="1" selected="0">
             <x v="4"/>
           </reference>
         </references>
@@ -40273,6 +43413,1247 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F839C698-B2FB-9645-B31D-4DB912AD364B}">
+  <dimension ref="A1:E109"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="16" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="16" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="17" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B4" s="18">
+        <v>28.5</v>
+      </c>
+      <c r="C4" s="18">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="21" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B5" s="18">
+        <v>28.5</v>
+      </c>
+      <c r="C5" s="18">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="17" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B6" s="18">
+        <v>26</v>
+      </c>
+      <c r="C6" s="18">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="18">
+        <v>26</v>
+      </c>
+      <c r="C7" s="18">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="18">
+        <v>25.5</v>
+      </c>
+      <c r="C8" s="18">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="21" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B9" s="18">
+        <v>25.5</v>
+      </c>
+      <c r="C9" s="18">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="17" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B10" s="18">
+        <v>32.5</v>
+      </c>
+      <c r="C10" s="18">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="18">
+        <v>32.5</v>
+      </c>
+      <c r="C11" s="18">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="17" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B12" s="18">
+        <v>28.5</v>
+      </c>
+      <c r="C12" s="18">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="18">
+        <v>28.5</v>
+      </c>
+      <c r="C13" s="18">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" s="18">
+        <v>25.5</v>
+      </c>
+      <c r="C14" s="18">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="21" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B15" s="18">
+        <v>25.5</v>
+      </c>
+      <c r="C15" s="18">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="17" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B16" s="18">
+        <v>31</v>
+      </c>
+      <c r="C16" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="B17" s="18">
+        <v>31</v>
+      </c>
+      <c r="C17" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="17" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B18" s="18">
+        <v>30.5</v>
+      </c>
+      <c r="C18" s="18">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="21" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B19" s="18">
+        <v>30.5</v>
+      </c>
+      <c r="C19" s="18">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="17" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B20" s="18">
+        <v>36.5</v>
+      </c>
+      <c r="C20" s="18">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="21" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B21" s="18">
+        <v>36.5</v>
+      </c>
+      <c r="C21" s="18">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="17" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B22" s="18">
+        <v>27</v>
+      </c>
+      <c r="C22" s="18">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="B23" s="18">
+        <v>27</v>
+      </c>
+      <c r="C23" s="18">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="17" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B24" s="18">
+        <v>25</v>
+      </c>
+      <c r="C24" s="18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="B25" s="18">
+        <v>25</v>
+      </c>
+      <c r="C25" s="18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="17" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B26" s="18">
+        <v>28</v>
+      </c>
+      <c r="C26" s="18">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="21" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B27" s="18">
+        <v>28</v>
+      </c>
+      <c r="C27" s="18">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="17" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B28" s="18">
+        <v>30</v>
+      </c>
+      <c r="C28" s="18">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="21" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B29" s="18">
+        <v>30</v>
+      </c>
+      <c r="C29" s="18">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="17" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B30" s="18">
+        <v>30.5</v>
+      </c>
+      <c r="C30" s="18">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="21" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B31" s="18">
+        <v>30.5</v>
+      </c>
+      <c r="C31" s="18">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B32" s="18">
+        <v>30</v>
+      </c>
+      <c r="C32" s="18">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="21" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B33" s="18">
+        <v>30</v>
+      </c>
+      <c r="C33" s="18">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="17" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B34" s="18">
+        <v>27</v>
+      </c>
+      <c r="C34" s="18">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="21" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B35" s="18">
+        <v>27</v>
+      </c>
+      <c r="C35" s="18">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="17" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B36" s="18">
+        <v>27</v>
+      </c>
+      <c r="C36" s="18">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="B37" s="18">
+        <v>27</v>
+      </c>
+      <c r="C37" s="18">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="17" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B38" s="18">
+        <v>30.5</v>
+      </c>
+      <c r="C38" s="18">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="B39" s="18">
+        <v>30.5</v>
+      </c>
+      <c r="C39" s="18">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="17" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B40" s="18">
+        <v>36.5</v>
+      </c>
+      <c r="C40" s="18">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="B41" s="18">
+        <v>36.5</v>
+      </c>
+      <c r="C41" s="18">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="17" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B42" s="18">
+        <v>32</v>
+      </c>
+      <c r="C42" s="18">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="21" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B43" s="18">
+        <v>32</v>
+      </c>
+      <c r="C43" s="18">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="17" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B44" s="18">
+        <v>28</v>
+      </c>
+      <c r="C44" s="18">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="B45" s="18">
+        <v>28</v>
+      </c>
+      <c r="C45" s="18">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="17" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B46" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="C46" s="18">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="21" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B47" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="C47" s="18">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="17" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B48" s="18">
+        <v>30</v>
+      </c>
+      <c r="C48" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="21" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B49" s="18">
+        <v>30</v>
+      </c>
+      <c r="C49" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="17" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B50" s="18">
+        <v>31</v>
+      </c>
+      <c r="C50" s="18">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="21" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B51" s="18">
+        <v>31</v>
+      </c>
+      <c r="C51" s="18">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="17" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B52" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="C52" s="18">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="21" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B53" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="C53" s="18">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="17" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B54" s="18">
+        <v>26</v>
+      </c>
+      <c r="C54" s="18">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="B55" s="18">
+        <v>26</v>
+      </c>
+      <c r="C55" s="18">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="17" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B56" s="18">
+        <v>29.9</v>
+      </c>
+      <c r="C56" s="18">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="21" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B57" s="18">
+        <v>29.9</v>
+      </c>
+      <c r="C57" s="18">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="17" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B58" s="18">
+        <v>32.5</v>
+      </c>
+      <c r="C58" s="18">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="21" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B59" s="18">
+        <v>32.5</v>
+      </c>
+      <c r="C59" s="18">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B60" s="18">
+        <v>33.5</v>
+      </c>
+      <c r="C60" s="18">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="21" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B61" s="18">
+        <v>33.5</v>
+      </c>
+      <c r="C61" s="18">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="17" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B62" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="C62" s="18">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="21" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B63" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="C63" s="18">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="17" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B64" s="18">
+        <v>41</v>
+      </c>
+      <c r="C64" s="18">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="21" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B65" s="18">
+        <v>41</v>
+      </c>
+      <c r="C65" s="18">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="17" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B66" s="18">
+        <v>30.529032258064515</v>
+      </c>
+      <c r="C66" s="18">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="B74" s="16" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="B76" s="16" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E76" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="B77" s="17" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C77" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="D77" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="E77">
+        <f>D77-C77</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="B78" s="17" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C78" s="18">
+        <v>36.5</v>
+      </c>
+      <c r="D78" s="18">
+        <v>40.5</v>
+      </c>
+      <c r="E78">
+        <f t="shared" ref="E78:E107" si="0">D78-C78</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="B79" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C79" s="18">
+        <v>30.5</v>
+      </c>
+      <c r="D79" s="18">
+        <v>28</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="0"/>
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="B80" s="17" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C80" s="18">
+        <v>27</v>
+      </c>
+      <c r="D80" s="18">
+        <v>33</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5">
+      <c r="B81" s="17" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C81" s="18">
+        <v>30</v>
+      </c>
+      <c r="D81" s="18">
+        <v>36.5</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5">
+      <c r="B82" s="17" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C82" s="18">
+        <v>25.5</v>
+      </c>
+      <c r="D82" s="18">
+        <v>28</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5">
+      <c r="B83" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C83" s="18">
+        <v>28.5</v>
+      </c>
+      <c r="D83" s="18">
+        <v>36</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5">
+      <c r="B84" s="17" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C84" s="18">
+        <v>33.5</v>
+      </c>
+      <c r="D84" s="18">
+        <v>38.5</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5">
+      <c r="B85" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="C85" s="18">
+        <v>27</v>
+      </c>
+      <c r="D85" s="18">
+        <v>39.5</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5">
+      <c r="B86" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C86" s="18">
+        <v>29.9</v>
+      </c>
+      <c r="D86" s="18">
+        <v>34</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="0"/>
+        <v>4.1000000000000014</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5">
+      <c r="B87" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="C87" s="18">
+        <v>26</v>
+      </c>
+      <c r="D87" s="18">
+        <v>31</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5">
+      <c r="B88" s="17" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C88" s="18">
+        <v>28.5</v>
+      </c>
+      <c r="D88" s="18">
+        <v>35</v>
+      </c>
+      <c r="E88">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5">
+      <c r="B89" s="17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C89" s="18">
+        <v>30.5</v>
+      </c>
+      <c r="D89" s="18">
+        <v>37.5</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5">
+      <c r="B90" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="C90" s="18">
+        <v>30.5</v>
+      </c>
+      <c r="D90" s="18">
+        <v>30.5</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5">
+      <c r="B91" s="17" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C91" s="18">
+        <v>25.5</v>
+      </c>
+      <c r="D91" s="18">
+        <v>27.5</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5">
+      <c r="B92" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="C92" s="18">
+        <v>25</v>
+      </c>
+      <c r="D92" s="18">
+        <v>27</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5">
+      <c r="B93" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="C93" s="18">
+        <v>32.5</v>
+      </c>
+      <c r="D93" s="18">
+        <v>46.5</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5">
+      <c r="B94" s="17" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C94" s="18">
+        <v>41</v>
+      </c>
+      <c r="D94" s="18">
+        <v>47.5</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5">
+      <c r="B95" s="17" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C95" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="D95" s="18">
+        <v>46.5</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5">
+      <c r="B96" s="17" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C96" s="18">
+        <v>30</v>
+      </c>
+      <c r="D96" s="18">
+        <v>35</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5">
+      <c r="B97" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="C97" s="18">
+        <v>31</v>
+      </c>
+      <c r="D97" s="18">
+        <v>40</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5">
+      <c r="B98" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="C98" s="18">
+        <v>28</v>
+      </c>
+      <c r="D98" s="18">
+        <v>31</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5">
+      <c r="B99" s="17" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C99" s="18">
+        <v>28</v>
+      </c>
+      <c r="D99" s="18">
+        <v>28</v>
+      </c>
+      <c r="E99">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5">
+      <c r="B100" s="17" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C100" s="18">
+        <v>32</v>
+      </c>
+      <c r="D100" s="18">
+        <v>33.5</v>
+      </c>
+      <c r="E100">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5">
+      <c r="B101" s="17" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C101" s="18">
+        <v>31</v>
+      </c>
+      <c r="D101" s="18">
+        <v>31</v>
+      </c>
+      <c r="E101">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5">
+      <c r="B102" s="17" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C102" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="D102" s="18">
+        <v>35.5</v>
+      </c>
+      <c r="E102">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5">
+      <c r="B103" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="C103" s="18">
+        <v>27</v>
+      </c>
+      <c r="D103" s="18">
+        <v>34.5</v>
+      </c>
+      <c r="E103">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5">
+      <c r="B104" s="17" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C104" s="18">
+        <v>32.5</v>
+      </c>
+      <c r="D104" s="18">
+        <v>32.5</v>
+      </c>
+      <c r="E104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5">
+      <c r="B105" s="17" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C105" s="18">
+        <v>30</v>
+      </c>
+      <c r="D105" s="18">
+        <v>30</v>
+      </c>
+      <c r="E105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5">
+      <c r="B106" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C106" s="18">
+        <v>26</v>
+      </c>
+      <c r="D106" s="18">
+        <v>29</v>
+      </c>
+      <c r="E106">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5">
+      <c r="B107" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="C107" s="18">
+        <v>36.5</v>
+      </c>
+      <c r="D107" s="18">
+        <v>46.5</v>
+      </c>
+      <c r="E107">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5">
+      <c r="B108" s="17" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C108" s="18">
+        <v>30.529032258064515</v>
+      </c>
+      <c r="D108" s="18">
+        <v>35</v>
+      </c>
+      <c r="E108">
+        <f>SUM(E77:E107)/31</f>
+        <v>4.4709677419354836</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5">
+      <c r="D109" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E109">
+        <f>E108/C108</f>
+        <v>0.14644970414201183</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89EF37-C3F3-8243-B091-96A26EC57E26}">
   <dimension ref="A1:BJ113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -40363,7 +44744,7 @@
         <v>1196</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>936</v>
@@ -40912,7 +45293,7 @@
         <v>26</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>973</v>
@@ -41100,7 +45481,7 @@
         <v>25</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>971</v>
@@ -41288,7 +45669,7 @@
         <v>26</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>564</v>
@@ -41470,7 +45851,7 @@
         <v>27</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>122</v>
@@ -42195,7 +46576,7 @@
         <v>27</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>209</v>
@@ -42738,7 +47119,7 @@
         <v>28</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>247</v>
@@ -43269,7 +47650,7 @@
         <v>28</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>162</v>
@@ -43630,7 +48011,7 @@
         <v>28</v>
       </c>
       <c r="O19" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>962</v>
@@ -44358,7 +48739,7 @@
         <v>25</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>388</v>
@@ -45614,7 +49995,7 @@
         <v>24.5</v>
       </c>
       <c r="O30" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="S30" s="2" t="s">
         <v>468</v>
@@ -47732,7 +52113,7 @@
         <v>35.5</v>
       </c>
       <c r="O42" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>949</v>
@@ -48090,7 +52471,7 @@
         <v>29</v>
       </c>
       <c r="O44" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="V44" s="2" t="s">
         <v>47</v>
@@ -48263,7 +52644,7 @@
         <v>30</v>
       </c>
       <c r="O45" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>886</v>
@@ -48438,6 +52819,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
+      <c r="O46" s="14" t="s">
+        <v>1199</v>
+      </c>
       <c r="P46" s="2" t="s">
         <v>947</v>
       </c>
@@ -48621,7 +53005,7 @@
         <v>15</v>
       </c>
       <c r="O47" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>945</v>
@@ -48728,7 +53112,7 @@
         <v>15</v>
       </c>
       <c r="O48" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>943</v>
@@ -48832,7 +53216,7 @@
         <v>15</v>
       </c>
       <c r="O49" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>941</v>
@@ -48936,7 +53320,7 @@
         <v>15</v>
       </c>
       <c r="O50" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>939</v>
@@ -49202,15 +53586,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F3EDA-67FF-1141-88FB-67CF8719809C}">
   <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">

--- a/db/A7XLK-1102-HouseBigData.xlsx
+++ b/db/A7XLK-1102-HouseBigData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21577979-A999-CB45-8EF1-34F66D01F639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17030D2-0EC2-6B4D-80E1-23993BD15668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15620" yWindow="-20600" windowWidth="35780" windowHeight="16200" firstSheet="4" activeTab="15" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
+    <workbookView xWindow="-8480" yWindow="-15900" windowWidth="35780" windowHeight="16200" firstSheet="4" activeTab="15" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure-1" sheetId="2" r:id="rId1"/>
@@ -38,8 +38,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="142" r:id="rId18"/>
-    <pivotCache cacheId="155" r:id="rId19"/>
+    <pivotCache cacheId="159" r:id="rId18"/>
+    <pivotCache cacheId="160" r:id="rId19"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="1268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2954" uniqueCount="1271">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4766,6 +4766,18 @@
   </si>
   <si>
     <t>平均值 - 2020每坪開價-最高</t>
+  </si>
+  <si>
+    <t>2020目標值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>目標誤差比例</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020 目標誤差比例</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4931,52 +4943,7 @@
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="8" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="0_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="0_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="8" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="0_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="0_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="8" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="0_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="0_ "/>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
     </dxf>
@@ -12428,6 +12395,2044 @@
       </c16:pivotOptions16>
     </c:ext>
   </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-22'!$C$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平均值 - 實價2021</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Figure-22'!$B$142:$B$173</c:f>
+              <c:strCache>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>大亮時代A7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>友文化</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>文華天際</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>水悅青青</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>台北國際村</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>玉子園</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>禾悅花園</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>竹城甲子園</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>竹城明治</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>君邑丘比特</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>和洲金剛</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>和發大境</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>和耀恆美</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>金捷市</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>皇普MVP</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>根津苑</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>富宇哈佛苑</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>富宇悅峰</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>富宇敦峰</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>富御捷境</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>詠勝市中欣</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>新A7</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>新未來1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>新未來3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>新潤鉑麗</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>新潤翡麗</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>樂田田</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>樂捷市</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>頤昌璞岳</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>鴻典</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>耀台北</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>櫻花澍</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-22'!$C$142:$C$173</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>29.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.59</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.71</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22.83</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21.64</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>29.88</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>26.45</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.56</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27.47</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>26.33</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>27.72</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25.24</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>26.46</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>24.17</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>23.36</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>34.08</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>24.96</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>29.71</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>25.73</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21.19</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>26.59</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>34.36</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>30.02</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>26.4</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26.84</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>22.84</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>24.46</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>27.11</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>24.35</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>24.43</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DE3C-2C4B-AF10-D1AE07C653BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-22'!$D$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平均值 - 2020每坪開價-最低</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Figure-22'!$B$142:$B$173</c:f>
+              <c:strCache>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>大亮時代A7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>友文化</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>文華天際</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>水悅青青</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>台北國際村</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>玉子園</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>禾悅花園</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>竹城甲子園</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>竹城明治</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>君邑丘比特</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>和洲金剛</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>和發大境</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>和耀恆美</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>金捷市</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>皇普MVP</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>根津苑</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>富宇哈佛苑</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>富宇悅峰</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>富宇敦峰</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>富御捷境</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>詠勝市中欣</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>新A7</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>新未來1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>新未來3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>新潤鉑麗</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>新潤翡麗</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>樂田田</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>樂捷市</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>頤昌璞岳</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>鴻典</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>耀台北</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>櫻花澍</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-22'!$D$142:$D$173</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>28</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DE3C-2C4B-AF10-D1AE07C653BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-22'!$E$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平均值 - 2020每坪開價-最高</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Figure-22'!$B$142:$B$173</c:f>
+              <c:strCache>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>大亮時代A7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>友文化</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>文華天際</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>水悅青青</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>台北國際村</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>玉子園</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>禾悅花園</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>竹城甲子園</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>竹城明治</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>君邑丘比特</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>和洲金剛</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>和發大境</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>和耀恆美</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>金捷市</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>皇普MVP</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>根津苑</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>富宇哈佛苑</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>富宇悅峰</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>富宇敦峰</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>富御捷境</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>詠勝市中欣</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>新A7</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>新未來1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>新未來3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>新潤鉑麗</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>新潤翡麗</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>樂田田</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>樂捷市</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>頤昌璞岳</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>鴻典</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>耀台北</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>櫻花澍</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-22'!$E$142:$E$173</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DE3C-2C4B-AF10-D1AE07C653BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-22'!$F$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2020目標值</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Figure-22'!$B$142:$B$173</c:f>
+              <c:strCache>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>大亮時代A7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>友文化</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>文華天際</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>水悅青青</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>台北國際村</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>玉子園</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>禾悅花園</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>竹城甲子園</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>竹城明治</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>君邑丘比特</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>和洲金剛</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>和發大境</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>和耀恆美</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>金捷市</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>皇普MVP</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>根津苑</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>富宇哈佛苑</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>富宇悅峰</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>富宇敦峰</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>富御捷境</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>詠勝市中欣</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>新A7</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>新未來1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>新未來3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>新潤鉑麗</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>新潤翡麗</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>樂田田</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>樂捷市</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>頤昌璞岳</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>鴻典</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>耀台北</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>櫻花澍</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-22'!$F$142:$F$173</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>29.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-DE3C-2C4B-AF10-D1AE07C653BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-22'!$G$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>目標誤差比例</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Figure-22'!$B$142:$B$173</c:f>
+              <c:strCache>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>大亮時代A7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>友文化</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>文華天際</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>水悅青青</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>台北國際村</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>玉子園</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>禾悅花園</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>竹城甲子園</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>竹城明治</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>君邑丘比特</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>和洲金剛</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>和發大境</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>和耀恆美</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>金捷市</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>皇普MVP</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>根津苑</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>富宇哈佛苑</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>富宇悅峰</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>富宇敦峰</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>富御捷境</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>詠勝市中欣</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>新A7</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>新未來1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>新未來3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>新潤鉑麗</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>新潤翡麗</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>樂田田</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>樂捷市</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>頤昌璞岳</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>鴻典</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>耀台北</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>櫻花澍</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-22'!$G$142:$G$173</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>0.20748299319727898</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.29292072912250955</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.0175029171528551E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.21163166397415178</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1169513797634692</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.24768946395563768</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.6184738955823264E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.0793950850661654E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.1867469879518118E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.8460138332726604E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.2533232054690403E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.8138528138528181E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.20839936608557852</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.15268329554043836</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.5026892842366497E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.0205479452054825E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.166666666666672E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.20192307692307687</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.3419723998653625E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.8223863194714328E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.39216611609249635</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.20345994734862732</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.3178114086146702E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.18254497001998668</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.0606060606060663E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.9612518628912124E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.11646234676007006</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6.2959934587080907E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.19881962375507195</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6.7761806981519443E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.10519852640196481</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.14503816793893132</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-DE3C-2C4B-AF10-D1AE07C653BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1627172496"/>
+        <c:axId val="1627188944"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1627172496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1627188944"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1627188944"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1627172496"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Figure-22'!$C$179</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2020 目標誤差比例</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Figure-22'!$B$180:$B$211</c:f>
+              <c:strCache>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>詠勝市中欣</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>友文化</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>玉子園</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>水悅青青</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>和耀恆美</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>大亮時代A7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>新A7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>富宇悅峰</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>頤昌璞岳</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>新未來3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>金捷市</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>櫻花澍</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>台北國際村</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>樂田田</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>耀台北</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>竹城明治</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>君邑丘比特</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>富御捷境</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>根津苑</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>鴻典</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>樂捷市</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>新潤鉑麗</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>皇普MVP</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>文華天際</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>富宇敦峰</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>富宇哈佛苑</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>新未來1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>和發大境</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>竹城甲子園</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>新潤翡麗</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>和洲金剛</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>禾悅花園</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Figure-22'!$C$180:$C$211</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>0.39216611609249635</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.29292072912250955</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.24768946395563768</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.21163166397415178</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.20839936608557852</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20748299319727898</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.20345994734862732</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.20192307692307687</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.19881962375507195</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.18254497001998668</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.15268329554043836</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.14503816793893132</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.1169513797634692</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.11646234676007006</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.10519852640196481</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.1867469879518118E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.8460138332726604E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.8223863194714328E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.0205479452054825E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.7761806981519443E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.2959934587080907E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.0606060606060663E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.5026892842366497E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.0175029171528551E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.3419723998653625E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.166666666666672E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.3178114086146702E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.8138528138528181E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.0793950850661654E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.9612518628912124E-3</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-1.2533232054690403E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-4.6184738955823264E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1C4E-D741-A61B-D5303040313A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
+        <c:axId val="892868687"/>
+        <c:axId val="893107727"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="892868687"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="893107727"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="893107727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200"/>
+                  <a:t>2020 </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="zh-TW" sz="1200"/>
+                  <a:t>開價誤差比例</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="892868687"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+          <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
@@ -20536,6 +22541,86 @@
 </file>
 
 <file path=xl/charts/colors17.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors18.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors19.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -25419,6 +27504,1012 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style18.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style19.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -29893,15 +32984,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1066800</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>673100</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -29922,6 +33013,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FD4826B-803D-4D4B-995F-CAFD08ED5986}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>181</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="圖表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03F266BF-A06B-604A-8577-1CF162E06831}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -38044,7 +41207,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A3CA2B-B6E6-A64B-BB28-39916B3C266F}" name="樞紐分析表1" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A3CA2B-B6E6-A64B-BB28-39916B3C266F}" name="樞紐分析表1" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:C53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -38442,7 +41605,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F52A0184-F9FB-7249-BCA8-2F8B6C3580F3}" name="樞紐分析表1" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F52A0184-F9FB-7249-BCA8-2F8B6C3580F3}" name="樞紐分析表1" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -39065,7 +42228,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A05ECE1-698D-3F42-A1F5-015F41A70879}" name="樞紐分析表2" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A05ECE1-698D-3F42-A1F5-015F41A70879}" name="樞紐分析表2" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A37:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -39258,7 +42421,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7019A1B8-C948-9248-8ABA-BFD05B6AA01A}" name="樞紐分析表1" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7019A1B8-C948-9248-8ABA-BFD05B6AA01A}" name="樞紐分析表1" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -39415,7 +42578,569 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4D14CAE-2C58-9D43-B1F7-B8BBC66C68B5}" name="樞紐分析表2" cacheId="155" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34FE811F-B077-FD42-9008-279DB01289D2}" name="樞紐分析表1" cacheId="160" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="66">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" numFmtId="177" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="20">
+        <item h="1" x="18"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="20">
+        <item x="14"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item h="1" x="17"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item h="1" x="5"/>
+        <item h="1" x="16"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="38"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="13" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - 每坪價-平均" fld="13" subtotal="average" baseField="0" baseItem="0" numFmtId="179"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8299DB4-79E1-2840-954E-122EFC07C81F}" name="樞紐分析表3" cacheId="160" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="B86:C118" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="66">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="50">
+        <item x="39"/>
+        <item x="14"/>
+        <item x="22"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="38"/>
+        <item x="47"/>
+        <item x="25"/>
+        <item x="43"/>
+        <item x="42"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="46"/>
+        <item x="18"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="31"/>
+        <item x="20"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="19"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="40"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="45"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="37"/>
+        <item x="32"/>
+        <item x="1"/>
+        <item x="27"/>
+        <item x="48"/>
+        <item x="9"/>
+        <item x="44"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="31">
+        <item x="25"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="24"/>
+        <item x="28"/>
+        <item x="16"/>
+        <item x="23"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="22"/>
+        <item x="19"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="27"/>
+        <item x="4"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="1"/>
+        <item x="29"/>
+        <item x="26"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="20">
+        <item h="1" x="14"/>
+        <item h="1" x="4"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="13"/>
+        <item h="1" x="17"/>
+        <item h="1" x="8"/>
+        <item h="1" x="12"/>
+        <item h="1" x="5"/>
+        <item h="1" x="16"/>
+        <item h="1" x="1"/>
+        <item h="1" x="9"/>
+        <item h="1" x="6"/>
+        <item h="1" x="11"/>
+        <item h="1" x="7"/>
+        <item h="1" x="10"/>
+        <item h="1" x="18"/>
+        <item x="0"/>
+        <item h="1" x="15"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="37"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="32">
+    <i>
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="45"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+    </i>
+    <i r="1">
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="40"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="38" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - 每坪價-平均" fld="13" subtotal="average" baseField="0" baseItem="0" numFmtId="179"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4D14CAE-2C58-9D43-B1F7-B8BBC66C68B5}" name="樞紐分析表2" cacheId="160" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="B48:D64" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="66">
     <pivotField showAll="0"/>
@@ -39679,570 +43404,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34FE811F-B077-FD42-9008-279DB01289D2}" name="樞紐分析表1" cacheId="155" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="66">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField axis="axisPage" dataField="1" numFmtId="177" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="20">
-        <item h="1" x="18"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="17"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="12"/>
-        <item x="5"/>
-        <item x="15"/>
-        <item x="13"/>
-        <item x="9"/>
-        <item x="16"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="20">
-        <item x="14"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="13"/>
-        <item h="1" x="17"/>
-        <item x="8"/>
-        <item x="12"/>
-        <item h="1" x="5"/>
-        <item h="1" x="16"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="11"/>
-        <item x="7"/>
-        <item x="10"/>
-        <item x="18"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="38"/>
-  </rowFields>
-  <rowItems count="16">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="13" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="平均值 - 每坪價-平均" fld="13" subtotal="average" baseField="0" baseItem="0" numFmtId="179"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8299DB4-79E1-2840-954E-122EFC07C81F}" name="樞紐分析表3" cacheId="155" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="B86:C118" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="66">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="50">
-        <item x="39"/>
-        <item x="14"/>
-        <item x="22"/>
-        <item x="24"/>
-        <item x="23"/>
-        <item x="6"/>
-        <item x="12"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="38"/>
-        <item x="47"/>
-        <item x="25"/>
-        <item x="43"/>
-        <item x="42"/>
-        <item x="36"/>
-        <item x="35"/>
-        <item x="0"/>
-        <item x="13"/>
-        <item x="3"/>
-        <item x="15"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="46"/>
-        <item x="18"/>
-        <item x="7"/>
-        <item x="41"/>
-        <item x="31"/>
-        <item x="20"/>
-        <item x="11"/>
-        <item x="30"/>
-        <item x="19"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="40"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="45"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="37"/>
-        <item x="32"/>
-        <item x="1"/>
-        <item x="27"/>
-        <item x="48"/>
-        <item x="9"/>
-        <item x="44"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField dataField="1" numFmtId="177" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField numFmtId="177" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="31">
-        <item x="25"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="5"/>
-        <item x="15"/>
-        <item x="24"/>
-        <item x="28"/>
-        <item x="16"/>
-        <item x="23"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="22"/>
-        <item x="19"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item x="27"/>
-        <item x="4"/>
-        <item x="17"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="21"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="1"/>
-        <item x="29"/>
-        <item x="26"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="20">
-        <item h="1" x="14"/>
-        <item h="1" x="4"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="13"/>
-        <item h="1" x="17"/>
-        <item h="1" x="8"/>
-        <item h="1" x="12"/>
-        <item h="1" x="5"/>
-        <item h="1" x="16"/>
-        <item h="1" x="1"/>
-        <item h="1" x="9"/>
-        <item h="1" x="6"/>
-        <item h="1" x="11"/>
-        <item h="1" x="7"/>
-        <item h="1" x="10"/>
-        <item h="1" x="18"/>
-        <item x="0"/>
-        <item h="1" x="15"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="37"/>
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="32">
-    <i>
-      <x v="26"/>
-    </i>
-    <i r="1">
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i r="1">
-      <x v="45"/>
-    </i>
-    <i r="1">
-      <x v="21"/>
-    </i>
-    <i r="1">
-      <x v="44"/>
-    </i>
-    <i r="1">
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i r="1">
-      <x v="18"/>
-    </i>
-    <i r="1">
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i r="1">
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i r="1">
-      <x v="17"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i r="1">
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="40"/>
-    </i>
-    <i r="1">
-      <x v="19"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="38" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="平均值 - 每坪價-平均" fld="13" subtotal="average" baseField="0" baseItem="0" numFmtId="179"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{458FE396-6E8A-064D-96E2-0847BBE52133}" name="樞紐分析表7" cacheId="155" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="3ㄒㄧ1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{458FE396-6E8A-064D-96E2-0847BBE52133}" name="樞紐分析表7" cacheId="160" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="3ㄒㄧ1">
   <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="66">
     <pivotField dataField="1" showAll="0"/>
@@ -40372,7 +43535,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B833B209-0CFF-0548-B5A9-F2903FE4CB01}" name="樞紐分析表1" cacheId="155" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B833B209-0CFF-0548-B5A9-F2903FE4CB01}" name="樞紐分析表1" cacheId="160" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="66">
     <pivotField showAll="0"/>
@@ -40560,7 +43723,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EAAEFCC-9164-E944-82C8-7A061A3EB16F}" name="樞紐分析表2" cacheId="155" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EAAEFCC-9164-E944-82C8-7A061A3EB16F}" name="樞紐分析表2" cacheId="160" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B76:D108" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="66">
     <pivotField showAll="0"/>
@@ -40821,7 +43984,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7C0AAB9-C4B2-6E4F-822E-42DD3E7664C6}" name="樞紐分析表1" cacheId="155" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7C0AAB9-C4B2-6E4F-822E-42DD3E7664C6}" name="樞紐分析表1" cacheId="160" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:C66" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="66">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -41264,7 +44427,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D90A3B06-44FC-DF47-95B9-374674E5983F}" name="樞紐分析表2" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D90A3B06-44FC-DF47-95B9-374674E5983F}" name="樞紐分析表2" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:A53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -41545,7 +44708,7 @@
     <i/>
   </colItems>
   <formats count="1">
-    <format dxfId="17">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -41562,7 +44725,403 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{23795CE1-36F7-DB4B-B9B6-F0E0362CF4A1}" name="樞紐分析表6" cacheId="155" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CA5682F6-CB99-BD42-8981-C5F2FA0078E5}" name="樞紐分析表7" cacheId="160" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B103:E136" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="66">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="50">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item h="1" x="45"/>
+        <item h="1" x="46"/>
+        <item h="1" x="47"/>
+        <item h="1" x="48"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="50">
+        <item x="39"/>
+        <item x="14"/>
+        <item x="22"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="38"/>
+        <item x="47"/>
+        <item x="25"/>
+        <item x="43"/>
+        <item x="42"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="46"/>
+        <item x="18"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="31"/>
+        <item x="20"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="19"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="40"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="45"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="37"/>
+        <item x="32"/>
+        <item x="1"/>
+        <item x="27"/>
+        <item x="48"/>
+        <item x="9"/>
+        <item x="44"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="38">
+        <item x="21"/>
+        <item x="5"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="16"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="17"/>
+        <item x="15"/>
+        <item x="11"/>
+        <item x="18"/>
+        <item x="23"/>
+        <item x="32"/>
+        <item x="26"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="31"/>
+        <item x="22"/>
+        <item x="12"/>
+        <item x="28"/>
+        <item x="27"/>
+        <item x="0"/>
+        <item x="29"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="25"/>
+        <item x="24"/>
+        <item x="30"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0">
+      <items count="17">
+        <item x="15"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="177" showAll="0">
+      <items count="16">
+        <item x="14"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="33">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="0" hier="-1"/>
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="平均值 - 實價2021" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="178"/>
+    <dataField name="平均值 - 2020每坪開價-最低" fld="11" subtotal="average" baseField="0" baseItem="0" numFmtId="178"/>
+    <dataField name="平均值 - 2020每坪開價-最高" fld="12" subtotal="average" baseField="0" baseItem="0" numFmtId="178"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable21.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{23795CE1-36F7-DB4B-B9B6-F0E0362CF4A1}" name="樞紐分析表6" cacheId="160" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A4:D48" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="66">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -42044,7 +45603,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C48516-4469-E144-BC4C-C411D0731588}" name="樞紐分析表4" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C48516-4469-E144-BC4C-C411D0731588}" name="樞紐分析表4" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:C53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -42337,7 +45896,7 @@
     <dataField name="平均值 - 建蔽比率" fld="48" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="16">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2" selected="0">
@@ -42381,7 +45940,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E3E605F-0935-CE47-93A7-EE637CD6D22D}" name="樞紐分析表3" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E3E605F-0935-CE47-93A7-EE637CD6D22D}" name="樞紐分析表3" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B64" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -42739,7 +46298,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCF300E8-2DA3-FD4D-8DB5-C4AF4C0B2B4D}" name="樞紐分析表5" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCF300E8-2DA3-FD4D-8DB5-C4AF4C0B2B4D}" name="樞紐分析表5" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -43159,7 +46718,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{537918C9-6258-454A-9359-2B209B13DC90}" name="樞紐分析表6" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{537918C9-6258-454A-9359-2B209B13DC90}" name="樞紐分析表6" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -43481,7 +47040,7 @@
     <dataField name="加總 - 建築面積" fld="57" baseField="0" baseItem="0" numFmtId="179"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="15">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -43509,7 +47068,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A78E8CA-AA2E-4542-B594-47B469B1ECF7}" name="樞紐分析表7" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A78E8CA-AA2E-4542-B594-47B469B1ECF7}" name="樞紐分析表7" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -43831,7 +47390,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4AA391D-DCC2-A047-A23D-C8888E109D7F}" name="樞紐分析表8" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4AA391D-DCC2-A047-A23D-C8888E109D7F}" name="樞紐分析表8" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -44156,7 +47715,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E436F8BC-6E9C-CD4C-8D5F-9F959847D2E8}" name="樞紐分析表9" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E436F8BC-6E9C-CD4C-8D5F-9F959847D2E8}" name="樞紐分析表9" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="65">
     <pivotField showAll="0"/>
@@ -47786,15 +51345,16 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CF9E9E-525A-1441-A75E-26BF1197A2E5}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="27.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="16" t="s">
         <v>1255</v>
       </c>
@@ -47802,7 +51362,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="16" t="s">
         <v>1265</v>
       </c>
@@ -47810,7 +51370,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="16" t="s">
         <v>1023</v>
       </c>
@@ -47823,8 +51383,11 @@
       <c r="D4" t="s">
         <v>1267</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="17" t="s">
         <v>1092</v>
       </c>
@@ -47837,8 +51400,12 @@
       <c r="D5" s="23">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="23">
+        <f>(C5+D5)/2</f>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="20" t="s">
         <v>1193</v>
       </c>
@@ -47851,8 +51418,12 @@
       <c r="D6" s="23">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="23">
+        <f t="shared" ref="E6:E47" si="0">(C6+D6)/2</f>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="17" t="s">
         <v>1148</v>
       </c>
@@ -47865,8 +51436,12 @@
       <c r="D7" s="23">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="23">
+        <f t="shared" si="0"/>
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="20" t="s">
         <v>183</v>
       </c>
@@ -47879,8 +51454,12 @@
       <c r="D8" s="23">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="23">
+        <f t="shared" si="0"/>
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="17" t="s">
         <v>275</v>
       </c>
@@ -47893,8 +51472,12 @@
       <c r="D9" s="23">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="23">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="20" t="s">
         <v>267</v>
       </c>
@@ -47907,8 +51490,12 @@
       <c r="D10" s="23">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="23">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="20" t="s">
         <v>523</v>
       </c>
@@ -47921,8 +51508,12 @@
       <c r="D11" s="23">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="23">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="17" t="s">
         <v>1096</v>
       </c>
@@ -47935,8 +51526,12 @@
       <c r="D12" s="23">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="23">
+        <f t="shared" si="0"/>
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="20" t="s">
         <v>1196</v>
       </c>
@@ -47949,8 +51544,12 @@
       <c r="D13" s="23">
         <v>32</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="23">
+        <f t="shared" si="0"/>
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="17" t="s">
         <v>167</v>
       </c>
@@ -47963,8 +51562,12 @@
       <c r="D14" s="23">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="23">
+        <f t="shared" si="0"/>
+        <v>32.166666666666664</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="20" t="s">
         <v>1198</v>
       </c>
@@ -47977,8 +51580,12 @@
       <c r="D15" s="23">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="23">
+        <f t="shared" si="0"/>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="20" t="s">
         <v>1199</v>
       </c>
@@ -47991,8 +51598,12 @@
       <c r="D16" s="23">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="23">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="20" t="s">
         <v>224</v>
       </c>
@@ -48005,8 +51616,12 @@
       <c r="D17" s="23">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="23">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="17" t="s">
         <v>473</v>
       </c>
@@ -48019,8 +51634,12 @@
       <c r="D18" s="23">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="23">
+        <f t="shared" si="0"/>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="20" t="s">
         <v>463</v>
       </c>
@@ -48033,8 +51652,12 @@
       <c r="D19" s="23">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="23">
+        <f t="shared" si="0"/>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="17" t="s">
         <v>316</v>
       </c>
@@ -48047,8 +51670,12 @@
       <c r="D20" s="23">
         <v>28.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="23">
+        <f t="shared" si="0"/>
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="20" t="s">
         <v>1252</v>
       </c>
@@ -48061,8 +51688,12 @@
       <c r="D21" s="23">
         <v>29</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="23">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="20" t="s">
         <v>308</v>
       </c>
@@ -48075,8 +51706,12 @@
       <c r="D22" s="23">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="23">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="17" t="s">
         <v>1101</v>
       </c>
@@ -48089,8 +51724,12 @@
       <c r="D23" s="23">
         <v>38</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="23">
+        <f t="shared" si="0"/>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="20" t="s">
         <v>1253</v>
       </c>
@@ -48103,8 +51742,12 @@
       <c r="D24" s="23">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="23">
+        <f t="shared" si="0"/>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="20" t="s">
         <v>1202</v>
       </c>
@@ -48117,8 +51760,12 @@
       <c r="D25" s="23">
         <v>38</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="23">
+        <f t="shared" si="0"/>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="17" t="s">
         <v>1103</v>
       </c>
@@ -48131,8 +51778,12 @@
       <c r="D26" s="23">
         <v>33</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="23">
+        <f t="shared" si="0"/>
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="20" t="s">
         <v>1203</v>
       </c>
@@ -48145,8 +51796,12 @@
       <c r="D27" s="23">
         <v>33</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="23">
+        <f t="shared" si="0"/>
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="17" t="s">
         <v>1146</v>
       </c>
@@ -48159,8 +51814,12 @@
       <c r="D28" s="23">
         <v>28.382352941176471</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="23">
+        <f t="shared" si="0"/>
+        <v>27.676470588235293</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="20" t="s">
         <v>1158</v>
       </c>
@@ -48173,8 +51832,12 @@
       <c r="D29" s="23">
         <v>31</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29" s="23">
+        <f t="shared" si="0"/>
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="20" t="s">
         <v>1159</v>
       </c>
@@ -48187,8 +51850,12 @@
       <c r="D30" s="23">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="23">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="20" t="s">
         <v>1157</v>
       </c>
@@ -48201,8 +51868,12 @@
       <c r="D31" s="23">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" s="23">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="20" t="s">
         <v>1161</v>
       </c>
@@ -48215,8 +51886,12 @@
       <c r="D32" s="23">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="23">
+        <f t="shared" si="0"/>
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="20" t="s">
         <v>1160</v>
       </c>
@@ -48229,8 +51904,12 @@
       <c r="D33" s="23">
         <v>28</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" s="23">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="20" t="s">
         <v>442</v>
       </c>
@@ -48243,8 +51922,12 @@
       <c r="D34" s="23">
         <v>27</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34" s="23">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="20" t="s">
         <v>1162</v>
       </c>
@@ -48257,8 +51940,12 @@
       <c r="D35" s="23">
         <v>29</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" s="23">
+        <f t="shared" si="0"/>
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="20" t="s">
         <v>1155</v>
       </c>
@@ -48271,8 +51958,12 @@
       <c r="D36" s="23">
         <v>33</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36" s="23">
+        <f t="shared" si="0"/>
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="20" t="s">
         <v>329</v>
       </c>
@@ -48285,8 +51976,12 @@
       <c r="D37" s="23">
         <v>30.5</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="23">
+        <f t="shared" si="0"/>
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="20" t="s">
         <v>1163</v>
       </c>
@@ -48299,8 +51994,12 @@
       <c r="D38" s="23">
         <v>26</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="23">
+        <f t="shared" si="0"/>
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="20" t="s">
         <v>349</v>
       </c>
@@ -48313,8 +52012,12 @@
       <c r="D39" s="23">
         <v>26</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" s="23">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="20" t="s">
         <v>488</v>
       </c>
@@ -48327,8 +52030,12 @@
       <c r="D40" s="23">
         <v>29</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40" s="23">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="20" t="s">
         <v>1154</v>
       </c>
@@ -48341,8 +52048,12 @@
       <c r="D41" s="23">
         <v>33</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="E41" s="23">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="20" t="s">
         <v>1164</v>
       </c>
@@ -48355,8 +52066,12 @@
       <c r="D42" s="23">
         <v>26</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="E42" s="23">
+        <f t="shared" si="0"/>
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="20" t="s">
         <v>73</v>
       </c>
@@ -48369,8 +52084,12 @@
       <c r="D43" s="23">
         <v>26</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="E43" s="23">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" s="20" t="s">
         <v>41</v>
       </c>
@@ -48383,8 +52102,12 @@
       <c r="D44" s="23">
         <v>26</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44" s="23">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" s="20" t="s">
         <v>1156</v>
       </c>
@@ -48397,8 +52120,12 @@
       <c r="D45" s="23">
         <v>28</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="E45" s="23">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" s="17" t="s">
         <v>1106</v>
       </c>
@@ -48411,8 +52138,12 @@
       <c r="D46" s="23">
         <v>32</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46" s="23">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" s="20" t="s">
         <v>1254</v>
       </c>
@@ -48425,8 +52156,12 @@
       <c r="D47" s="23">
         <v>32</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="E47" s="23">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" s="17" t="s">
         <v>1024</v>
       </c>
@@ -48440,10 +52175,1755 @@
         <v>30.296875</v>
       </c>
     </row>
+    <row r="100" spans="2:7">
+      <c r="B100" s="16" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7">
+      <c r="B101" s="16" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7">
+      <c r="B103" s="16" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E103" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F103" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G103" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
+      <c r="B104" s="17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C104" s="23">
+        <v>29.4</v>
+      </c>
+      <c r="D104" s="23">
+        <v>35</v>
+      </c>
+      <c r="E104" s="23">
+        <v>36</v>
+      </c>
+      <c r="F104" s="23">
+        <f>(D104+E104)/2</f>
+        <v>35.5</v>
+      </c>
+      <c r="G104" s="19">
+        <f>(F104-C104)/C104</f>
+        <v>0.20748299319727898</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7">
+      <c r="B105" s="17" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C105" s="23">
+        <v>23.59</v>
+      </c>
+      <c r="D105" s="23">
+        <v>30</v>
+      </c>
+      <c r="E105" s="23">
+        <v>31</v>
+      </c>
+      <c r="F105" s="23">
+        <f t="shared" ref="F105:F135" si="1">(D105+E105)/2</f>
+        <v>30.5</v>
+      </c>
+      <c r="G105" s="19">
+        <f t="shared" ref="G105:G135" si="2">(F105-C105)/C105</f>
+        <v>0.29292072912250955</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7">
+      <c r="B106" s="17" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C106" s="23">
+        <v>25.71</v>
+      </c>
+      <c r="D106" s="23">
+        <v>27</v>
+      </c>
+      <c r="E106" s="23">
+        <v>27</v>
+      </c>
+      <c r="F106" s="23">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="G106" s="19">
+        <f t="shared" si="2"/>
+        <v>5.0175029171528551E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7">
+      <c r="B107" s="17" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C107" s="23">
+        <v>24.76</v>
+      </c>
+      <c r="D107" s="23">
+        <v>29</v>
+      </c>
+      <c r="E107" s="23">
+        <v>31</v>
+      </c>
+      <c r="F107" s="23">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G107" s="19">
+        <f t="shared" si="2"/>
+        <v>0.21163166397415178</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7">
+      <c r="B108" s="17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C108" s="23">
+        <v>22.83</v>
+      </c>
+      <c r="D108" s="23">
+        <v>25</v>
+      </c>
+      <c r="E108" s="23">
+        <v>26</v>
+      </c>
+      <c r="F108" s="23">
+        <f t="shared" si="1"/>
+        <v>25.5</v>
+      </c>
+      <c r="G108" s="19">
+        <f t="shared" si="2"/>
+        <v>0.1169513797634692</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7">
+      <c r="B109" s="17" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C109" s="23">
+        <v>21.64</v>
+      </c>
+      <c r="D109" s="23">
+        <v>26</v>
+      </c>
+      <c r="E109" s="23">
+        <v>28</v>
+      </c>
+      <c r="F109" s="23">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="G109" s="19">
+        <f t="shared" si="2"/>
+        <v>0.24768946395563768</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7">
+      <c r="B110" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C110" s="23">
+        <v>29.88</v>
+      </c>
+      <c r="D110" s="23">
+        <v>28</v>
+      </c>
+      <c r="E110" s="23">
+        <v>29</v>
+      </c>
+      <c r="F110" s="23">
+        <f t="shared" si="1"/>
+        <v>28.5</v>
+      </c>
+      <c r="G110" s="19">
+        <f t="shared" si="2"/>
+        <v>-4.6184738955823264E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7">
+      <c r="B111" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="C111" s="23">
+        <v>26.45</v>
+      </c>
+      <c r="D111" s="23">
+        <v>26</v>
+      </c>
+      <c r="E111" s="23">
+        <v>28</v>
+      </c>
+      <c r="F111" s="23">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="G111" s="19">
+        <f t="shared" si="2"/>
+        <v>2.0793950850661654E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7">
+      <c r="B112" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="C112" s="23">
+        <v>26.56</v>
+      </c>
+      <c r="D112" s="23">
+        <v>28</v>
+      </c>
+      <c r="E112" s="23">
+        <v>30</v>
+      </c>
+      <c r="F112" s="23">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="G112" s="19">
+        <f t="shared" si="2"/>
+        <v>9.1867469879518118E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7">
+      <c r="B113" s="17" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C113" s="23">
+        <v>27.47</v>
+      </c>
+      <c r="D113" s="23">
+        <v>27.8</v>
+      </c>
+      <c r="E113" s="23">
+        <v>32</v>
+      </c>
+      <c r="F113" s="23">
+        <f t="shared" si="1"/>
+        <v>29.9</v>
+      </c>
+      <c r="G113" s="19">
+        <f t="shared" si="2"/>
+        <v>8.8460138332726604E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7">
+      <c r="B114" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="C114" s="23">
+        <v>26.33</v>
+      </c>
+      <c r="D114" s="23">
+        <v>25</v>
+      </c>
+      <c r="E114" s="23">
+        <v>27</v>
+      </c>
+      <c r="F114" s="23">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="G114" s="19">
+        <f t="shared" si="2"/>
+        <v>-1.2533232054690403E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7">
+      <c r="B115" s="17" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C115" s="23">
+        <v>27.72</v>
+      </c>
+      <c r="D115" s="23">
+        <v>28</v>
+      </c>
+      <c r="E115" s="23">
+        <v>29</v>
+      </c>
+      <c r="F115" s="23">
+        <f t="shared" si="1"/>
+        <v>28.5</v>
+      </c>
+      <c r="G115" s="19">
+        <f t="shared" si="2"/>
+        <v>2.8138528138528181E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7">
+      <c r="B116" s="17" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C116" s="23">
+        <v>25.24</v>
+      </c>
+      <c r="D116" s="23">
+        <v>28</v>
+      </c>
+      <c r="E116" s="23">
+        <v>33</v>
+      </c>
+      <c r="F116" s="23">
+        <f t="shared" si="1"/>
+        <v>30.5</v>
+      </c>
+      <c r="G116" s="19">
+        <f t="shared" si="2"/>
+        <v>0.20839936608557852</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7">
+      <c r="B117" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C117" s="23">
+        <v>26.46</v>
+      </c>
+      <c r="D117" s="23">
+        <v>30.5</v>
+      </c>
+      <c r="E117" s="23">
+        <v>30.5</v>
+      </c>
+      <c r="F117" s="23">
+        <f t="shared" si="1"/>
+        <v>30.5</v>
+      </c>
+      <c r="G117" s="19">
+        <f t="shared" si="2"/>
+        <v>0.15268329554043836</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7">
+      <c r="B118" s="17" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C118" s="23">
+        <v>24.17</v>
+      </c>
+      <c r="D118" s="23">
+        <v>25</v>
+      </c>
+      <c r="E118" s="23">
+        <v>26</v>
+      </c>
+      <c r="F118" s="23">
+        <f t="shared" si="1"/>
+        <v>25.5</v>
+      </c>
+      <c r="G118" s="19">
+        <f t="shared" si="2"/>
+        <v>5.5026892842366497E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7">
+      <c r="B119" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="C119" s="23">
+        <v>23.36</v>
+      </c>
+      <c r="D119" s="23">
+        <v>24</v>
+      </c>
+      <c r="E119" s="23">
+        <v>26</v>
+      </c>
+      <c r="F119" s="23">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="G119" s="19">
+        <f t="shared" si="2"/>
+        <v>7.0205479452054825E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7">
+      <c r="B120" s="17" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C120" s="23">
+        <v>34.08</v>
+      </c>
+      <c r="D120" s="23">
+        <v>33</v>
+      </c>
+      <c r="E120" s="23">
+        <v>38</v>
+      </c>
+      <c r="F120" s="23">
+        <f t="shared" si="1"/>
+        <v>35.5</v>
+      </c>
+      <c r="G120" s="19">
+        <f t="shared" si="2"/>
+        <v>4.166666666666672E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7">
+      <c r="B121" s="17" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C121" s="23">
+        <v>24.96</v>
+      </c>
+      <c r="D121" s="23">
+        <v>28</v>
+      </c>
+      <c r="E121" s="23">
+        <v>32</v>
+      </c>
+      <c r="F121" s="23">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G121" s="19">
+        <f t="shared" si="2"/>
+        <v>0.20192307692307687</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7">
+      <c r="B122" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="C122" s="23">
+        <v>29.71</v>
+      </c>
+      <c r="D122" s="23">
+        <v>30</v>
+      </c>
+      <c r="E122" s="23">
+        <v>32</v>
+      </c>
+      <c r="F122" s="23">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="G122" s="19">
+        <f t="shared" si="2"/>
+        <v>4.3419723998653625E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7">
+      <c r="B123" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="C123" s="23">
+        <v>25.73</v>
+      </c>
+      <c r="D123" s="23">
+        <v>27</v>
+      </c>
+      <c r="E123" s="23">
+        <v>29</v>
+      </c>
+      <c r="F123" s="23">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="G123" s="19">
+        <f t="shared" si="2"/>
+        <v>8.8223863194714328E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7">
+      <c r="B124" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="C124" s="23">
+        <v>21.19</v>
+      </c>
+      <c r="D124" s="23">
+        <v>27</v>
+      </c>
+      <c r="E124" s="23">
+        <v>32</v>
+      </c>
+      <c r="F124" s="23">
+        <f t="shared" si="1"/>
+        <v>29.5</v>
+      </c>
+      <c r="G124" s="19">
+        <f t="shared" si="2"/>
+        <v>0.39216611609249635</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7">
+      <c r="B125" s="17" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C125" s="23">
+        <v>26.59</v>
+      </c>
+      <c r="D125" s="23">
+        <v>31</v>
+      </c>
+      <c r="E125" s="23">
+        <v>33</v>
+      </c>
+      <c r="F125" s="23">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="G125" s="19">
+        <f t="shared" si="2"/>
+        <v>0.20345994734862732</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7">
+      <c r="B126" s="17" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C126" s="23">
+        <v>34.36</v>
+      </c>
+      <c r="D126" s="23">
+        <v>33</v>
+      </c>
+      <c r="E126" s="23">
+        <v>38</v>
+      </c>
+      <c r="F126" s="23">
+        <f t="shared" si="1"/>
+        <v>35.5</v>
+      </c>
+      <c r="G126" s="19">
+        <f t="shared" si="2"/>
+        <v>3.3178114086146702E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7">
+      <c r="B127" s="17" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C127" s="23">
+        <v>30.02</v>
+      </c>
+      <c r="D127" s="23">
+        <v>33</v>
+      </c>
+      <c r="E127" s="23">
+        <v>38</v>
+      </c>
+      <c r="F127" s="23">
+        <f t="shared" si="1"/>
+        <v>35.5</v>
+      </c>
+      <c r="G127" s="19">
+        <f t="shared" si="2"/>
+        <v>0.18254497001998668</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7">
+      <c r="B128" s="17" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C128" s="23">
+        <v>26.4</v>
+      </c>
+      <c r="D128" s="23">
+        <v>27</v>
+      </c>
+      <c r="E128" s="23">
+        <v>29</v>
+      </c>
+      <c r="F128" s="23">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="G128" s="19">
+        <f t="shared" si="2"/>
+        <v>6.0606060606060663E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7">
+      <c r="B129" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="C129" s="23">
+        <v>26.84</v>
+      </c>
+      <c r="D129" s="23">
+        <v>26</v>
+      </c>
+      <c r="E129" s="23">
+        <v>28</v>
+      </c>
+      <c r="F129" s="23">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="G129" s="19">
+        <f t="shared" si="2"/>
+        <v>5.9612518628912124E-3</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7">
+      <c r="B130" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C130" s="23">
+        <v>22.84</v>
+      </c>
+      <c r="D130" s="23">
+        <v>25</v>
+      </c>
+      <c r="E130" s="23">
+        <v>26</v>
+      </c>
+      <c r="F130" s="23">
+        <f t="shared" si="1"/>
+        <v>25.5</v>
+      </c>
+      <c r="G130" s="19">
+        <f t="shared" si="2"/>
+        <v>0.11646234676007006</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7">
+      <c r="B131" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C131" s="23">
+        <v>24.46</v>
+      </c>
+      <c r="D131" s="23">
+        <v>26</v>
+      </c>
+      <c r="E131" s="23">
+        <v>26</v>
+      </c>
+      <c r="F131" s="23">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="G131" s="19">
+        <f t="shared" si="2"/>
+        <v>6.2959934587080907E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="2:7">
+      <c r="B132" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C132" s="23">
+        <v>27.11</v>
+      </c>
+      <c r="D132" s="23">
+        <v>32</v>
+      </c>
+      <c r="E132" s="23">
+        <v>33</v>
+      </c>
+      <c r="F132" s="23">
+        <f t="shared" si="1"/>
+        <v>32.5</v>
+      </c>
+      <c r="G132" s="19">
+        <f t="shared" si="2"/>
+        <v>0.19881962375507195</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7">
+      <c r="B133" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C133" s="23">
+        <v>24.35</v>
+      </c>
+      <c r="D133" s="23">
+        <v>26</v>
+      </c>
+      <c r="E133" s="23">
+        <v>26</v>
+      </c>
+      <c r="F133" s="23">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="G133" s="19">
+        <f t="shared" si="2"/>
+        <v>6.7761806981519443E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7">
+      <c r="B134" s="17" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C134" s="23">
+        <v>24.43</v>
+      </c>
+      <c r="D134" s="23">
+        <v>26</v>
+      </c>
+      <c r="E134" s="23">
+        <v>28</v>
+      </c>
+      <c r="F134" s="23">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="G134" s="19">
+        <f t="shared" si="2"/>
+        <v>0.10519852640196481</v>
+      </c>
+    </row>
+    <row r="135" spans="2:7">
+      <c r="B135" s="17" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C135" s="23">
+        <v>26.2</v>
+      </c>
+      <c r="D135" s="23">
+        <v>28</v>
+      </c>
+      <c r="E135" s="23">
+        <v>32</v>
+      </c>
+      <c r="F135" s="23">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G135" s="19">
+        <f t="shared" si="2"/>
+        <v>0.14503816793893132</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7">
+      <c r="B136" s="17" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C136" s="23">
+        <v>26.276250000000001</v>
+      </c>
+      <c r="D136" s="23">
+        <v>28.134374999999999</v>
+      </c>
+      <c r="E136" s="23">
+        <v>30.296875</v>
+      </c>
+    </row>
+    <row r="141" spans="2:7">
+      <c r="B141" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D141" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E141" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G141" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="142" spans="2:7">
+      <c r="B142" s="17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C142" s="23">
+        <v>29.4</v>
+      </c>
+      <c r="D142" s="23">
+        <v>35</v>
+      </c>
+      <c r="E142" s="23">
+        <v>36</v>
+      </c>
+      <c r="F142" s="23">
+        <f>(D142+E142)/2</f>
+        <v>35.5</v>
+      </c>
+      <c r="G142" s="19">
+        <f>(F142-C142)/C142</f>
+        <v>0.20748299319727898</v>
+      </c>
+    </row>
+    <row r="143" spans="2:7">
+      <c r="B143" s="17" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C143" s="23">
+        <v>23.59</v>
+      </c>
+      <c r="D143" s="23">
+        <v>30</v>
+      </c>
+      <c r="E143" s="23">
+        <v>31</v>
+      </c>
+      <c r="F143" s="23">
+        <f t="shared" ref="F143:F173" si="3">(D143+E143)/2</f>
+        <v>30.5</v>
+      </c>
+      <c r="G143" s="19">
+        <f t="shared" ref="G143:G173" si="4">(F143-C143)/C143</f>
+        <v>0.29292072912250955</v>
+      </c>
+    </row>
+    <row r="144" spans="2:7">
+      <c r="B144" s="17" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C144" s="23">
+        <v>25.71</v>
+      </c>
+      <c r="D144" s="23">
+        <v>27</v>
+      </c>
+      <c r="E144" s="23">
+        <v>27</v>
+      </c>
+      <c r="F144" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="G144" s="19">
+        <f t="shared" si="4"/>
+        <v>5.0175029171528551E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="2:7">
+      <c r="B145" s="17" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C145" s="23">
+        <v>24.76</v>
+      </c>
+      <c r="D145" s="23">
+        <v>29</v>
+      </c>
+      <c r="E145" s="23">
+        <v>31</v>
+      </c>
+      <c r="F145" s="23">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="G145" s="19">
+        <f t="shared" si="4"/>
+        <v>0.21163166397415178</v>
+      </c>
+    </row>
+    <row r="146" spans="2:7">
+      <c r="B146" s="17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C146" s="23">
+        <v>22.83</v>
+      </c>
+      <c r="D146" s="23">
+        <v>25</v>
+      </c>
+      <c r="E146" s="23">
+        <v>26</v>
+      </c>
+      <c r="F146" s="23">
+        <f t="shared" si="3"/>
+        <v>25.5</v>
+      </c>
+      <c r="G146" s="19">
+        <f t="shared" si="4"/>
+        <v>0.1169513797634692</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7">
+      <c r="B147" s="17" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C147" s="23">
+        <v>21.64</v>
+      </c>
+      <c r="D147" s="23">
+        <v>26</v>
+      </c>
+      <c r="E147" s="23">
+        <v>28</v>
+      </c>
+      <c r="F147" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="G147" s="19">
+        <f t="shared" si="4"/>
+        <v>0.24768946395563768</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7">
+      <c r="B148" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C148" s="23">
+        <v>29.88</v>
+      </c>
+      <c r="D148" s="23">
+        <v>28</v>
+      </c>
+      <c r="E148" s="23">
+        <v>29</v>
+      </c>
+      <c r="F148" s="23">
+        <f t="shared" si="3"/>
+        <v>28.5</v>
+      </c>
+      <c r="G148" s="19">
+        <f t="shared" si="4"/>
+        <v>-4.6184738955823264E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="2:7">
+      <c r="B149" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="C149" s="23">
+        <v>26.45</v>
+      </c>
+      <c r="D149" s="23">
+        <v>26</v>
+      </c>
+      <c r="E149" s="23">
+        <v>28</v>
+      </c>
+      <c r="F149" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="G149" s="19">
+        <f t="shared" si="4"/>
+        <v>2.0793950850661654E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7">
+      <c r="B150" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="C150" s="23">
+        <v>26.56</v>
+      </c>
+      <c r="D150" s="23">
+        <v>28</v>
+      </c>
+      <c r="E150" s="23">
+        <v>30</v>
+      </c>
+      <c r="F150" s="23">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="G150" s="19">
+        <f t="shared" si="4"/>
+        <v>9.1867469879518118E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="2:7">
+      <c r="B151" s="17" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C151" s="23">
+        <v>27.47</v>
+      </c>
+      <c r="D151" s="23">
+        <v>27.8</v>
+      </c>
+      <c r="E151" s="23">
+        <v>32</v>
+      </c>
+      <c r="F151" s="23">
+        <f t="shared" si="3"/>
+        <v>29.9</v>
+      </c>
+      <c r="G151" s="19">
+        <f t="shared" si="4"/>
+        <v>8.8460138332726604E-2</v>
+      </c>
+    </row>
+    <row r="152" spans="2:7">
+      <c r="B152" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="C152" s="23">
+        <v>26.33</v>
+      </c>
+      <c r="D152" s="23">
+        <v>25</v>
+      </c>
+      <c r="E152" s="23">
+        <v>27</v>
+      </c>
+      <c r="F152" s="23">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="G152" s="19">
+        <f t="shared" si="4"/>
+        <v>-1.2533232054690403E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="2:7">
+      <c r="B153" s="17" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C153" s="23">
+        <v>27.72</v>
+      </c>
+      <c r="D153" s="23">
+        <v>28</v>
+      </c>
+      <c r="E153" s="23">
+        <v>29</v>
+      </c>
+      <c r="F153" s="23">
+        <f t="shared" si="3"/>
+        <v>28.5</v>
+      </c>
+      <c r="G153" s="19">
+        <f t="shared" si="4"/>
+        <v>2.8138528138528181E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="2:7">
+      <c r="B154" s="17" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C154" s="23">
+        <v>25.24</v>
+      </c>
+      <c r="D154" s="23">
+        <v>28</v>
+      </c>
+      <c r="E154" s="23">
+        <v>33</v>
+      </c>
+      <c r="F154" s="23">
+        <f t="shared" si="3"/>
+        <v>30.5</v>
+      </c>
+      <c r="G154" s="19">
+        <f t="shared" si="4"/>
+        <v>0.20839936608557852</v>
+      </c>
+    </row>
+    <row r="155" spans="2:7">
+      <c r="B155" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C155" s="23">
+        <v>26.46</v>
+      </c>
+      <c r="D155" s="23">
+        <v>30.5</v>
+      </c>
+      <c r="E155" s="23">
+        <v>30.5</v>
+      </c>
+      <c r="F155" s="23">
+        <f t="shared" si="3"/>
+        <v>30.5</v>
+      </c>
+      <c r="G155" s="19">
+        <f t="shared" si="4"/>
+        <v>0.15268329554043836</v>
+      </c>
+    </row>
+    <row r="156" spans="2:7">
+      <c r="B156" s="17" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C156" s="23">
+        <v>24.17</v>
+      </c>
+      <c r="D156" s="23">
+        <v>25</v>
+      </c>
+      <c r="E156" s="23">
+        <v>26</v>
+      </c>
+      <c r="F156" s="23">
+        <f t="shared" si="3"/>
+        <v>25.5</v>
+      </c>
+      <c r="G156" s="19">
+        <f t="shared" si="4"/>
+        <v>5.5026892842366497E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7">
+      <c r="B157" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="C157" s="23">
+        <v>23.36</v>
+      </c>
+      <c r="D157" s="23">
+        <v>24</v>
+      </c>
+      <c r="E157" s="23">
+        <v>26</v>
+      </c>
+      <c r="F157" s="23">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="G157" s="19">
+        <f t="shared" si="4"/>
+        <v>7.0205479452054825E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:7">
+      <c r="B158" s="17" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C158" s="23">
+        <v>34.08</v>
+      </c>
+      <c r="D158" s="23">
+        <v>33</v>
+      </c>
+      <c r="E158" s="23">
+        <v>38</v>
+      </c>
+      <c r="F158" s="23">
+        <f t="shared" si="3"/>
+        <v>35.5</v>
+      </c>
+      <c r="G158" s="19">
+        <f t="shared" si="4"/>
+        <v>4.166666666666672E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7">
+      <c r="B159" s="17" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C159" s="23">
+        <v>24.96</v>
+      </c>
+      <c r="D159" s="23">
+        <v>28</v>
+      </c>
+      <c r="E159" s="23">
+        <v>32</v>
+      </c>
+      <c r="F159" s="23">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="G159" s="19">
+        <f t="shared" si="4"/>
+        <v>0.20192307692307687</v>
+      </c>
+    </row>
+    <row r="160" spans="2:7">
+      <c r="B160" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="C160" s="23">
+        <v>29.71</v>
+      </c>
+      <c r="D160" s="23">
+        <v>30</v>
+      </c>
+      <c r="E160" s="23">
+        <v>32</v>
+      </c>
+      <c r="F160" s="23">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="G160" s="19">
+        <f t="shared" si="4"/>
+        <v>4.3419723998653625E-2</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7">
+      <c r="B161" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="C161" s="23">
+        <v>25.73</v>
+      </c>
+      <c r="D161" s="23">
+        <v>27</v>
+      </c>
+      <c r="E161" s="23">
+        <v>29</v>
+      </c>
+      <c r="F161" s="23">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="G161" s="19">
+        <f t="shared" si="4"/>
+        <v>8.8223863194714328E-2</v>
+      </c>
+    </row>
+    <row r="162" spans="2:7">
+      <c r="B162" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="C162" s="23">
+        <v>21.19</v>
+      </c>
+      <c r="D162" s="23">
+        <v>27</v>
+      </c>
+      <c r="E162" s="23">
+        <v>32</v>
+      </c>
+      <c r="F162" s="23">
+        <f t="shared" si="3"/>
+        <v>29.5</v>
+      </c>
+      <c r="G162" s="19">
+        <f t="shared" si="4"/>
+        <v>0.39216611609249635</v>
+      </c>
+    </row>
+    <row r="163" spans="2:7">
+      <c r="B163" s="17" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C163" s="23">
+        <v>26.59</v>
+      </c>
+      <c r="D163" s="23">
+        <v>31</v>
+      </c>
+      <c r="E163" s="23">
+        <v>33</v>
+      </c>
+      <c r="F163" s="23">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="G163" s="19">
+        <f t="shared" si="4"/>
+        <v>0.20345994734862732</v>
+      </c>
+    </row>
+    <row r="164" spans="2:7">
+      <c r="B164" s="17" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C164" s="23">
+        <v>34.36</v>
+      </c>
+      <c r="D164" s="23">
+        <v>33</v>
+      </c>
+      <c r="E164" s="23">
+        <v>38</v>
+      </c>
+      <c r="F164" s="23">
+        <f t="shared" si="3"/>
+        <v>35.5</v>
+      </c>
+      <c r="G164" s="19">
+        <f t="shared" si="4"/>
+        <v>3.3178114086146702E-2</v>
+      </c>
+    </row>
+    <row r="165" spans="2:7">
+      <c r="B165" s="17" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C165" s="23">
+        <v>30.02</v>
+      </c>
+      <c r="D165" s="23">
+        <v>33</v>
+      </c>
+      <c r="E165" s="23">
+        <v>38</v>
+      </c>
+      <c r="F165" s="23">
+        <f t="shared" si="3"/>
+        <v>35.5</v>
+      </c>
+      <c r="G165" s="19">
+        <f t="shared" si="4"/>
+        <v>0.18254497001998668</v>
+      </c>
+    </row>
+    <row r="166" spans="2:7">
+      <c r="B166" s="17" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C166" s="23">
+        <v>26.4</v>
+      </c>
+      <c r="D166" s="23">
+        <v>27</v>
+      </c>
+      <c r="E166" s="23">
+        <v>29</v>
+      </c>
+      <c r="F166" s="23">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="G166" s="19">
+        <f t="shared" si="4"/>
+        <v>6.0606060606060663E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="2:7">
+      <c r="B167" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="C167" s="23">
+        <v>26.84</v>
+      </c>
+      <c r="D167" s="23">
+        <v>26</v>
+      </c>
+      <c r="E167" s="23">
+        <v>28</v>
+      </c>
+      <c r="F167" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="G167" s="19">
+        <f t="shared" si="4"/>
+        <v>5.9612518628912124E-3</v>
+      </c>
+    </row>
+    <row r="168" spans="2:7">
+      <c r="B168" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C168" s="23">
+        <v>22.84</v>
+      </c>
+      <c r="D168" s="23">
+        <v>25</v>
+      </c>
+      <c r="E168" s="23">
+        <v>26</v>
+      </c>
+      <c r="F168" s="23">
+        <f t="shared" si="3"/>
+        <v>25.5</v>
+      </c>
+      <c r="G168" s="19">
+        <f t="shared" si="4"/>
+        <v>0.11646234676007006</v>
+      </c>
+    </row>
+    <row r="169" spans="2:7">
+      <c r="B169" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C169" s="23">
+        <v>24.46</v>
+      </c>
+      <c r="D169" s="23">
+        <v>26</v>
+      </c>
+      <c r="E169" s="23">
+        <v>26</v>
+      </c>
+      <c r="F169" s="23">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="G169" s="19">
+        <f t="shared" si="4"/>
+        <v>6.2959934587080907E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="2:7">
+      <c r="B170" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C170" s="23">
+        <v>27.11</v>
+      </c>
+      <c r="D170" s="23">
+        <v>32</v>
+      </c>
+      <c r="E170" s="23">
+        <v>33</v>
+      </c>
+      <c r="F170" s="23">
+        <f t="shared" si="3"/>
+        <v>32.5</v>
+      </c>
+      <c r="G170" s="19">
+        <f t="shared" si="4"/>
+        <v>0.19881962375507195</v>
+      </c>
+    </row>
+    <row r="171" spans="2:7">
+      <c r="B171" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C171" s="23">
+        <v>24.35</v>
+      </c>
+      <c r="D171" s="23">
+        <v>26</v>
+      </c>
+      <c r="E171" s="23">
+        <v>26</v>
+      </c>
+      <c r="F171" s="23">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="G171" s="19">
+        <f t="shared" si="4"/>
+        <v>6.7761806981519443E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="2:7">
+      <c r="B172" s="17" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C172" s="23">
+        <v>24.43</v>
+      </c>
+      <c r="D172" s="23">
+        <v>26</v>
+      </c>
+      <c r="E172" s="23">
+        <v>28</v>
+      </c>
+      <c r="F172" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="G172" s="19">
+        <f t="shared" si="4"/>
+        <v>0.10519852640196481</v>
+      </c>
+    </row>
+    <row r="173" spans="2:7">
+      <c r="B173" s="17" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C173" s="23">
+        <v>26.2</v>
+      </c>
+      <c r="D173" s="23">
+        <v>28</v>
+      </c>
+      <c r="E173" s="23">
+        <v>32</v>
+      </c>
+      <c r="F173" s="23">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="G173" s="19">
+        <f t="shared" si="4"/>
+        <v>0.14503816793893132</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3">
+      <c r="B179" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C179" s="19" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3">
+      <c r="B180" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="C180" s="19">
+        <v>0.39216611609249635</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3">
+      <c r="B181" s="17" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C181" s="19">
+        <v>0.29292072912250955</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3">
+      <c r="B182" s="17" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C182" s="19">
+        <v>0.24768946395563768</v>
+      </c>
+    </row>
+    <row r="183" spans="2:3">
+      <c r="B183" s="17" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C183" s="19">
+        <v>0.21163166397415178</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3">
+      <c r="B184" s="17" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C184" s="19">
+        <v>0.20839936608557852</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3">
+      <c r="B185" s="17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C185" s="19">
+        <v>0.20748299319727898</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3">
+      <c r="B186" s="17" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C186" s="19">
+        <v>0.20345994734862732</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3">
+      <c r="B187" s="17" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C187" s="19">
+        <v>0.20192307692307687</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3">
+      <c r="B188" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C188" s="19">
+        <v>0.19881962375507195</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3">
+      <c r="B189" s="17" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C189" s="19">
+        <v>0.18254497001998668</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3">
+      <c r="B190" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C190" s="19">
+        <v>0.15268329554043836</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3">
+      <c r="B191" s="17" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C191" s="19">
+        <v>0.14503816793893132</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3">
+      <c r="B192" s="17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C192" s="19">
+        <v>0.1169513797634692</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3">
+      <c r="B193" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C193" s="19">
+        <v>0.11646234676007006</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3">
+      <c r="B194" s="17" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C194" s="19">
+        <v>0.10519852640196481</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3">
+      <c r="B195" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="C195" s="19">
+        <v>9.1867469879518118E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="2:3">
+      <c r="B196" s="17" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C196" s="19">
+        <v>8.8460138332726604E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3">
+      <c r="B197" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="C197" s="19">
+        <v>8.8223863194714328E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3">
+      <c r="B198" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="C198" s="19">
+        <v>7.0205479452054825E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3">
+      <c r="B199" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C199" s="19">
+        <v>6.7761806981519443E-2</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3">
+      <c r="B200" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C200" s="19">
+        <v>6.2959934587080907E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3">
+      <c r="B201" s="17" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C201" s="19">
+        <v>6.0606060606060663E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="2:3">
+      <c r="B202" s="17" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C202" s="19">
+        <v>5.5026892842366497E-2</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3">
+      <c r="B203" s="17" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C203" s="19">
+        <v>5.0175029171528551E-2</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3">
+      <c r="B204" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="C204" s="19">
+        <v>4.3419723998653625E-2</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3">
+      <c r="B205" s="17" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C205" s="19">
+        <v>4.166666666666672E-2</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3">
+      <c r="B206" s="17" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C206" s="19">
+        <v>3.3178114086146702E-2</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3">
+      <c r="B207" s="17" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C207" s="19">
+        <v>2.8138528138528181E-2</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3">
+      <c r="B208" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="C208" s="19">
+        <v>2.0793950850661654E-2</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3">
+      <c r="B209" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="C209" s="19">
+        <v>5.9612518628912124E-3</v>
+      </c>
+    </row>
+    <row r="210" spans="2:3">
+      <c r="B210" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="C210" s="19">
+        <v>-1.2533232054690403E-2</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3">
+      <c r="B211" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C211" s="19">
+        <v>-4.6184738955823264E-2</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B180:C211">
+    <sortCondition descending="1" ref="C180:C211"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
